--- a/data/sample_data1.xlsx
+++ b/data/sample_data1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\00.디혁\04.대시보드\3.운영\5.개발\2023.03.13_actuarial Report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MALIFE\Documents\Actuarial-Report\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -522,7 +522,7 @@
         <v>8</v>
       </c>
       <c r="F2" s="4">
-        <v>47.459872109999999</v>
+        <v>18.983948844</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -562,7 +562,7 @@
         <v>13</v>
       </c>
       <c r="F4" s="4">
-        <v>-2.4560068400000001</v>
+        <v>-0.98240273600000005</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -582,7 +582,7 @@
         <v>14</v>
       </c>
       <c r="F5" s="4">
-        <v>41.457804269999997</v>
+        <v>16.583121708</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -602,7 +602,7 @@
         <v>11</v>
       </c>
       <c r="F6" s="4">
-        <v>7.7033082300000002</v>
+        <v>3.0813232920000004</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -622,7 +622,7 @@
         <v>14</v>
       </c>
       <c r="F7" s="4">
-        <v>39.0127363</v>
+        <v>15.605094520000002</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -642,7 +642,7 @@
         <v>15</v>
       </c>
       <c r="F8" s="4">
-        <v>2.4128944899999998</v>
+        <v>0.96515779599999996</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -662,7 +662,7 @@
         <v>13</v>
       </c>
       <c r="F9" s="4">
-        <v>-2.5172661500000002</v>
+        <v>-1.0069064600000002</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -702,7 +702,7 @@
         <v>11</v>
       </c>
       <c r="F11" s="4">
-        <v>11.63906697</v>
+        <v>4.6556267880000002</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -722,7 +722,7 @@
         <v>13</v>
       </c>
       <c r="F12" s="4">
-        <v>-1.4347896</v>
+        <v>-0.57391584000000007</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -742,7 +742,7 @@
         <v>13</v>
       </c>
       <c r="F13" s="4">
-        <v>-2.2464837200000001</v>
+        <v>-0.89859348800000005</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -802,7 +802,7 @@
         <v>8</v>
       </c>
       <c r="F16" s="4">
-        <v>47.200505200000002</v>
+        <v>18.88020208</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -842,7 +842,7 @@
         <v>15</v>
       </c>
       <c r="F18" s="4">
-        <v>0.55590993</v>
+        <v>0.22236397200000002</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -862,7 +862,7 @@
         <v>11</v>
       </c>
       <c r="F19" s="4">
-        <v>11.77422228</v>
+        <v>4.7096889119999998</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -882,7 +882,7 @@
         <v>18</v>
       </c>
       <c r="F20" s="4">
-        <v>46.205529859999999</v>
+        <v>18.482211943999999</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -902,7 +902,7 @@
         <v>19</v>
       </c>
       <c r="F21" s="4">
-        <v>0.46632206999999998</v>
+        <v>0.18652882800000001</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -922,7 +922,7 @@
         <v>15</v>
       </c>
       <c r="F22" s="4">
-        <v>0.56734658999999998</v>
+        <v>0.226938636</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -962,7 +962,7 @@
         <v>20</v>
       </c>
       <c r="F24" s="4">
-        <v>45.473492960000002</v>
+        <v>18.189397184000001</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -982,7 +982,7 @@
         <v>21</v>
       </c>
       <c r="F25" s="4">
-        <v>8.1499232500000005</v>
+        <v>3.2599693000000003</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
@@ -1022,7 +1022,7 @@
         <v>14</v>
       </c>
       <c r="F27" s="4">
-        <v>41.457804269999997</v>
+        <v>16.583121708</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -1042,7 +1042,7 @@
         <v>19</v>
       </c>
       <c r="F28" s="4">
-        <v>-0.13058122</v>
+        <v>-5.2232488000000001E-2</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
@@ -1082,7 +1082,7 @@
         <v>23</v>
       </c>
       <c r="F30" s="4">
-        <v>34.813882069999998</v>
+        <v>13.925552828000001</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
@@ -1122,7 +1122,7 @@
         <v>21</v>
       </c>
       <c r="F32" s="4">
-        <v>1.41831391</v>
+        <v>0.567325564</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
@@ -1142,7 +1142,7 @@
         <v>13</v>
       </c>
       <c r="F33" s="4">
-        <v>0.19881726</v>
+        <v>7.9526904000000009E-2</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -1162,7 +1162,7 @@
         <v>11</v>
       </c>
       <c r="F34" s="4">
-        <v>11.52856448</v>
+        <v>4.6114257920000004</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
@@ -1182,7 +1182,7 @@
         <v>24</v>
       </c>
       <c r="F35" s="4">
-        <v>-1.5505307699999999</v>
+        <v>-0.62021230800000005</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
@@ -1202,7 +1202,7 @@
         <v>11</v>
       </c>
       <c r="F36" s="4">
-        <v>8.1827419199999998</v>
+        <v>3.2730967680000003</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -1222,7 +1222,7 @@
         <v>23</v>
       </c>
       <c r="F37" s="4">
-        <v>37.073559349999996</v>
+        <v>14.829423739999999</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
@@ -1242,7 +1242,7 @@
         <v>21</v>
       </c>
       <c r="F38" s="4">
-        <v>1.3045180199999999</v>
+        <v>0.52180720800000002</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -1262,7 +1262,7 @@
         <v>21</v>
       </c>
       <c r="F39" s="4">
-        <v>8.3068545300000007</v>
+        <v>3.3227418120000003</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
@@ -1282,7 +1282,7 @@
         <v>21</v>
       </c>
       <c r="F40" s="4">
-        <v>1.2559540199999999</v>
+        <v>0.50238160799999998</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -1302,7 +1302,7 @@
         <v>21</v>
       </c>
       <c r="F41" s="4">
-        <v>8.5246920199999998</v>
+        <v>3.4098768079999999</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
@@ -1322,7 +1322,7 @@
         <v>14</v>
       </c>
       <c r="F42" s="4">
-        <v>40.26744308</v>
+        <v>16.106977232000002</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
@@ -1342,7 +1342,7 @@
         <v>24</v>
       </c>
       <c r="F43" s="4">
-        <v>-19.048524159999999</v>
+        <v>-7.619409664</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -1362,7 +1362,7 @@
         <v>15</v>
       </c>
       <c r="F44" s="4">
-        <v>0.68614984000000001</v>
+        <v>0.27445993600000002</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -1382,7 +1382,7 @@
         <v>15</v>
       </c>
       <c r="F45" s="4">
-        <v>0.33769486999999998</v>
+        <v>0.135077948</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -1402,7 +1402,7 @@
         <v>21</v>
       </c>
       <c r="F46" s="4">
-        <v>1.5740006200000001</v>
+        <v>0.62960024800000003</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -1442,7 +1442,7 @@
         <v>26</v>
       </c>
       <c r="F48" s="4">
-        <v>42.206015059999999</v>
+        <v>16.882406024000002</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
@@ -1462,7 +1462,7 @@
         <v>21</v>
       </c>
       <c r="F49" s="4">
-        <v>9.3894007300000002</v>
+        <v>3.7557602920000002</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
@@ -1482,7 +1482,7 @@
         <v>14</v>
       </c>
       <c r="F50" s="4">
-        <v>57.036192870000001</v>
+        <v>22.814477148000002</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
@@ -1522,7 +1522,7 @@
         <v>21</v>
       </c>
       <c r="F52" s="4">
-        <v>1.3636051899999999</v>
+        <v>0.54544207599999994</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
@@ -1542,7 +1542,7 @@
         <v>13</v>
       </c>
       <c r="F53" s="4">
-        <v>-2.5598360499999999</v>
+        <v>-1.02393442</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
@@ -1562,7 +1562,7 @@
         <v>14</v>
       </c>
       <c r="F54" s="4">
-        <v>76.893692040000005</v>
+        <v>30.757476816000004</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
@@ -1582,7 +1582,7 @@
         <v>27</v>
       </c>
       <c r="F55" s="4">
-        <v>0.58086691999999995</v>
+        <v>0.23234676799999998</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
@@ -1622,7 +1622,7 @@
         <v>21</v>
       </c>
       <c r="F57" s="4">
-        <v>8.10499978</v>
+        <v>3.2419999120000003</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
@@ -1642,7 +1642,7 @@
         <v>19</v>
       </c>
       <c r="F58" s="4">
-        <v>-0.1614294</v>
+        <v>-6.4571760000000006E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
@@ -1662,7 +1662,7 @@
         <v>27</v>
       </c>
       <c r="F59" s="4">
-        <v>4.1264735799999999</v>
+        <v>1.6505894320000001</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
@@ -1682,7 +1682,7 @@
         <v>19</v>
       </c>
       <c r="F60" s="4">
-        <v>-1.3934100000000001E-3</v>
+        <v>-5.5736400000000008E-4</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
@@ -1702,7 +1702,7 @@
         <v>13</v>
       </c>
       <c r="F61" s="4">
-        <v>-2.0879523299999998</v>
+        <v>-0.83518093199999999</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
@@ -1722,7 +1722,7 @@
         <v>8</v>
       </c>
       <c r="F62" s="4">
-        <v>46.743538989999998</v>
+        <v>18.697415595999999</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
@@ -1742,7 +1742,7 @@
         <v>8</v>
       </c>
       <c r="F63" s="4">
-        <v>55.660736159999999</v>
+        <v>22.264294464000002</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
@@ -1762,7 +1762,7 @@
         <v>24</v>
       </c>
       <c r="F64" s="4">
-        <v>15.751989249999999</v>
+        <v>6.3007957000000001</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
@@ -1782,7 +1782,7 @@
         <v>13</v>
       </c>
       <c r="F65" s="4">
-        <v>1.71075128</v>
+        <v>0.68430051200000008</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
@@ -1802,7 +1802,7 @@
         <v>18</v>
       </c>
       <c r="F66" s="4">
-        <v>45.812387180000002</v>
+        <v>18.324954872000003</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
@@ -1822,7 +1822,7 @@
         <v>23</v>
       </c>
       <c r="F67" s="4">
-        <v>15.615153879999999</v>
+        <v>6.2460615520000005</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
@@ -1842,7 +1842,7 @@
         <v>20</v>
       </c>
       <c r="F68" s="4">
-        <v>307.28727873999998</v>
+        <v>122.914911496</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
@@ -1862,7 +1862,7 @@
         <v>18</v>
       </c>
       <c r="F69" s="4">
-        <v>84.108104089999998</v>
+        <v>33.643241635999999</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
@@ -1882,7 +1882,7 @@
         <v>13</v>
       </c>
       <c r="F70" s="4">
-        <v>-2.3370342800000001</v>
+        <v>-0.93481371200000007</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
@@ -1902,7 +1902,7 @@
         <v>8</v>
       </c>
       <c r="F71" s="4">
-        <v>45.126340169999999</v>
+        <v>18.050536068</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
@@ -1922,7 +1922,7 @@
         <v>21</v>
       </c>
       <c r="F72" s="4">
-        <v>1.37950913</v>
+        <v>0.55180365200000003</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
@@ -1942,7 +1942,7 @@
         <v>19</v>
       </c>
       <c r="F73" s="4">
-        <v>-9.1283520000000007E-2</v>
+        <v>-3.6513408000000004E-2</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
@@ -1962,7 +1962,7 @@
         <v>13</v>
       </c>
       <c r="F74" s="4">
-        <v>-2.1224342900000002</v>
+        <v>-0.84897371600000016</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
@@ -1982,7 +1982,7 @@
         <v>11</v>
       </c>
       <c r="F75" s="4">
-        <v>7.8369094400000003</v>
+        <v>3.1347637760000002</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
@@ -2002,7 +2002,7 @@
         <v>23</v>
       </c>
       <c r="F76" s="4">
-        <v>15.637141850000001</v>
+        <v>6.254856740000001</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
@@ -2042,7 +2042,7 @@
         <v>21</v>
       </c>
       <c r="F78" s="4">
-        <v>2.3809188400000001</v>
+        <v>0.95236753600000013</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
@@ -2062,7 +2062,7 @@
         <v>23</v>
       </c>
       <c r="F79" s="4">
-        <v>15.78785149</v>
+        <v>6.315140596</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
@@ -2082,7 +2082,7 @@
         <v>11</v>
       </c>
       <c r="F80" s="4">
-        <v>7.9790079699999996</v>
+        <v>3.1916031880000002</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
@@ -2162,7 +2162,7 @@
         <v>20</v>
       </c>
       <c r="F84" s="4">
-        <v>102.97683134</v>
+        <v>41.190732536000006</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
@@ -2202,7 +2202,7 @@
         <v>27</v>
       </c>
       <c r="F86" s="4">
-        <v>1.3680004800000001</v>
+        <v>0.54720019200000003</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
@@ -2222,7 +2222,7 @@
         <v>23</v>
       </c>
       <c r="F87" s="4">
-        <v>36.363534659999999</v>
+        <v>14.545413864</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
@@ -2242,7 +2242,7 @@
         <v>23</v>
       </c>
       <c r="F88" s="4">
-        <v>37.427237030000001</v>
+        <v>14.970894812000001</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
@@ -2262,7 +2262,7 @@
         <v>14</v>
       </c>
       <c r="F89" s="4">
-        <v>72.966564059999996</v>
+        <v>29.186625624000001</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
@@ -2302,7 +2302,7 @@
         <v>13</v>
       </c>
       <c r="F91" s="4">
-        <v>-9.7571550000000007E-2</v>
+        <v>-3.9028620000000007E-2</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
@@ -2322,7 +2322,7 @@
         <v>27</v>
       </c>
       <c r="F92" s="4">
-        <v>24.399193149999999</v>
+        <v>9.7596772600000001</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
@@ -2342,7 +2342,7 @@
         <v>13</v>
       </c>
       <c r="F93" s="4">
-        <v>-2.3370342800000001</v>
+        <v>-0.93481371200000007</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
@@ -2362,7 +2362,7 @@
         <v>14</v>
       </c>
       <c r="F94" s="4">
-        <v>90.781570430000002</v>
+        <v>36.312628172000004</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
@@ -2382,7 +2382,7 @@
         <v>23</v>
       </c>
       <c r="F95" s="4">
-        <v>31.84185883</v>
+        <v>12.736743532</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
@@ -2402,7 +2402,7 @@
         <v>23</v>
       </c>
       <c r="F96" s="4">
-        <v>12.66808779</v>
+        <v>5.067235116</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
@@ -2422,7 +2422,7 @@
         <v>13</v>
       </c>
       <c r="F97" s="4">
-        <v>-0.65467841999999998</v>
+        <v>-0.26187136799999999</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
@@ -2462,7 +2462,7 @@
         <v>8</v>
       </c>
       <c r="F99" s="4">
-        <v>79.358595780000002</v>
+        <v>31.743438312000002</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
@@ -2482,7 +2482,7 @@
         <v>13</v>
       </c>
       <c r="F100" s="4">
-        <v>-2.5172661500000002</v>
+        <v>-1.0069064600000002</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
@@ -2522,7 +2522,7 @@
         <v>13</v>
       </c>
       <c r="F102" s="4">
-        <v>-0.74697409999999997</v>
+        <v>-0.29878964000000002</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
@@ -2562,7 +2562,7 @@
         <v>8</v>
       </c>
       <c r="F104" s="4">
-        <v>84.697050790000006</v>
+        <v>33.878820316000002</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
@@ -2582,7 +2582,7 @@
         <v>23</v>
       </c>
       <c r="F105" s="4">
-        <v>15.94541091</v>
+        <v>6.3781643639999999</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
@@ -2602,7 +2602,7 @@
         <v>23</v>
       </c>
       <c r="F106" s="4">
-        <v>15.97432807</v>
+        <v>6.3897312280000005</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
@@ -2622,7 +2622,7 @@
         <v>23</v>
       </c>
       <c r="F107" s="4">
-        <v>35.521017649999997</v>
+        <v>14.208407059999999</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
@@ -2642,7 +2642,7 @@
         <v>11</v>
       </c>
       <c r="F108" s="4">
-        <v>18.731223010000001</v>
+        <v>7.4924892040000008</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
@@ -2682,7 +2682,7 @@
         <v>11</v>
       </c>
       <c r="F110" s="4">
-        <v>7.7999352399999999</v>
+        <v>3.119974096</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
@@ -2702,7 +2702,7 @@
         <v>14</v>
       </c>
       <c r="F111" s="4">
-        <v>81.493693019999995</v>
+        <v>32.597477208000001</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
@@ -2722,7 +2722,7 @@
         <v>14</v>
       </c>
       <c r="F112" s="4">
-        <v>67.528705540000004</v>
+        <v>27.011482216000005</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
@@ -2742,7 +2742,7 @@
         <v>20</v>
       </c>
       <c r="F113" s="4">
-        <v>313.54666679000002</v>
+        <v>125.41866671600002</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
@@ -2782,7 +2782,7 @@
         <v>14</v>
       </c>
       <c r="F115" s="4">
-        <v>76.320735979999995</v>
+        <v>30.528294391999999</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
@@ -2802,7 +2802,7 @@
         <v>15</v>
       </c>
       <c r="F116" s="4">
-        <v>2.4538947000000002</v>
+        <v>0.9815578800000001</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
@@ -2822,7 +2822,7 @@
         <v>13</v>
       </c>
       <c r="F117" s="4">
-        <v>-0.30025081999999997</v>
+        <v>-0.12010032799999999</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
@@ -2842,7 +2842,7 @@
         <v>14</v>
       </c>
       <c r="F118" s="4">
-        <v>81.493693019999995</v>
+        <v>32.597477208000001</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
@@ -2862,7 +2862,7 @@
         <v>14</v>
       </c>
       <c r="F119" s="4">
-        <v>63.328390429999999</v>
+        <v>25.331356172</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
@@ -2882,7 +2882,7 @@
         <v>24</v>
       </c>
       <c r="F120" s="4">
-        <v>1.4713920599999999</v>
+        <v>0.58855682399999998</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
@@ -2922,7 +2922,7 @@
         <v>18</v>
       </c>
       <c r="F122" s="4">
-        <v>286.47837981999999</v>
+        <v>114.59135192799999</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
@@ -2942,7 +2942,7 @@
         <v>26</v>
       </c>
       <c r="F123" s="4">
-        <v>72.973716300000007</v>
+        <v>29.189486520000003</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
@@ -2962,7 +2962,7 @@
         <v>21</v>
       </c>
       <c r="F124" s="4">
-        <v>1.5936275600000001</v>
+        <v>0.63745102400000009</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
@@ -2982,7 +2982,7 @@
         <v>15</v>
       </c>
       <c r="F125" s="4">
-        <v>0.55821805999999996</v>
+        <v>0.22328722400000001</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
@@ -3002,7 +3002,7 @@
         <v>24</v>
       </c>
       <c r="F126" s="4">
-        <v>-19.03465662</v>
+        <v>-7.6138626480000005</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
@@ -3042,7 +3042,7 @@
         <v>24</v>
       </c>
       <c r="F128" s="4">
-        <v>32.868670870000003</v>
+        <v>13.147468348000002</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
@@ -3062,7 +3062,7 @@
         <v>21</v>
       </c>
       <c r="F129" s="4">
-        <v>1.60632504</v>
+        <v>0.64253001600000004</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
@@ -3102,7 +3102,7 @@
         <v>8</v>
       </c>
       <c r="F131" s="4">
-        <v>47.325545630000001</v>
+        <v>18.930218252</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
@@ -3142,7 +3142,7 @@
         <v>13</v>
       </c>
       <c r="F133" s="4">
-        <v>-2.3340410500000002</v>
+        <v>-0.93361642000000011</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
@@ -3182,7 +3182,7 @@
         <v>23</v>
       </c>
       <c r="F135" s="4">
-        <v>15.960856789999999</v>
+        <v>6.3843427159999999</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
@@ -3202,7 +3202,7 @@
         <v>19</v>
       </c>
       <c r="F136" s="4">
-        <v>-6.7084069999999996E-2</v>
+        <v>-2.6833627999999998E-2</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
@@ -3242,7 +3242,7 @@
         <v>23</v>
       </c>
       <c r="F138" s="4">
-        <v>36.502484039999999</v>
+        <v>14.600993616</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
@@ -3262,7 +3262,7 @@
         <v>19</v>
       </c>
       <c r="F139" s="4">
-        <v>5.9131179999999998E-2</v>
+        <v>2.3652472000000001E-2</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
@@ -3282,7 +3282,7 @@
         <v>27</v>
       </c>
       <c r="F140" s="4">
-        <v>2.09756477</v>
+        <v>0.83902590799999999</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
@@ -3302,7 +3302,7 @@
         <v>20</v>
       </c>
       <c r="F141" s="4">
-        <v>35.587314139999997</v>
+        <v>14.234925656</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
@@ -3322,7 +3322,7 @@
         <v>20</v>
       </c>
       <c r="F142" s="4">
-        <v>82.988038239999995</v>
+        <v>33.195215296000001</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
@@ -3342,7 +3342,7 @@
         <v>13</v>
       </c>
       <c r="F143" s="4">
-        <v>-0.65978711000000001</v>
+        <v>-0.26391484400000004</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
@@ -3362,7 +3362,7 @@
         <v>21</v>
       </c>
       <c r="F144" s="4">
-        <v>1.32679904</v>
+        <v>0.53071961600000006</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
@@ -3382,7 +3382,7 @@
         <v>11</v>
       </c>
       <c r="F145" s="4">
-        <v>7.9479024999999996</v>
+        <v>3.1791610000000001</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
@@ -3402,7 +3402,7 @@
         <v>21</v>
       </c>
       <c r="F146" s="4">
-        <v>0.94437842000000005</v>
+        <v>0.37775136800000003</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
@@ -3442,7 +3442,7 @@
         <v>20</v>
       </c>
       <c r="F148" s="4">
-        <v>81.164360090000002</v>
+        <v>32.465744036000004</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
@@ -3462,7 +3462,7 @@
         <v>27</v>
       </c>
       <c r="F149" s="4">
-        <v>6.3322522599999997</v>
+        <v>2.5329009039999999</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
@@ -3502,7 +3502,7 @@
         <v>11</v>
       </c>
       <c r="F151" s="4">
-        <v>11.426033500000001</v>
+        <v>4.5704134000000005</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
@@ -3522,7 +3522,7 @@
         <v>14</v>
       </c>
       <c r="F152" s="4">
-        <v>71.135159349999995</v>
+        <v>28.454063739999999</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.3">
@@ -3542,7 +3542,7 @@
         <v>21</v>
       </c>
       <c r="F153" s="4">
-        <v>8.3137036299999991</v>
+        <v>3.325481452</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.3">
@@ -3562,7 +3562,7 @@
         <v>24</v>
       </c>
       <c r="F154" s="4">
-        <v>22.916858189999999</v>
+        <v>9.1667432760000001</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.3">
@@ -3582,7 +3582,7 @@
         <v>14</v>
       </c>
       <c r="F155" s="4">
-        <v>35.757629659999999</v>
+        <v>14.303051864</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.3">
@@ -3602,7 +3602,7 @@
         <v>15</v>
       </c>
       <c r="F156" s="4">
-        <v>0.64416773000000005</v>
+        <v>0.25766709200000004</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.3">
@@ -3622,7 +3622,7 @@
         <v>13</v>
       </c>
       <c r="F157" s="4">
-        <v>0.30638693</v>
+        <v>0.12255477200000001</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.3">
@@ -3642,7 +3642,7 @@
         <v>19</v>
       </c>
       <c r="F158" s="4">
-        <v>-4.3639730000000002E-2</v>
+        <v>-1.7455892000000001E-2</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.3">
@@ -3662,7 +3662,7 @@
         <v>19</v>
       </c>
       <c r="F159" s="4">
-        <v>-0.27510236999999998</v>
+        <v>-0.110040948</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.3">
@@ -3702,7 +3702,7 @@
         <v>13</v>
       </c>
       <c r="F161" s="4">
-        <v>-0.56339899000000004</v>
+        <v>-0.22535959600000002</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.3">
@@ -3742,7 +3742,7 @@
         <v>21</v>
       </c>
       <c r="F163" s="4">
-        <v>1.4015539299999999</v>
+        <v>0.56062157199999996</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.3">
@@ -3762,7 +3762,7 @@
         <v>15</v>
       </c>
       <c r="F164" s="4">
-        <v>2.7126308300000002</v>
+        <v>1.0850523320000001</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.3">
@@ -3782,7 +3782,7 @@
         <v>13</v>
       </c>
       <c r="F165" s="4">
-        <v>-0.7053836</v>
+        <v>-0.28215344000000003</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.3">
@@ -3802,7 +3802,7 @@
         <v>26</v>
       </c>
       <c r="F166" s="4">
-        <v>46.6570356</v>
+        <v>18.662814239999999</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.3">
@@ -3842,7 +3842,7 @@
         <v>14</v>
       </c>
       <c r="F168" s="4">
-        <v>76.320735979999995</v>
+        <v>30.528294391999999</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.3">
@@ -3862,7 +3862,7 @@
         <v>11</v>
       </c>
       <c r="F169" s="4">
-        <v>7.8561905699999999</v>
+        <v>3.142476228</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.3">
@@ -3882,7 +3882,7 @@
         <v>15</v>
       </c>
       <c r="F170" s="4">
-        <v>0.34523764000000001</v>
+        <v>0.13809505600000002</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.3">
@@ -3942,7 +3942,7 @@
         <v>21</v>
       </c>
       <c r="F173" s="4">
-        <v>1.2802276800000001</v>
+        <v>0.51209107200000004</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.3">
@@ -3982,7 +3982,7 @@
         <v>18</v>
       </c>
       <c r="F175" s="4">
-        <v>77.104920469999996</v>
+        <v>30.841968187999999</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.3">
@@ -4002,7 +4002,7 @@
         <v>14</v>
       </c>
       <c r="F176" s="4">
-        <v>76.056847790000006</v>
+        <v>30.422739116000002</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.3">
@@ -4022,7 +4022,7 @@
         <v>15</v>
       </c>
       <c r="F177" s="4">
-        <v>0.57847607999999995</v>
+        <v>0.23139043199999998</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.3">
@@ -4042,7 +4042,7 @@
         <v>23</v>
       </c>
       <c r="F178" s="4">
-        <v>38.592163200000002</v>
+        <v>15.436865280000001</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.3">
@@ -4102,7 +4102,7 @@
         <v>19</v>
       </c>
       <c r="F181" s="4">
-        <v>-0.56533825000000004</v>
+        <v>-0.22613530000000004</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.3">
@@ -4122,7 +4122,7 @@
         <v>18</v>
       </c>
       <c r="F182" s="4">
-        <v>297.62432023999997</v>
+        <v>119.049728096</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.3">
@@ -4142,7 +4142,7 @@
         <v>15</v>
       </c>
       <c r="F183" s="4">
-        <v>2.4812405800000001</v>
+        <v>0.99249623200000014</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.3">
@@ -4162,7 +4162,7 @@
         <v>23</v>
       </c>
       <c r="F184" s="4">
-        <v>16.84011602</v>
+        <v>6.736046408</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.3">
@@ -4182,7 +4182,7 @@
         <v>18</v>
       </c>
       <c r="F185" s="4">
-        <v>257.56020801</v>
+        <v>103.02408320400001</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.3">
@@ -4202,7 +4202,7 @@
         <v>13</v>
       </c>
       <c r="F186" s="4">
-        <v>-0.62105836000000003</v>
+        <v>-0.24842334400000002</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.3">
@@ -4222,7 +4222,7 @@
         <v>26</v>
       </c>
       <c r="F187" s="4">
-        <v>66.447698209999999</v>
+        <v>26.579079284000002</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.3">
@@ -4282,7 +4282,7 @@
         <v>21</v>
       </c>
       <c r="F190" s="4">
-        <v>1.5882033900000001</v>
+        <v>0.63528135600000013</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.3">
@@ -4302,7 +4302,7 @@
         <v>11</v>
       </c>
       <c r="F191" s="4">
-        <v>16.30108676</v>
+        <v>6.5204347040000004</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.3">
@@ -4322,7 +4322,7 @@
         <v>13</v>
       </c>
       <c r="F192" s="4">
-        <v>-0.57829227999999999</v>
+        <v>-0.23131691200000001</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.3">
@@ -4342,7 +4342,7 @@
         <v>23</v>
       </c>
       <c r="F193" s="4">
-        <v>16.14217902</v>
+        <v>6.4568716080000002</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.3">
@@ -4362,7 +4362,7 @@
         <v>19</v>
       </c>
       <c r="F194" s="4">
-        <v>-2.1082960900000001</v>
+        <v>-0.84331843600000012</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.3">
@@ -4382,7 +4382,7 @@
         <v>23</v>
       </c>
       <c r="F195" s="4">
-        <v>16.036121139999999</v>
+        <v>6.4144484559999997</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.3">
@@ -4402,7 +4402,7 @@
         <v>15</v>
       </c>
       <c r="F196" s="4">
-        <v>0.6899786</v>
+        <v>0.27599144000000003</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.3">
@@ -4422,7 +4422,7 @@
         <v>21</v>
       </c>
       <c r="F197" s="4">
-        <v>8.5102837499999993</v>
+        <v>3.4041134999999998</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.3">
@@ -4442,7 +4442,7 @@
         <v>14</v>
       </c>
       <c r="F198" s="4">
-        <v>72.966564059999996</v>
+        <v>29.186625624000001</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.3">
@@ -4462,7 +4462,7 @@
         <v>15</v>
       </c>
       <c r="F199" s="4">
-        <v>0.57571437999999997</v>
+        <v>0.23028575200000001</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.3">
@@ -4482,7 +4482,7 @@
         <v>15</v>
       </c>
       <c r="F200" s="4">
-        <v>0.63477377999999995</v>
+        <v>0.253909512</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.3">
@@ -4502,7 +4502,7 @@
         <v>15</v>
       </c>
       <c r="F201" s="4">
-        <v>0.60079212000000004</v>
+        <v>0.24031684800000003</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.3">
@@ -4522,7 +4522,7 @@
         <v>21</v>
       </c>
       <c r="F202" s="4">
-        <v>1.2902670700000001</v>
+        <v>0.51610682800000007</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.3">
@@ -4542,7 +4542,7 @@
         <v>11</v>
       </c>
       <c r="F203" s="4">
-        <v>17.354889709999998</v>
+        <v>6.9419558839999995</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.3">
@@ -4562,7 +4562,7 @@
         <v>27</v>
       </c>
       <c r="F204" s="4">
-        <v>-5.4521479999999997E-2</v>
+        <v>-2.1808592000000002E-2</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.3">
@@ -4582,7 +4582,7 @@
         <v>21</v>
       </c>
       <c r="F205" s="4">
-        <v>9.5080412800000005</v>
+        <v>3.8032165120000005</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.3">
@@ -4602,7 +4602,7 @@
         <v>13</v>
       </c>
       <c r="F206" s="4">
-        <v>-0.66361133999999999</v>
+        <v>-0.26544453600000001</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.3">
@@ -4642,7 +4642,7 @@
         <v>23</v>
       </c>
       <c r="F208" s="4">
-        <v>35.524039340000002</v>
+        <v>14.209615736000002</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.3">
@@ -4682,7 +4682,7 @@
         <v>23</v>
       </c>
       <c r="F210" s="4">
-        <v>8.7297192700000004</v>
+        <v>3.4918877080000001</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.3">
@@ -4722,7 +4722,7 @@
         <v>14</v>
       </c>
       <c r="F212" s="4">
-        <v>61.854826389999999</v>
+        <v>24.741930556</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.3">
@@ -4742,7 +4742,7 @@
         <v>8</v>
       </c>
       <c r="F213" s="4">
-        <v>46.094537080000002</v>
+        <v>18.437814832000001</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.3">
@@ -4802,7 +4802,7 @@
         <v>15</v>
       </c>
       <c r="F216" s="4">
-        <v>2.9049380500000002</v>
+        <v>1.1619752200000002</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.3">
@@ -4822,7 +4822,7 @@
         <v>11</v>
       </c>
       <c r="F217" s="4">
-        <v>16.572111159999999</v>
+        <v>6.6288444640000002</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.3">
@@ -4842,7 +4842,7 @@
         <v>13</v>
       </c>
       <c r="F218" s="4">
-        <v>-0.11261268000000001</v>
+        <v>-4.5045072000000005E-2</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.3">
@@ -4862,7 +4862,7 @@
         <v>24</v>
       </c>
       <c r="F219" s="4">
-        <v>31.561263180000001</v>
+        <v>12.624505272</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.3">
@@ -4902,7 +4902,7 @@
         <v>15</v>
       </c>
       <c r="F221" s="4">
-        <v>0.56427713000000002</v>
+        <v>0.22571085200000002</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.3">
@@ -4922,7 +4922,7 @@
         <v>8</v>
       </c>
       <c r="F222" s="4">
-        <v>54.421120909999999</v>
+        <v>21.768448364000001</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.3">
@@ -4942,7 +4942,7 @@
         <v>8</v>
       </c>
       <c r="F223" s="4">
-        <v>56.615463120000001</v>
+        <v>22.646185248000002</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.3">
@@ -4962,7 +4962,7 @@
         <v>21</v>
       </c>
       <c r="F224" s="4">
-        <v>2.1031473799999998</v>
+        <v>0.841258952</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.3">
@@ -5002,7 +5002,7 @@
         <v>15</v>
       </c>
       <c r="F226" s="4">
-        <v>0.56480061000000004</v>
+        <v>0.22592024400000002</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.3">
@@ -5022,7 +5022,7 @@
         <v>23</v>
       </c>
       <c r="F227" s="4">
-        <v>15.381097069999999</v>
+        <v>6.1524388280000002</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.3">
@@ -5042,7 +5042,7 @@
         <v>21</v>
       </c>
       <c r="F228" s="4">
-        <v>9.4116454699999998</v>
+        <v>3.7646581880000003</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.3">
@@ -5062,7 +5062,7 @@
         <v>23</v>
       </c>
       <c r="F229" s="4">
-        <v>24.108025720000001</v>
+        <v>9.6432102880000006</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.3">
@@ -5082,7 +5082,7 @@
         <v>15</v>
       </c>
       <c r="F230" s="4">
-        <v>0.70120625999999997</v>
+        <v>0.28048250400000002</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.3">
@@ -5122,7 +5122,7 @@
         <v>14</v>
       </c>
       <c r="F232" s="4">
-        <v>65.427051590000005</v>
+        <v>26.170820636000002</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.3">
@@ -5142,7 +5142,7 @@
         <v>19</v>
       </c>
       <c r="F233" s="4">
-        <v>-0.14719032000000001</v>
+        <v>-5.8876128000000007E-2</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.3">
@@ -5162,7 +5162,7 @@
         <v>21</v>
       </c>
       <c r="F234" s="4">
-        <v>1.5988385599999999</v>
+        <v>0.63953542399999996</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.3">
@@ -5182,7 +5182,7 @@
         <v>14</v>
       </c>
       <c r="F235" s="4">
-        <v>36.832995490000002</v>
+        <v>14.733198196000002</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.3">
@@ -5222,7 +5222,7 @@
         <v>14</v>
       </c>
       <c r="F237" s="4">
-        <v>36.832995490000002</v>
+        <v>14.733198196000002</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.3">
@@ -5242,7 +5242,7 @@
         <v>21</v>
       </c>
       <c r="F238" s="4">
-        <v>1.16921275</v>
+        <v>0.46768510000000002</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.3">
@@ -5262,7 +5262,7 @@
         <v>27</v>
       </c>
       <c r="F239" s="4">
-        <v>3.9696331200000001</v>
+        <v>1.5878532480000001</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.3">
@@ -5282,7 +5282,7 @@
         <v>13</v>
       </c>
       <c r="F240" s="4">
-        <v>-0.62105836000000003</v>
+        <v>-0.24842334400000002</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.3">
@@ -5302,7 +5302,7 @@
         <v>21</v>
       </c>
       <c r="F241" s="4">
-        <v>1.3759020099999999</v>
+        <v>0.55036080399999998</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.3">
@@ -5322,7 +5322,7 @@
         <v>14</v>
       </c>
       <c r="F242" s="4">
-        <v>39.681403779999997</v>
+        <v>15.872561511999999</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.3">
@@ -5342,7 +5342,7 @@
         <v>13</v>
       </c>
       <c r="F243" s="4">
-        <v>-0.62224003999999999</v>
+        <v>-0.248896016</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.3">
@@ -5362,7 +5362,7 @@
         <v>20</v>
       </c>
       <c r="F244" s="4">
-        <v>325.34912502999998</v>
+        <v>130.139650012</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.3">
@@ -5422,7 +5422,7 @@
         <v>23</v>
       </c>
       <c r="F247" s="4">
-        <v>33.589706960000001</v>
+        <v>13.435882784</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.3">
@@ -5442,7 +5442,7 @@
         <v>18</v>
       </c>
       <c r="F248" s="4">
-        <v>86.100511280000006</v>
+        <v>34.440204512000001</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.3">
@@ -5462,7 +5462,7 @@
         <v>19</v>
       </c>
       <c r="F249" s="4">
-        <v>-7.7996270000000006E-2</v>
+        <v>-3.1198508000000003E-2</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.3">
@@ -5482,7 +5482,7 @@
         <v>21</v>
       </c>
       <c r="F250" s="4">
-        <v>9.0610958799999999</v>
+        <v>3.6244383520000003</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.3">
@@ -5502,7 +5502,7 @@
         <v>15</v>
       </c>
       <c r="F251" s="4">
-        <v>2.3022242400000001</v>
+        <v>0.92088969600000015</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.3">
@@ -5522,7 +5522,7 @@
         <v>19</v>
       </c>
       <c r="F252" s="4">
-        <v>3.006323E-2</v>
+        <v>1.2025292E-2</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.3">
@@ -5542,7 +5542,7 @@
         <v>21</v>
       </c>
       <c r="F253" s="4">
-        <v>8.7690293500000003</v>
+        <v>3.5076117400000002</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.3">
@@ -5582,7 +5582,7 @@
         <v>14</v>
       </c>
       <c r="F255" s="4">
-        <v>75.306966419999995</v>
+        <v>30.122786567999999</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.3">
@@ -5602,7 +5602,7 @@
         <v>15</v>
       </c>
       <c r="F256" s="4">
-        <v>0.68916111000000002</v>
+        <v>0.27566444400000001</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.3">
@@ -5622,7 +5622,7 @@
         <v>24</v>
       </c>
       <c r="F257" s="4">
-        <v>21.85001308</v>
+        <v>8.7400052319999997</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.3">
@@ -5662,7 +5662,7 @@
         <v>13</v>
       </c>
       <c r="F259" s="4">
-        <v>-2.4243323399999999</v>
+        <v>-0.96973293599999999</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.3">
@@ -5682,7 +5682,7 @@
         <v>23</v>
       </c>
       <c r="F260" s="4">
-        <v>17.325794460000001</v>
+        <v>6.9303177840000005</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.3">
@@ -5702,7 +5702,7 @@
         <v>21</v>
       </c>
       <c r="F261" s="4">
-        <v>1.2192560299999999</v>
+        <v>0.48770241199999997</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.3">
@@ -5722,7 +5722,7 @@
         <v>13</v>
       </c>
       <c r="F262" s="4">
-        <v>-9.7571550000000007E-2</v>
+        <v>-3.9028620000000007E-2</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.3">
@@ -5742,7 +5742,7 @@
         <v>13</v>
       </c>
       <c r="F263" s="4">
-        <v>-2.1224342900000002</v>
+        <v>-0.84897371600000016</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.3">
@@ -5762,7 +5762,7 @@
         <v>14</v>
       </c>
       <c r="F264" s="4">
-        <v>40.841752990000003</v>
+        <v>16.336701196000003</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.3">
@@ -5782,7 +5782,7 @@
         <v>23</v>
       </c>
       <c r="F265" s="4">
-        <v>9.0177443299999993</v>
+        <v>3.6070977319999997</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.3">
@@ -5822,7 +5822,7 @@
         <v>18</v>
       </c>
       <c r="F267" s="4">
-        <v>254.96070205999999</v>
+        <v>101.984280824</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.3">
@@ -5842,7 +5842,7 @@
         <v>23</v>
       </c>
       <c r="F268" s="4">
-        <v>15.889064230000001</v>
+        <v>6.3556256920000003</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.3">
@@ -5862,7 +5862,7 @@
         <v>18</v>
       </c>
       <c r="F269" s="4">
-        <v>261.20393702000001</v>
+        <v>104.481574808</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.3">
@@ -5902,7 +5902,7 @@
         <v>19</v>
       </c>
       <c r="F271" s="4">
-        <v>-1.000449E-2</v>
+        <v>-4.0017960000000002E-3</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.3">
@@ -5922,7 +5922,7 @@
         <v>13</v>
       </c>
       <c r="F272" s="4">
-        <v>-2.4560068400000001</v>
+        <v>-0.98240273600000005</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.3">
@@ -5942,7 +5942,7 @@
         <v>15</v>
       </c>
       <c r="F273" s="4">
-        <v>0.63110445000000004</v>
+        <v>0.25244178</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.3">
@@ -5962,7 +5962,7 @@
         <v>14</v>
       </c>
       <c r="F274" s="4">
-        <v>77.561434059999996</v>
+        <v>31.024573623999999</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.3">
@@ -5982,7 +5982,7 @@
         <v>14</v>
       </c>
       <c r="F275" s="4">
-        <v>69.673022840000002</v>
+        <v>27.869209136000002</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.3">
@@ -6002,7 +6002,7 @@
         <v>23</v>
       </c>
       <c r="F276" s="4">
-        <v>19.435264480000001</v>
+        <v>7.7741057920000003</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.3">
@@ -6022,7 +6022,7 @@
         <v>20</v>
       </c>
       <c r="F277" s="4">
-        <v>46.186448149999997</v>
+        <v>18.474579259999999</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.3">
@@ -6082,7 +6082,7 @@
         <v>15</v>
       </c>
       <c r="F280" s="4">
-        <v>0.36129439000000002</v>
+        <v>0.14451775600000002</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.3">
@@ -6102,7 +6102,7 @@
         <v>24</v>
       </c>
       <c r="F281" s="4">
-        <v>1.91812088</v>
+        <v>0.76724835200000008</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.3">
@@ -6122,7 +6122,7 @@
         <v>27</v>
       </c>
       <c r="F282" s="4">
-        <v>13.88302747</v>
+        <v>5.553210988</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.3">
@@ -6142,7 +6142,7 @@
         <v>20</v>
       </c>
       <c r="F283" s="4">
-        <v>92.622052650000001</v>
+        <v>37.048821060000002</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.3">
@@ -6162,7 +6162,7 @@
         <v>27</v>
       </c>
       <c r="F284" s="4">
-        <v>9.9368461900000007</v>
+        <v>3.9747384760000006</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.3">
@@ -6182,7 +6182,7 @@
         <v>15</v>
       </c>
       <c r="F285" s="4">
-        <v>0.37967627999999998</v>
+        <v>0.15187051200000001</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.3">
@@ -6202,7 +6202,7 @@
         <v>19</v>
       </c>
       <c r="F286" s="4">
-        <v>-0.14603932</v>
+        <v>-5.8415728E-2</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.3">
@@ -6222,7 +6222,7 @@
         <v>13</v>
       </c>
       <c r="F287" s="4">
-        <v>-1.4347896</v>
+        <v>-0.57391584000000007</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.3">
@@ -6242,7 +6242,7 @@
         <v>23</v>
       </c>
       <c r="F288" s="4">
-        <v>32.823164269999999</v>
+        <v>13.129265708</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.3">
@@ -6262,7 +6262,7 @@
         <v>21</v>
       </c>
       <c r="F289" s="4">
-        <v>1.74715413</v>
+        <v>0.69886165200000006</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.3">
@@ -6302,7 +6302,7 @@
         <v>18</v>
       </c>
       <c r="F291" s="4">
-        <v>45.915376500000001</v>
+        <v>18.366150600000001</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.3">
@@ -6322,7 +6322,7 @@
         <v>11</v>
       </c>
       <c r="F292" s="4">
-        <v>11.57029618</v>
+        <v>4.6281184719999997</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.3">
@@ -6342,7 +6342,7 @@
         <v>24</v>
       </c>
       <c r="F293" s="4">
-        <v>17.108861009999998</v>
+        <v>6.8435444039999993</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.3">
@@ -6362,7 +6362,7 @@
         <v>14</v>
       </c>
       <c r="F294" s="4">
-        <v>55.781518560000002</v>
+        <v>22.312607424000003</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.3">
@@ -6382,7 +6382,7 @@
         <v>21</v>
       </c>
       <c r="F295" s="4">
-        <v>9.0642045200000005</v>
+        <v>3.6256818080000004</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.3">
@@ -6422,7 +6422,7 @@
         <v>15</v>
       </c>
       <c r="F297" s="4">
-        <v>0.56496698999999995</v>
+        <v>0.22598679599999999</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.3">
@@ -6442,7 +6442,7 @@
         <v>13</v>
       </c>
       <c r="F298" s="4">
-        <v>2.201204E-2</v>
+        <v>8.804816E-3</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.3">
@@ -6462,7 +6462,7 @@
         <v>13</v>
       </c>
       <c r="F299" s="4">
-        <v>-0.11261268000000001</v>
+        <v>-4.5045072000000005E-2</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.3">
@@ -6482,7 +6482,7 @@
         <v>14</v>
       </c>
       <c r="F300" s="4">
-        <v>67.528705540000004</v>
+        <v>27.011482216000005</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.3">
@@ -6502,7 +6502,7 @@
         <v>13</v>
       </c>
       <c r="F301" s="4">
-        <v>-0.65978711000000001</v>
+        <v>-0.26391484400000004</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.3">
@@ -6542,7 +6542,7 @@
         <v>18</v>
       </c>
       <c r="F303" s="4">
-        <v>45.894754429999999</v>
+        <v>18.357901772000002</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.3">
@@ -6562,7 +6562,7 @@
         <v>23</v>
       </c>
       <c r="F304" s="4">
-        <v>48.086122709999998</v>
+        <v>19.234449084000001</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.3">
@@ -6602,7 +6602,7 @@
         <v>15</v>
       </c>
       <c r="F306" s="4">
-        <v>2.47489669</v>
+        <v>0.98995867600000009</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.3">
@@ -6642,7 +6642,7 @@
         <v>8</v>
       </c>
       <c r="F308" s="4">
-        <v>40.538149689999997</v>
+        <v>16.215259876000001</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.3">
@@ -6682,7 +6682,7 @@
         <v>24</v>
       </c>
       <c r="F310" s="4">
-        <v>23.783330490000001</v>
+        <v>9.5133321960000004</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.3">
@@ -6702,7 +6702,7 @@
         <v>13</v>
       </c>
       <c r="F311" s="4">
-        <v>-0.7053836</v>
+        <v>-0.28215344000000003</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.3">
@@ -6742,7 +6742,7 @@
         <v>19</v>
       </c>
       <c r="F313" s="4">
-        <v>-9.1971479999999994E-2</v>
+        <v>-3.6788592000000002E-2</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.3">
@@ -6782,7 +6782,7 @@
         <v>13</v>
       </c>
       <c r="F315" s="4">
-        <v>0.19881726</v>
+        <v>7.9526904000000009E-2</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.3">
@@ -6802,7 +6802,7 @@
         <v>8</v>
       </c>
       <c r="F316" s="4">
-        <v>46.245563599999997</v>
+        <v>18.498225439999999</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.3">
@@ -6822,7 +6822,7 @@
         <v>27</v>
       </c>
       <c r="F317" s="4">
-        <v>4.6895568799999996</v>
+        <v>1.8758227519999999</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.3">
@@ -6842,7 +6842,7 @@
         <v>13</v>
       </c>
       <c r="F318" s="4">
-        <v>-0.62971188</v>
+        <v>-0.25188475199999999</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.3">
@@ -6862,7 +6862,7 @@
         <v>21</v>
       </c>
       <c r="F319" s="4">
-        <v>8.8623290299999997</v>
+        <v>3.5449316120000001</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.3">
@@ -6882,7 +6882,7 @@
         <v>26</v>
       </c>
       <c r="F320" s="4">
-        <v>47.101925799999997</v>
+        <v>18.840770320000001</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.3">
@@ -6902,7 +6902,7 @@
         <v>15</v>
       </c>
       <c r="F321" s="4">
-        <v>0.62154977</v>
+        <v>0.248619908</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.3">
@@ -6942,7 +6942,7 @@
         <v>8</v>
       </c>
       <c r="F323" s="4">
-        <v>89.20524838</v>
+        <v>35.682099352000002</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.3">
@@ -6962,7 +6962,7 @@
         <v>14</v>
       </c>
       <c r="F324" s="4">
-        <v>65.427051590000005</v>
+        <v>26.170820636000002</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.3">
@@ -6982,7 +6982,7 @@
         <v>23</v>
       </c>
       <c r="F325" s="4">
-        <v>37.864063680000001</v>
+        <v>15.145625472000001</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.3">
@@ -7002,7 +7002,7 @@
         <v>21</v>
       </c>
       <c r="F326" s="4">
-        <v>8.4926190399999992</v>
+        <v>3.397047616</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.3">
@@ -7022,7 +7022,7 @@
         <v>8</v>
       </c>
       <c r="F327" s="4">
-        <v>63.793874240000001</v>
+        <v>25.517549696000003</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.3">
@@ -7042,7 +7042,7 @@
         <v>23</v>
       </c>
       <c r="F328" s="4">
-        <v>16.34188881</v>
+        <v>6.5367555240000002</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.3">
@@ -7062,7 +7062,7 @@
         <v>27</v>
       </c>
       <c r="F329" s="4">
-        <v>-0.73810202999999996</v>
+        <v>-0.29524081200000002</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.3">
@@ -7082,7 +7082,7 @@
         <v>14</v>
       </c>
       <c r="F330" s="4">
-        <v>75.724074329999993</v>
+        <v>30.289629731999998</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.3">
@@ -7102,7 +7102,7 @@
         <v>27</v>
       </c>
       <c r="F331" s="4">
-        <v>2.72623091</v>
+        <v>1.0904923639999999</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.3">
@@ -7122,7 +7122,7 @@
         <v>15</v>
       </c>
       <c r="F332" s="4">
-        <v>2.6518639400000001</v>
+        <v>1.0607455760000002</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.3">
@@ -7142,7 +7142,7 @@
         <v>21</v>
       </c>
       <c r="F333" s="4">
-        <v>1.2474337499999999</v>
+        <v>0.49897349999999996</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.3">
@@ -7162,7 +7162,7 @@
         <v>26</v>
       </c>
       <c r="F334" s="4">
-        <v>52.02393481</v>
+        <v>20.809573924000002</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.3">
@@ -7182,7 +7182,7 @@
         <v>23</v>
       </c>
       <c r="F335" s="4">
-        <v>39.698646320000002</v>
+        <v>15.879458528000001</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.3">
@@ -7202,7 +7202,7 @@
         <v>23</v>
       </c>
       <c r="F336" s="4">
-        <v>16.364286280000002</v>
+        <v>6.5457145120000009</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.3">
@@ -7242,7 +7242,7 @@
         <v>27</v>
       </c>
       <c r="F338" s="4">
-        <v>23.78133528</v>
+        <v>9.5125341120000009</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.3">
@@ -7262,7 +7262,7 @@
         <v>27</v>
       </c>
       <c r="F339" s="4">
-        <v>28.85768298</v>
+        <v>11.543073192000001</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.3">
@@ -7282,7 +7282,7 @@
         <v>13</v>
       </c>
       <c r="F340" s="4">
-        <v>-2.3340410500000002</v>
+        <v>-0.93361642000000011</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.3">
@@ -7342,7 +7342,7 @@
         <v>19</v>
       </c>
       <c r="F343" s="4">
-        <v>-3.09706E-3</v>
+        <v>-1.2388240000000001E-3</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.3">
@@ -7362,7 +7362,7 @@
         <v>20</v>
       </c>
       <c r="F344" s="4">
-        <v>33.5092347</v>
+        <v>13.403693880000001</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.3">
@@ -7382,7 +7382,7 @@
         <v>23</v>
       </c>
       <c r="F345" s="4">
-        <v>15.528715800000001</v>
+        <v>6.2114863200000006</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.3">
@@ -7402,7 +7402,7 @@
         <v>13</v>
       </c>
       <c r="F346" s="4">
-        <v>-2.2464837200000001</v>
+        <v>-0.89859348800000005</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.3">
@@ -7422,7 +7422,7 @@
         <v>13</v>
       </c>
       <c r="F347" s="4">
-        <v>-0.62971188</v>
+        <v>-0.25188475199999999</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.3">
@@ -7462,7 +7462,7 @@
         <v>18</v>
       </c>
       <c r="F349" s="4">
-        <v>56.375836219999997</v>
+        <v>22.550334488000001</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.3">
@@ -7482,7 +7482,7 @@
         <v>24</v>
       </c>
       <c r="F350" s="4">
-        <v>0.15209981</v>
+        <v>6.0839924000000004E-2</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.3">
@@ -7502,7 +7502,7 @@
         <v>19</v>
       </c>
       <c r="F351" s="4">
-        <v>-1.213698E-2</v>
+        <v>-4.8547920000000001E-3</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.3">
@@ -7522,7 +7522,7 @@
         <v>20</v>
       </c>
       <c r="F352" s="4">
-        <v>96.01270667</v>
+        <v>38.405082668000006</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.3">
@@ -7542,7 +7542,7 @@
         <v>24</v>
       </c>
       <c r="F353" s="4">
-        <v>27.025510839999999</v>
+        <v>10.810204336</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.3">
@@ -7562,7 +7562,7 @@
         <v>27</v>
       </c>
       <c r="F354" s="4">
-        <v>2.3392865600000001</v>
+        <v>0.93571462400000005</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.3">
@@ -7582,7 +7582,7 @@
         <v>24</v>
       </c>
       <c r="F355" s="4">
-        <v>-38.24192429</v>
+        <v>-15.296769716</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.3">
@@ -7602,7 +7602,7 @@
         <v>13</v>
       </c>
       <c r="F356" s="4">
-        <v>-2.0879523299999998</v>
+        <v>-0.83518093199999999</v>
       </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.3">
@@ -7622,7 +7622,7 @@
         <v>13</v>
       </c>
       <c r="F357" s="4">
-        <v>-0.58220373000000003</v>
+        <v>-0.23288149200000002</v>
       </c>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.3">
@@ -7682,7 +7682,7 @@
         <v>8</v>
       </c>
       <c r="F360" s="4">
-        <v>46.713552530000001</v>
+        <v>18.685421012000003</v>
       </c>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.3">
@@ -7702,7 +7702,7 @@
         <v>21</v>
       </c>
       <c r="F361" s="4">
-        <v>1.11141264</v>
+        <v>0.44456505600000001</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.3">
@@ -7742,7 +7742,7 @@
         <v>14</v>
       </c>
       <c r="F363" s="4">
-        <v>37.343307619999997</v>
+        <v>14.937323048</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.3">
@@ -7762,7 +7762,7 @@
         <v>8</v>
       </c>
       <c r="F364" s="4">
-        <v>81.805005280000003</v>
+        <v>32.722002112000006</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.3">
@@ -7782,7 +7782,7 @@
         <v>15</v>
       </c>
       <c r="F365" s="4">
-        <v>3.1804176200000001</v>
+        <v>1.272167048</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.3">
@@ -7802,7 +7802,7 @@
         <v>21</v>
       </c>
       <c r="F366" s="4">
-        <v>1.39229465</v>
+        <v>0.55691785999999999</v>
       </c>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.3">
@@ -7842,7 +7842,7 @@
         <v>23</v>
       </c>
       <c r="F368" s="4">
-        <v>15.96247035</v>
+        <v>6.3849881400000008</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.3">
@@ -7862,7 +7862,7 @@
         <v>21</v>
       </c>
       <c r="F369" s="4">
-        <v>1.62687742</v>
+        <v>0.6507509680000001</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.3">
@@ -7882,7 +7882,7 @@
         <v>21</v>
       </c>
       <c r="F370" s="4">
-        <v>1.84242035</v>
+        <v>0.7369681400000001</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.3">
@@ -7902,7 +7902,7 @@
         <v>15</v>
       </c>
       <c r="F371" s="4">
-        <v>0.59092286000000005</v>
+        <v>0.23636914400000003</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.3">
@@ -7922,7 +7922,7 @@
         <v>15</v>
       </c>
       <c r="F372" s="4">
-        <v>2.2782396899999999</v>
+        <v>0.91129587600000006</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.3">
@@ -7942,7 +7942,7 @@
         <v>23</v>
       </c>
       <c r="F373" s="4">
-        <v>16.830632749999999</v>
+        <v>6.7322531000000003</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.3">
@@ -7982,7 +7982,7 @@
         <v>15</v>
       </c>
       <c r="F375" s="4">
-        <v>2.37935549</v>
+        <v>0.9517421960000001</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.3">
@@ -8022,7 +8022,7 @@
         <v>20</v>
       </c>
       <c r="F377" s="4">
-        <v>43.476663500000001</v>
+        <v>17.3906654</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.3">
@@ -8042,7 +8042,7 @@
         <v>23</v>
       </c>
       <c r="F378" s="4">
-        <v>11.29717926</v>
+        <v>4.5188717040000004</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.3">
@@ -8102,7 +8102,7 @@
         <v>27</v>
       </c>
       <c r="F381" s="4">
-        <v>4.4407757099999996</v>
+        <v>1.776310284</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.3">
@@ -8122,7 +8122,7 @@
         <v>8</v>
       </c>
       <c r="F382" s="4">
-        <v>49.335943780000001</v>
+        <v>19.734377512000002</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.3">
@@ -8162,7 +8162,7 @@
         <v>20</v>
       </c>
       <c r="F384" s="4">
-        <v>302.15130826000001</v>
+        <v>120.86052330400001</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.3">
@@ -8182,7 +8182,7 @@
         <v>14</v>
       </c>
       <c r="F385" s="4">
-        <v>60.690788869999999</v>
+        <v>24.276315547999999</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.3">
@@ -8222,7 +8222,7 @@
         <v>14</v>
       </c>
       <c r="F387" s="4">
-        <v>55.781518560000002</v>
+        <v>22.312607424000003</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.3">
@@ -8242,7 +8242,7 @@
         <v>15</v>
       </c>
       <c r="F388" s="4">
-        <v>0.71299356000000003</v>
+        <v>0.28519742400000003</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.3">
@@ -8262,7 +8262,7 @@
         <v>13</v>
       </c>
       <c r="F389" s="4">
-        <v>-1.3672655899999999</v>
+        <v>-0.54690623599999999</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.3">
@@ -8282,7 +8282,7 @@
         <v>15</v>
       </c>
       <c r="F390" s="4">
-        <v>0.43565946</v>
+        <v>0.174263784</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.3">
@@ -8302,7 +8302,7 @@
         <v>19</v>
       </c>
       <c r="F391" s="4">
-        <v>6.162165E-2</v>
+        <v>2.4648660000000003E-2</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.3">
@@ -8322,7 +8322,7 @@
         <v>21</v>
       </c>
       <c r="F392" s="4">
-        <v>8.2737810100000004</v>
+        <v>3.3095124040000004</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.3">
@@ -8342,7 +8342,7 @@
         <v>21</v>
       </c>
       <c r="F393" s="4">
-        <v>1.6415950699999999</v>
+        <v>0.65663802800000004</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.3">
@@ -8382,7 +8382,7 @@
         <v>21</v>
       </c>
       <c r="F395" s="4">
-        <v>1.4025806199999999</v>
+        <v>0.56103224799999996</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.3">
@@ -8402,7 +8402,7 @@
         <v>8</v>
       </c>
       <c r="F396" s="4">
-        <v>87.231849010000005</v>
+        <v>34.892739604000006</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.3">
@@ -8422,7 +8422,7 @@
         <v>13</v>
       </c>
       <c r="F397" s="4">
-        <v>-2.5671765</v>
+        <v>-1.0268706000000001</v>
       </c>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.3">
@@ -8442,7 +8442,7 @@
         <v>27</v>
       </c>
       <c r="F398" s="4">
-        <v>0.80112927</v>
+        <v>0.320451708</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.3">
@@ -8462,7 +8462,7 @@
         <v>27</v>
       </c>
       <c r="F399" s="4">
-        <v>0.12927108000000001</v>
+        <v>5.1708432000000006E-2</v>
       </c>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.3">
@@ -8482,7 +8482,7 @@
         <v>13</v>
       </c>
       <c r="F400" s="4">
-        <v>-0.73542428000000004</v>
+        <v>-0.29416971200000003</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.3">
@@ -8522,7 +8522,7 @@
         <v>21</v>
       </c>
       <c r="F402" s="4">
-        <v>1.5580690500000001</v>
+        <v>0.62322762000000009</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.3">
@@ -8542,7 +8542,7 @@
         <v>18</v>
       </c>
       <c r="F403" s="4">
-        <v>47.49501532</v>
+        <v>18.998006128</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.3">
@@ -8582,7 +8582,7 @@
         <v>24</v>
       </c>
       <c r="F405" s="4">
-        <v>2.8770103800000002</v>
+        <v>1.1508041520000001</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.3">
@@ -8602,7 +8602,7 @@
         <v>24</v>
       </c>
       <c r="F406" s="4">
-        <v>14.67377372</v>
+        <v>5.8695094880000003</v>
       </c>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.3">
@@ -8622,7 +8622,7 @@
         <v>20</v>
       </c>
       <c r="F407" s="4">
-        <v>89.091197910000005</v>
+        <v>35.636479164000001</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.3">
@@ -8662,7 +8662,7 @@
         <v>11</v>
       </c>
       <c r="F409" s="4">
-        <v>11.03338589</v>
+        <v>4.4133543560000001</v>
       </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.3">
@@ -8722,7 +8722,7 @@
         <v>13</v>
       </c>
       <c r="F412" s="4">
-        <v>0.30638693</v>
+        <v>0.12255477200000001</v>
       </c>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.3">
@@ -8742,7 +8742,7 @@
         <v>15</v>
       </c>
       <c r="F413" s="4">
-        <v>0.36735040000000002</v>
+        <v>0.14694016000000001</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.3">
@@ -8762,7 +8762,7 @@
         <v>15</v>
       </c>
       <c r="F414" s="4">
-        <v>0.39113234000000002</v>
+        <v>0.15645293600000001</v>
       </c>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.3">
@@ -8782,7 +8782,7 @@
         <v>8</v>
       </c>
       <c r="F415" s="4">
-        <v>45.123409950000003</v>
+        <v>18.049363980000003</v>
       </c>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.3">
@@ -8822,7 +8822,7 @@
         <v>23</v>
       </c>
       <c r="F417" s="4">
-        <v>17.4058326</v>
+        <v>6.9623330400000008</v>
       </c>
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.3">
@@ -8842,7 +8842,7 @@
         <v>19</v>
       </c>
       <c r="F418" s="4">
-        <v>-9.6191319999999997E-2</v>
+        <v>-3.8476528000000003E-2</v>
       </c>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.3">
@@ -8862,7 +8862,7 @@
         <v>11</v>
       </c>
       <c r="F419" s="4">
-        <v>16.20845027</v>
+        <v>6.4833801080000004</v>
       </c>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.3">
@@ -8882,7 +8882,7 @@
         <v>15</v>
       </c>
       <c r="F420" s="4">
-        <v>0.59636520000000004</v>
+        <v>0.23854608000000002</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.3">
@@ -8902,7 +8902,7 @@
         <v>15</v>
       </c>
       <c r="F421" s="4">
-        <v>2.6717552100000002</v>
+        <v>1.0687020840000001</v>
       </c>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.3">
@@ -8922,7 +8922,7 @@
         <v>13</v>
       </c>
       <c r="F422" s="4">
-        <v>-0.74697409999999997</v>
+        <v>-0.29878964000000002</v>
       </c>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.3">
@@ -8942,7 +8942,7 @@
         <v>21</v>
       </c>
       <c r="F423" s="4">
-        <v>1.06929546</v>
+        <v>0.427718184</v>
       </c>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.3">
@@ -8962,7 +8962,7 @@
         <v>19</v>
       </c>
       <c r="F424" s="4">
-        <v>5.5924540000000002E-2</v>
+        <v>2.2369816000000001E-2</v>
       </c>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.3">
@@ -8982,7 +8982,7 @@
         <v>13</v>
       </c>
       <c r="F425" s="4">
-        <v>-1.3672655899999999</v>
+        <v>-0.54690623599999999</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.3">
@@ -9002,7 +9002,7 @@
         <v>21</v>
       </c>
       <c r="F426" s="4">
-        <v>11.01834517</v>
+        <v>4.4073380680000005</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.3">
@@ -9022,7 +9022,7 @@
         <v>11</v>
       </c>
       <c r="F427" s="4">
-        <v>17.762823749999999</v>
+        <v>7.1051295000000003</v>
       </c>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.3">
@@ -9042,7 +9042,7 @@
         <v>19</v>
       </c>
       <c r="F428" s="4">
-        <v>-0.10459441</v>
+        <v>-4.1837764E-2</v>
       </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.3">
@@ -9062,7 +9062,7 @@
         <v>11</v>
       </c>
       <c r="F429" s="4">
-        <v>16.491812939999999</v>
+        <v>6.5967251759999996</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.3">
@@ -9082,7 +9082,7 @@
         <v>19</v>
       </c>
       <c r="F430" s="4">
-        <v>-0.94990945999999998</v>
+        <v>-0.37996378400000003</v>
       </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.3">
@@ -9102,7 +9102,7 @@
         <v>27</v>
       </c>
       <c r="F431" s="4">
-        <v>5.1227195500000002</v>
+        <v>2.04908782</v>
       </c>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.3">
@@ -9142,7 +9142,7 @@
         <v>13</v>
       </c>
       <c r="F433" s="4">
-        <v>-0.57829227999999999</v>
+        <v>-0.23131691200000001</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.3">
@@ -9162,7 +9162,7 @@
         <v>13</v>
       </c>
       <c r="F434" s="4">
-        <v>-0.62725737999999998</v>
+        <v>-0.25090295200000001</v>
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.3">
@@ -9182,7 +9182,7 @@
         <v>14</v>
       </c>
       <c r="F435" s="4">
-        <v>59.423227320000002</v>
+        <v>23.769290928000004</v>
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.3">
@@ -9242,7 +9242,7 @@
         <v>8</v>
       </c>
       <c r="F438" s="4">
-        <v>85.748021219999998</v>
+        <v>34.299208487999998</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.3">
@@ -9262,7 +9262,7 @@
         <v>18</v>
       </c>
       <c r="F439" s="4">
-        <v>264.23972257999998</v>
+        <v>105.695889032</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.3">
@@ -9322,7 +9322,7 @@
         <v>21</v>
       </c>
       <c r="F442" s="4">
-        <v>8.83460453</v>
+        <v>3.5338418120000004</v>
       </c>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.3">
@@ -9342,7 +9342,7 @@
         <v>8</v>
       </c>
       <c r="F443" s="4">
-        <v>34.532493510000002</v>
+        <v>13.812997404000001</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.3">
@@ -9362,7 +9362,7 @@
         <v>27</v>
       </c>
       <c r="F444" s="4">
-        <v>13.855953510000001</v>
+        <v>5.5423814040000003</v>
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.3">
@@ -9382,7 +9382,7 @@
         <v>18</v>
       </c>
       <c r="F445" s="4">
-        <v>274.08511428000003</v>
+        <v>109.63404571200002</v>
       </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.3">
@@ -9402,7 +9402,7 @@
         <v>24</v>
       </c>
       <c r="F446" s="4">
-        <v>-26.37015942</v>
+        <v>-10.548063768</v>
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.3">
@@ -9562,7 +9562,7 @@
         <v>19</v>
       </c>
       <c r="F454" s="4">
-        <v>-0.13683878999999999</v>
+        <v>-5.4735515999999998E-2</v>
       </c>
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.3">
@@ -9582,7 +9582,7 @@
         <v>15</v>
       </c>
       <c r="F455" s="4">
-        <v>0.70276402999999998</v>
+        <v>0.281105612</v>
       </c>
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.3">
@@ -9622,7 +9622,7 @@
         <v>18</v>
       </c>
       <c r="F457" s="4">
-        <v>46.205273550000001</v>
+        <v>18.48210942</v>
       </c>
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.3">
@@ -9642,7 +9642,7 @@
         <v>14</v>
       </c>
       <c r="F458" s="4">
-        <v>61.854826389999999</v>
+        <v>24.741930556</v>
       </c>
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.3">
@@ -9662,7 +9662,7 @@
         <v>24</v>
       </c>
       <c r="F459" s="4">
-        <v>12.96326867</v>
+        <v>5.1853074680000004</v>
       </c>
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.3">
@@ -9762,7 +9762,7 @@
         <v>14</v>
       </c>
       <c r="F464" s="4">
-        <v>75.306966419999995</v>
+        <v>30.122786567999999</v>
       </c>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.3">
@@ -9782,7 +9782,7 @@
         <v>26</v>
       </c>
       <c r="F465" s="4">
-        <v>53.08691228</v>
+        <v>21.234764912000003</v>
       </c>
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.3">
@@ -9802,7 +9802,7 @@
         <v>11</v>
       </c>
       <c r="F466" s="4">
-        <v>16.838663369999999</v>
+        <v>6.735465348</v>
       </c>
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.3">
@@ -9842,7 +9842,7 @@
         <v>18</v>
       </c>
       <c r="F468" s="4">
-        <v>45.863392670000003</v>
+        <v>18.345357068000002</v>
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.3">
@@ -9862,7 +9862,7 @@
         <v>27</v>
       </c>
       <c r="F469" s="4">
-        <v>4.2870450599999996</v>
+        <v>1.7148180239999999</v>
       </c>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.3">
@@ -9882,7 +9882,7 @@
         <v>27</v>
       </c>
       <c r="F470" s="4">
-        <v>-1.47732971</v>
+        <v>-0.59093188400000007</v>
       </c>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.3">
@@ -9902,7 +9902,7 @@
         <v>14</v>
       </c>
       <c r="F471" s="4">
-        <v>37.829045690000001</v>
+        <v>15.131618276000001</v>
       </c>
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.3">
@@ -9922,7 +9922,7 @@
         <v>14</v>
       </c>
       <c r="F472" s="4">
-        <v>78.265309009999996</v>
+        <v>31.306123604</v>
       </c>
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.3">
@@ -9942,7 +9942,7 @@
         <v>18</v>
       </c>
       <c r="F473" s="4">
-        <v>86.099605089999997</v>
+        <v>34.439842036000002</v>
       </c>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.3">
@@ -9962,7 +9962,7 @@
         <v>8</v>
       </c>
       <c r="F474" s="4">
-        <v>44.345623230000001</v>
+        <v>17.738249292000003</v>
       </c>
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.3">
@@ -9982,7 +9982,7 @@
         <v>15</v>
       </c>
       <c r="F475" s="4">
-        <v>0.69943719999999998</v>
+        <v>0.27977488</v>
       </c>
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.3">
@@ -10002,7 +10002,7 @@
         <v>15</v>
       </c>
       <c r="F476" s="4">
-        <v>2.9805198399999999</v>
+        <v>1.192207936</v>
       </c>
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.3">
@@ -10022,7 +10022,7 @@
         <v>18</v>
       </c>
       <c r="F477" s="4">
-        <v>78.817414220000003</v>
+        <v>31.526965688000004</v>
       </c>
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.3">
@@ -10042,7 +10042,7 @@
         <v>14</v>
       </c>
       <c r="F478" s="4">
-        <v>39.681403779999997</v>
+        <v>15.872561511999999</v>
       </c>
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.3">
@@ -10062,7 +10062,7 @@
         <v>20</v>
       </c>
       <c r="F479" s="4">
-        <v>287.84566332999998</v>
+        <v>115.138265332</v>
       </c>
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.3">
@@ -10082,7 +10082,7 @@
         <v>23</v>
       </c>
       <c r="F480" s="4">
-        <v>36.760373700000002</v>
+        <v>14.704149480000002</v>
       </c>
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.3">
@@ -10102,7 +10102,7 @@
         <v>19</v>
       </c>
       <c r="F481" s="4">
-        <v>-4.8207380000000001E-2</v>
+        <v>-1.9282952000000003E-2</v>
       </c>
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.3">
@@ -10142,7 +10142,7 @@
         <v>13</v>
       </c>
       <c r="F483" s="4">
-        <v>-2.1191994200000002</v>
+        <v>-0.84767976800000011</v>
       </c>
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.3">
@@ -10162,7 +10162,7 @@
         <v>18</v>
       </c>
       <c r="F484" s="4">
-        <v>54.370264110000001</v>
+        <v>21.748105644000002</v>
       </c>
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.3">
@@ -10182,7 +10182,7 @@
         <v>15</v>
       </c>
       <c r="F485" s="4">
-        <v>0.55680726999999997</v>
+        <v>0.222722908</v>
       </c>
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.3">
@@ -10202,7 +10202,7 @@
         <v>24</v>
       </c>
       <c r="F486" s="4">
-        <v>11.97312878</v>
+        <v>4.7892515119999999</v>
       </c>
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.3">
@@ -10222,7 +10222,7 @@
         <v>13</v>
       </c>
       <c r="F487" s="4">
-        <v>-0.66312565000000001</v>
+        <v>-0.26525026000000002</v>
       </c>
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.3">
@@ -10262,7 +10262,7 @@
         <v>20</v>
       </c>
       <c r="F489" s="4">
-        <v>35.242097729999998</v>
+        <v>14.096839092</v>
       </c>
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.3">
@@ -10282,7 +10282,7 @@
         <v>19</v>
       </c>
       <c r="F490" s="4">
-        <v>-0.12640756</v>
+        <v>-5.0563024000000005E-2</v>
       </c>
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.3">
@@ -10302,7 +10302,7 @@
         <v>23</v>
       </c>
       <c r="F491" s="4">
-        <v>9.0299226299999997</v>
+        <v>3.6119690520000001</v>
       </c>
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.3">
@@ -10322,7 +10322,7 @@
         <v>24</v>
       </c>
       <c r="F492" s="4">
-        <v>-11.31587143</v>
+        <v>-4.5263485719999998</v>
       </c>
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.3">
@@ -10342,7 +10342,7 @@
         <v>19</v>
       </c>
       <c r="F493" s="4">
-        <v>0.10637149</v>
+        <v>4.2548596000000001E-2</v>
       </c>
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.3">
@@ -10382,7 +10382,7 @@
         <v>27</v>
       </c>
       <c r="F495" s="4">
-        <v>1.2793893300000001</v>
+        <v>0.51175573200000002</v>
       </c>
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.3">
@@ -10402,7 +10402,7 @@
         <v>24</v>
       </c>
       <c r="F496" s="4">
-        <v>183.71075431</v>
+        <v>73.484301724000005</v>
       </c>
     </row>
     <row r="497" spans="1:6" x14ac:dyDescent="0.3">
@@ -10422,7 +10422,7 @@
         <v>21</v>
       </c>
       <c r="F497" s="4">
-        <v>1.3950322799999999</v>
+        <v>0.55801291200000003</v>
       </c>
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.3">
@@ -10442,7 +10442,7 @@
         <v>15</v>
       </c>
       <c r="F498" s="4">
-        <v>0.68607996000000004</v>
+        <v>0.27443198400000002</v>
       </c>
     </row>
     <row r="499" spans="1:6" x14ac:dyDescent="0.3">
@@ -10482,7 +10482,7 @@
         <v>11</v>
       </c>
       <c r="F500" s="4">
-        <v>18.233265719999999</v>
+        <v>7.2933062880000001</v>
       </c>
     </row>
     <row r="501" spans="1:6" x14ac:dyDescent="0.3">
@@ -10502,7 +10502,7 @@
         <v>20</v>
       </c>
       <c r="F501" s="4">
-        <v>258.00398080999997</v>
+        <v>103.20159232399999</v>
       </c>
     </row>
     <row r="502" spans="1:6" x14ac:dyDescent="0.3">
@@ -10522,7 +10522,7 @@
         <v>20</v>
       </c>
       <c r="F502" s="4">
-        <v>366.69089451000002</v>
+        <v>146.67635780400002</v>
       </c>
     </row>
     <row r="503" spans="1:6" x14ac:dyDescent="0.3">
@@ -10542,7 +10542,7 @@
         <v>21</v>
       </c>
       <c r="F503" s="4">
-        <v>7.9155541899999999</v>
+        <v>3.1662216760000002</v>
       </c>
     </row>
     <row r="504" spans="1:6" x14ac:dyDescent="0.3">
@@ -10562,7 +10562,7 @@
         <v>27</v>
       </c>
       <c r="F504" s="4">
-        <v>0.36196639000000003</v>
+        <v>0.14478655600000001</v>
       </c>
     </row>
     <row r="505" spans="1:6" x14ac:dyDescent="0.3">
@@ -10582,7 +10582,7 @@
         <v>21</v>
       </c>
       <c r="F505" s="4">
-        <v>1.1561972199999999</v>
+        <v>0.46247888799999998</v>
       </c>
     </row>
     <row r="506" spans="1:6" x14ac:dyDescent="0.3">
@@ -10622,7 +10622,7 @@
         <v>20</v>
       </c>
       <c r="F507" s="4">
-        <v>82.731712250000001</v>
+        <v>33.092684900000002</v>
       </c>
     </row>
     <row r="508" spans="1:6" x14ac:dyDescent="0.3">
@@ -10642,7 +10642,7 @@
         <v>21</v>
       </c>
       <c r="F508" s="4">
-        <v>1.42505021</v>
+        <v>0.57002008400000004</v>
       </c>
     </row>
     <row r="509" spans="1:6" x14ac:dyDescent="0.3">
@@ -10662,7 +10662,7 @@
         <v>24</v>
       </c>
       <c r="F509" s="4">
-        <v>-16.580567810000002</v>
+        <v>-6.6322271240000008</v>
       </c>
     </row>
     <row r="510" spans="1:6" x14ac:dyDescent="0.3">
@@ -10682,7 +10682,7 @@
         <v>8</v>
       </c>
       <c r="F510" s="4">
-        <v>83.400156080000002</v>
+        <v>33.360062431999999</v>
       </c>
     </row>
     <row r="511" spans="1:6" x14ac:dyDescent="0.3">
@@ -10702,7 +10702,7 @@
         <v>15</v>
       </c>
       <c r="F511" s="4">
-        <v>2.4806938000000001</v>
+        <v>0.99227752000000002</v>
       </c>
     </row>
     <row r="512" spans="1:6" x14ac:dyDescent="0.3">
@@ -10722,7 +10722,7 @@
         <v>14</v>
       </c>
       <c r="F512" s="4">
-        <v>40.841752990000003</v>
+        <v>16.336701196000003</v>
       </c>
     </row>
     <row r="513" spans="1:6" x14ac:dyDescent="0.3">
@@ -10742,7 +10742,7 @@
         <v>24</v>
       </c>
       <c r="F513" s="4">
-        <v>-11.77232899</v>
+        <v>-4.7089315960000002</v>
       </c>
     </row>
     <row r="514" spans="1:6" x14ac:dyDescent="0.3">
@@ -10782,7 +10782,7 @@
         <v>20</v>
       </c>
       <c r="F515" s="4">
-        <v>78.114172539999998</v>
+        <v>31.245669016000001</v>
       </c>
     </row>
     <row r="516" spans="1:6" x14ac:dyDescent="0.3">
@@ -10802,7 +10802,7 @@
         <v>18</v>
       </c>
       <c r="F516" s="4">
-        <v>46.870123100000001</v>
+        <v>18.74804924</v>
       </c>
     </row>
     <row r="517" spans="1:6" x14ac:dyDescent="0.3">
@@ -10822,7 +10822,7 @@
         <v>19</v>
       </c>
       <c r="F517" s="4">
-        <v>0.13498505999999999</v>
+        <v>5.3994024000000002E-2</v>
       </c>
     </row>
     <row r="518" spans="1:6" x14ac:dyDescent="0.3">
@@ -10842,7 +10842,7 @@
         <v>14</v>
       </c>
       <c r="F518" s="4">
-        <v>78.940247990000003</v>
+        <v>31.576099196000001</v>
       </c>
     </row>
     <row r="519" spans="1:6" x14ac:dyDescent="0.3">
@@ -10862,7 +10862,7 @@
         <v>15</v>
       </c>
       <c r="F519" s="4">
-        <v>0.63050587000000002</v>
+        <v>0.25220234800000002</v>
       </c>
     </row>
     <row r="520" spans="1:6" x14ac:dyDescent="0.3">
@@ -10882,7 +10882,7 @@
         <v>21</v>
       </c>
       <c r="F520" s="4">
-        <v>1.4303018599999999</v>
+        <v>0.57212074400000001</v>
       </c>
     </row>
     <row r="521" spans="1:6" x14ac:dyDescent="0.3">
@@ -10902,7 +10902,7 @@
         <v>27</v>
       </c>
       <c r="F521" s="4">
-        <v>8.8197234000000009</v>
+        <v>3.5278893600000005</v>
       </c>
     </row>
     <row r="522" spans="1:6" x14ac:dyDescent="0.3">
@@ -10922,7 +10922,7 @@
         <v>24</v>
       </c>
       <c r="F522" s="4">
-        <v>-0.70702281</v>
+        <v>-0.28280912400000002</v>
       </c>
     </row>
     <row r="523" spans="1:6" x14ac:dyDescent="0.3">
@@ -10942,7 +10942,7 @@
         <v>23</v>
       </c>
       <c r="F523" s="4">
-        <v>19.18397672</v>
+        <v>7.6735906880000009</v>
       </c>
     </row>
     <row r="524" spans="1:6" x14ac:dyDescent="0.3">
@@ -10962,7 +10962,7 @@
         <v>21</v>
       </c>
       <c r="F524" s="4">
-        <v>9.35442471</v>
+        <v>3.741769884</v>
       </c>
     </row>
     <row r="525" spans="1:6" x14ac:dyDescent="0.3">
@@ -11002,7 +11002,7 @@
         <v>13</v>
       </c>
       <c r="F526" s="4">
-        <v>1.71075128</v>
+        <v>0.68430051200000008</v>
       </c>
     </row>
     <row r="527" spans="1:6" x14ac:dyDescent="0.3">
@@ -11022,7 +11022,7 @@
         <v>23</v>
       </c>
       <c r="F527" s="4">
-        <v>38.381357379999997</v>
+        <v>15.352542952</v>
       </c>
     </row>
     <row r="528" spans="1:6" x14ac:dyDescent="0.3">
@@ -11062,7 +11062,7 @@
         <v>18</v>
       </c>
       <c r="F529" s="4">
-        <v>86.298435359999999</v>
+        <v>34.519374144000004</v>
       </c>
     </row>
     <row r="530" spans="1:6" x14ac:dyDescent="0.3">
@@ -11082,7 +11082,7 @@
         <v>14</v>
       </c>
       <c r="F530" s="4">
-        <v>75.724074329999993</v>
+        <v>30.289629731999998</v>
       </c>
     </row>
     <row r="531" spans="1:6" x14ac:dyDescent="0.3">
@@ -11102,7 +11102,7 @@
         <v>8</v>
       </c>
       <c r="F531" s="4">
-        <v>34.553776599999999</v>
+        <v>13.82151064</v>
       </c>
     </row>
     <row r="532" spans="1:6" x14ac:dyDescent="0.3">
@@ -11122,7 +11122,7 @@
         <v>18</v>
       </c>
       <c r="F532" s="4">
-        <v>82.420071129999997</v>
+        <v>32.968028451999999</v>
       </c>
     </row>
     <row r="533" spans="1:6" x14ac:dyDescent="0.3">
@@ -11162,7 +11162,7 @@
         <v>8</v>
       </c>
       <c r="F534" s="4">
-        <v>76.233266549999996</v>
+        <v>30.493306619999998</v>
       </c>
     </row>
     <row r="535" spans="1:6" x14ac:dyDescent="0.3">
@@ -11182,7 +11182,7 @@
         <v>19</v>
       </c>
       <c r="F535" s="4">
-        <v>-0.16313567000000001</v>
+        <v>-6.5254268000000004E-2</v>
       </c>
     </row>
     <row r="536" spans="1:6" x14ac:dyDescent="0.3">
@@ -11202,7 +11202,7 @@
         <v>14</v>
       </c>
       <c r="F536" s="4">
-        <v>76.893692040000005</v>
+        <v>30.757476816000004</v>
       </c>
     </row>
     <row r="537" spans="1:6" x14ac:dyDescent="0.3">
@@ -11222,7 +11222,7 @@
         <v>21</v>
       </c>
       <c r="F537" s="4">
-        <v>1.4082376400000001</v>
+        <v>0.56329505600000007</v>
       </c>
     </row>
     <row r="538" spans="1:6" x14ac:dyDescent="0.3">
@@ -11242,7 +11242,7 @@
         <v>13</v>
       </c>
       <c r="F538" s="4">
-        <v>-0.66361133999999999</v>
+        <v>-0.26544453600000001</v>
       </c>
     </row>
     <row r="539" spans="1:6" x14ac:dyDescent="0.3">
@@ -11262,7 +11262,7 @@
         <v>20</v>
       </c>
       <c r="F539" s="4">
-        <v>245.96888512999999</v>
+        <v>98.387554051999999</v>
       </c>
     </row>
     <row r="540" spans="1:6" x14ac:dyDescent="0.3">
@@ -11282,7 +11282,7 @@
         <v>21</v>
       </c>
       <c r="F540" s="4">
-        <v>1.58492762</v>
+        <v>0.63397104800000004</v>
       </c>
     </row>
     <row r="541" spans="1:6" x14ac:dyDescent="0.3">
@@ -11302,7 +11302,7 @@
         <v>18</v>
       </c>
       <c r="F541" s="4">
-        <v>46.743349000000002</v>
+        <v>18.697339600000003</v>
       </c>
     </row>
     <row r="542" spans="1:6" x14ac:dyDescent="0.3">
@@ -11322,7 +11322,7 @@
         <v>24</v>
       </c>
       <c r="F542" s="4">
-        <v>13.83957277</v>
+        <v>5.5358291080000006</v>
       </c>
     </row>
     <row r="543" spans="1:6" x14ac:dyDescent="0.3">
@@ -11362,7 +11362,7 @@
         <v>21</v>
       </c>
       <c r="F544" s="4">
-        <v>8.7986421700000008</v>
+        <v>3.5194568680000007</v>
       </c>
     </row>
     <row r="545" spans="1:6" x14ac:dyDescent="0.3">
@@ -11422,7 +11422,7 @@
         <v>11</v>
       </c>
       <c r="F547" s="4">
-        <v>16.90155549</v>
+        <v>6.7606221959999999</v>
       </c>
     </row>
     <row r="548" spans="1:6" x14ac:dyDescent="0.3">
@@ -11462,7 +11462,7 @@
         <v>24</v>
       </c>
       <c r="F549" s="4">
-        <v>1.67335481</v>
+        <v>0.66934192400000003</v>
       </c>
     </row>
     <row r="550" spans="1:6" x14ac:dyDescent="0.3">
@@ -11482,7 +11482,7 @@
         <v>23</v>
       </c>
       <c r="F550" s="4">
-        <v>21.991964790000001</v>
+        <v>8.796785916000001</v>
       </c>
     </row>
     <row r="551" spans="1:6" x14ac:dyDescent="0.3">
@@ -11502,7 +11502,7 @@
         <v>14</v>
       </c>
       <c r="F551" s="4">
-        <v>36.285697890000002</v>
+        <v>14.514279156000001</v>
       </c>
     </row>
     <row r="552" spans="1:6" x14ac:dyDescent="0.3">
@@ -11542,7 +11542,7 @@
         <v>11</v>
       </c>
       <c r="F553" s="4">
-        <v>11.809493679999999</v>
+        <v>4.7237974720000002</v>
       </c>
     </row>
     <row r="554" spans="1:6" x14ac:dyDescent="0.3">
@@ -11582,7 +11582,7 @@
         <v>21</v>
       </c>
       <c r="F555" s="4">
-        <v>1.5832980800000001</v>
+        <v>0.63331923200000007</v>
       </c>
     </row>
     <row r="556" spans="1:6" x14ac:dyDescent="0.3">
@@ -11602,7 +11602,7 @@
         <v>26</v>
       </c>
       <c r="F556" s="4">
-        <v>46.60382654</v>
+        <v>18.641530616000001</v>
       </c>
     </row>
     <row r="557" spans="1:6" x14ac:dyDescent="0.3">
@@ -11642,7 +11642,7 @@
         <v>15</v>
       </c>
       <c r="F558" s="4">
-        <v>2.4408883000000001</v>
+        <v>0.97635532000000014</v>
       </c>
     </row>
     <row r="559" spans="1:6" x14ac:dyDescent="0.3">
@@ -11662,7 +11662,7 @@
         <v>23</v>
       </c>
       <c r="F559" s="4">
-        <v>10.05517659</v>
+        <v>4.0220706360000005</v>
       </c>
     </row>
     <row r="560" spans="1:6" x14ac:dyDescent="0.3">
@@ -11682,7 +11682,7 @@
         <v>14</v>
       </c>
       <c r="F560" s="4">
-        <v>40.895413980000001</v>
+        <v>16.358165592000002</v>
       </c>
     </row>
     <row r="561" spans="1:6" x14ac:dyDescent="0.3">
@@ -11702,7 +11702,7 @@
         <v>15</v>
       </c>
       <c r="F561" s="4">
-        <v>0.57939143000000004</v>
+        <v>0.23175657200000002</v>
       </c>
     </row>
     <row r="562" spans="1:6" x14ac:dyDescent="0.3">
@@ -11722,7 +11722,7 @@
         <v>14</v>
       </c>
       <c r="F562" s="4">
-        <v>90.781570430000002</v>
+        <v>36.312628172000004</v>
       </c>
     </row>
     <row r="563" spans="1:6" x14ac:dyDescent="0.3">
@@ -11742,7 +11742,7 @@
         <v>23</v>
       </c>
       <c r="F563" s="4">
-        <v>66.721213539999994</v>
+        <v>26.688485415999999</v>
       </c>
     </row>
     <row r="564" spans="1:6" x14ac:dyDescent="0.3">
@@ -11762,7 +11762,7 @@
         <v>20</v>
       </c>
       <c r="F564" s="4">
-        <v>267.47965986999998</v>
+        <v>106.991863948</v>
       </c>
     </row>
     <row r="565" spans="1:6" x14ac:dyDescent="0.3">
@@ -11782,7 +11782,7 @@
         <v>15</v>
       </c>
       <c r="F565" s="4">
-        <v>0.65398111999999997</v>
+        <v>0.26159244799999998</v>
       </c>
     </row>
     <row r="566" spans="1:6" x14ac:dyDescent="0.3">
@@ -11802,7 +11802,7 @@
         <v>23</v>
       </c>
       <c r="F566" s="4">
-        <v>9.4110370200000002</v>
+        <v>3.7644148080000002</v>
       </c>
     </row>
     <row r="567" spans="1:6" x14ac:dyDescent="0.3">
@@ -11822,7 +11822,7 @@
         <v>27</v>
       </c>
       <c r="F567" s="4">
-        <v>0.63650662999999996</v>
+        <v>0.25460265199999998</v>
       </c>
     </row>
     <row r="568" spans="1:6" x14ac:dyDescent="0.3">
@@ -11842,7 +11842,7 @@
         <v>15</v>
       </c>
       <c r="F568" s="4">
-        <v>3.5759546599999998</v>
+        <v>1.4303818640000001</v>
       </c>
     </row>
     <row r="569" spans="1:6" x14ac:dyDescent="0.3">
@@ -11922,7 +11922,7 @@
         <v>8</v>
       </c>
       <c r="F572" s="4">
-        <v>34.698195329999997</v>
+        <v>13.879278132</v>
       </c>
     </row>
     <row r="573" spans="1:6" x14ac:dyDescent="0.3">
@@ -11942,7 +11942,7 @@
         <v>8</v>
       </c>
       <c r="F573" s="4">
-        <v>45.475606730000003</v>
+        <v>18.190242692000002</v>
       </c>
     </row>
     <row r="574" spans="1:6" x14ac:dyDescent="0.3">
@@ -12002,7 +12002,7 @@
         <v>23</v>
       </c>
       <c r="F576" s="4">
-        <v>16.57314242</v>
+        <v>6.629256968</v>
       </c>
     </row>
     <row r="577" spans="1:6" x14ac:dyDescent="0.3">
@@ -12022,7 +12022,7 @@
         <v>18</v>
       </c>
       <c r="F577" s="4">
-        <v>84.289699200000001</v>
+        <v>33.71587968</v>
       </c>
     </row>
     <row r="578" spans="1:6" x14ac:dyDescent="0.3">
@@ -12062,7 +12062,7 @@
         <v>14</v>
       </c>
       <c r="F579" s="4">
-        <v>76.056847790000006</v>
+        <v>30.422739116000002</v>
       </c>
     </row>
     <row r="580" spans="1:6" x14ac:dyDescent="0.3">
@@ -12082,7 +12082,7 @@
         <v>23</v>
       </c>
       <c r="F580" s="4">
-        <v>10.13080081</v>
+        <v>4.0523203240000001</v>
       </c>
     </row>
     <row r="581" spans="1:6" x14ac:dyDescent="0.3">
@@ -12102,7 +12102,7 @@
         <v>13</v>
       </c>
       <c r="F581" s="4">
-        <v>0.12105008</v>
+        <v>4.8420032000000002E-2</v>
       </c>
     </row>
     <row r="582" spans="1:6" x14ac:dyDescent="0.3">
@@ -12122,7 +12122,7 @@
         <v>27</v>
       </c>
       <c r="F582" s="4">
-        <v>6.34465038</v>
+        <v>2.5378601520000004</v>
       </c>
     </row>
     <row r="583" spans="1:6" x14ac:dyDescent="0.3">
@@ -12142,7 +12142,7 @@
         <v>20</v>
       </c>
       <c r="F583" s="4">
-        <v>53.597948729999999</v>
+        <v>21.439179492000001</v>
       </c>
     </row>
     <row r="584" spans="1:6" x14ac:dyDescent="0.3">
@@ -12162,7 +12162,7 @@
         <v>24</v>
       </c>
       <c r="F584" s="4">
-        <v>11.736724110000001</v>
+        <v>4.6946896440000003</v>
       </c>
     </row>
     <row r="585" spans="1:6" x14ac:dyDescent="0.3">
@@ -12202,7 +12202,7 @@
         <v>14</v>
       </c>
       <c r="F586" s="4">
-        <v>75.967633219999996</v>
+        <v>30.387053288000001</v>
       </c>
     </row>
     <row r="587" spans="1:6" x14ac:dyDescent="0.3">
@@ -12242,7 +12242,7 @@
         <v>26</v>
       </c>
       <c r="F588" s="4">
-        <v>52.782092630000001</v>
+        <v>21.112837052000003</v>
       </c>
     </row>
     <row r="589" spans="1:6" x14ac:dyDescent="0.3">
@@ -12262,7 +12262,7 @@
         <v>15</v>
       </c>
       <c r="F589" s="4">
-        <v>0.40103127999999999</v>
+        <v>0.16041251200000001</v>
       </c>
     </row>
     <row r="590" spans="1:6" x14ac:dyDescent="0.3">
@@ -12282,7 +12282,7 @@
         <v>20</v>
       </c>
       <c r="F590" s="4">
-        <v>40.65187495</v>
+        <v>16.26074998</v>
       </c>
     </row>
     <row r="591" spans="1:6" x14ac:dyDescent="0.3">
@@ -12302,7 +12302,7 @@
         <v>8</v>
       </c>
       <c r="F591" s="4">
-        <v>39.99590388</v>
+        <v>15.998361552</v>
       </c>
     </row>
     <row r="592" spans="1:6" x14ac:dyDescent="0.3">
@@ -12342,7 +12342,7 @@
         <v>18</v>
       </c>
       <c r="F593" s="4">
-        <v>270.88106385999998</v>
+        <v>108.352425544</v>
       </c>
     </row>
     <row r="594" spans="1:6" x14ac:dyDescent="0.3">
@@ -12362,7 +12362,7 @@
         <v>15</v>
       </c>
       <c r="F594" s="4">
-        <v>2.70800654</v>
+        <v>1.0832026160000001</v>
       </c>
     </row>
     <row r="595" spans="1:6" x14ac:dyDescent="0.3">
@@ -12382,7 +12382,7 @@
         <v>18</v>
       </c>
       <c r="F595" s="4">
-        <v>78.164434119999996</v>
+        <v>31.265773648</v>
       </c>
     </row>
     <row r="596" spans="1:6" x14ac:dyDescent="0.3">
@@ -12402,7 +12402,7 @@
         <v>23</v>
       </c>
       <c r="F596" s="4">
-        <v>23.399157290000002</v>
+        <v>9.3596629160000013</v>
       </c>
     </row>
     <row r="597" spans="1:6" x14ac:dyDescent="0.3">
@@ -12422,7 +12422,7 @@
         <v>13</v>
       </c>
       <c r="F597" s="4">
-        <v>-2.5671765</v>
+        <v>-1.0268706000000001</v>
       </c>
     </row>
     <row r="598" spans="1:6" x14ac:dyDescent="0.3">
@@ -12442,7 +12442,7 @@
         <v>21</v>
       </c>
       <c r="F598" s="4">
-        <v>8.1231812600000008</v>
+        <v>3.2492725040000003</v>
       </c>
     </row>
     <row r="599" spans="1:6" x14ac:dyDescent="0.3">
@@ -12462,7 +12462,7 @@
         <v>27</v>
       </c>
       <c r="F599" s="4">
-        <v>4.9439698500000002</v>
+        <v>1.9775879400000003</v>
       </c>
     </row>
     <row r="600" spans="1:6" x14ac:dyDescent="0.3">
@@ -12482,7 +12482,7 @@
         <v>13</v>
       </c>
       <c r="F600" s="4">
-        <v>-0.73542428000000004</v>
+        <v>-0.29416971200000003</v>
       </c>
     </row>
     <row r="601" spans="1:6" x14ac:dyDescent="0.3">
@@ -12502,7 +12502,7 @@
         <v>11</v>
       </c>
       <c r="F601" s="4">
-        <v>11.17915719</v>
+        <v>4.4716628759999999</v>
       </c>
     </row>
     <row r="602" spans="1:6" x14ac:dyDescent="0.3">
@@ -12522,7 +12522,7 @@
         <v>14</v>
       </c>
       <c r="F602" s="4">
-        <v>35.757629659999999</v>
+        <v>14.303051864</v>
       </c>
     </row>
     <row r="603" spans="1:6" x14ac:dyDescent="0.3">
@@ -12542,7 +12542,7 @@
         <v>27</v>
       </c>
       <c r="F603" s="4">
-        <v>8.6485728599999998</v>
+        <v>3.459429144</v>
       </c>
     </row>
     <row r="604" spans="1:6" x14ac:dyDescent="0.3">
@@ -12562,7 +12562,7 @@
         <v>20</v>
       </c>
       <c r="F604" s="4">
-        <v>38.663492290000001</v>
+        <v>15.465396916000001</v>
       </c>
     </row>
     <row r="605" spans="1:6" x14ac:dyDescent="0.3">
@@ -12622,7 +12622,7 @@
         <v>23</v>
       </c>
       <c r="F607" s="4">
-        <v>30.13106277</v>
+        <v>12.052425108000001</v>
       </c>
     </row>
     <row r="608" spans="1:6" x14ac:dyDescent="0.3">
@@ -12662,7 +12662,7 @@
         <v>8</v>
       </c>
       <c r="F609" s="4">
-        <v>46.315808570000002</v>
+        <v>18.526323428000001</v>
       </c>
     </row>
     <row r="610" spans="1:6" x14ac:dyDescent="0.3">
@@ -12682,7 +12682,7 @@
         <v>23</v>
       </c>
       <c r="F610" s="4">
-        <v>47.589781049999999</v>
+        <v>19.035912419999999</v>
       </c>
     </row>
     <row r="611" spans="1:6" x14ac:dyDescent="0.3">
@@ -12702,7 +12702,7 @@
         <v>20</v>
       </c>
       <c r="F611" s="4">
-        <v>301.70792559</v>
+        <v>120.68317023600001</v>
       </c>
     </row>
     <row r="612" spans="1:6" x14ac:dyDescent="0.3">
@@ -12742,7 +12742,7 @@
         <v>14</v>
       </c>
       <c r="F613" s="4">
-        <v>59.423227320000002</v>
+        <v>23.769290928000004</v>
       </c>
     </row>
     <row r="614" spans="1:6" x14ac:dyDescent="0.3">
@@ -12762,7 +12762,7 @@
         <v>15</v>
       </c>
       <c r="F614" s="4">
-        <v>2.5511533200000001</v>
+        <v>1.0204613280000001</v>
       </c>
     </row>
     <row r="615" spans="1:6" x14ac:dyDescent="0.3">
@@ -12782,7 +12782,7 @@
         <v>14</v>
       </c>
       <c r="F615" s="4">
-        <v>39.0127363</v>
+        <v>15.605094520000002</v>
       </c>
     </row>
     <row r="616" spans="1:6" x14ac:dyDescent="0.3">
@@ -12802,7 +12802,7 @@
         <v>15</v>
       </c>
       <c r="F616" s="4">
-        <v>0.36740426999999998</v>
+        <v>0.146961708</v>
       </c>
     </row>
     <row r="617" spans="1:6" x14ac:dyDescent="0.3">
@@ -12822,7 +12822,7 @@
         <v>14</v>
       </c>
       <c r="F617" s="4">
-        <v>77.561434059999996</v>
+        <v>31.024573623999999</v>
       </c>
     </row>
     <row r="618" spans="1:6" x14ac:dyDescent="0.3">
@@ -12842,7 +12842,7 @@
         <v>13</v>
       </c>
       <c r="F618" s="4">
-        <v>-0.66312565000000001</v>
+        <v>-0.26525026000000002</v>
       </c>
     </row>
     <row r="619" spans="1:6" x14ac:dyDescent="0.3">
@@ -12882,7 +12882,7 @@
         <v>14</v>
       </c>
       <c r="F620" s="4">
-        <v>38.431937300000001</v>
+        <v>15.372774920000001</v>
       </c>
     </row>
     <row r="621" spans="1:6" x14ac:dyDescent="0.3">
@@ -12902,7 +12902,7 @@
         <v>27</v>
       </c>
       <c r="F621" s="4">
-        <v>22.45167464</v>
+        <v>8.9806698560000005</v>
       </c>
     </row>
     <row r="622" spans="1:6" x14ac:dyDescent="0.3">
@@ -12942,7 +12942,7 @@
         <v>18</v>
       </c>
       <c r="F623" s="4">
-        <v>82.424264600000001</v>
+        <v>32.969705840000003</v>
       </c>
     </row>
     <row r="624" spans="1:6" x14ac:dyDescent="0.3">
@@ -12962,7 +12962,7 @@
         <v>20</v>
       </c>
       <c r="F624" s="4">
-        <v>72.825136580000006</v>
+        <v>29.130054632000004</v>
       </c>
     </row>
     <row r="625" spans="1:6" x14ac:dyDescent="0.3">
@@ -12982,7 +12982,7 @@
         <v>14</v>
       </c>
       <c r="F625" s="4">
-        <v>76.134591920000005</v>
+        <v>30.453836768000002</v>
       </c>
     </row>
     <row r="626" spans="1:6" x14ac:dyDescent="0.3">
@@ -13002,7 +13002,7 @@
         <v>23</v>
       </c>
       <c r="F626" s="4">
-        <v>18.35381602</v>
+        <v>7.341526408</v>
       </c>
     </row>
     <row r="627" spans="1:6" x14ac:dyDescent="0.3">
@@ -13022,7 +13022,7 @@
         <v>21</v>
       </c>
       <c r="F627" s="4">
-        <v>2.1759905000000002</v>
+        <v>0.87039620000000006</v>
       </c>
     </row>
     <row r="628" spans="1:6" x14ac:dyDescent="0.3">
@@ -13042,7 +13042,7 @@
         <v>15</v>
       </c>
       <c r="F628" s="4">
-        <v>0.69209969999999998</v>
+        <v>0.27683987999999998</v>
       </c>
     </row>
     <row r="629" spans="1:6" x14ac:dyDescent="0.3">
@@ -13102,7 +13102,7 @@
         <v>15</v>
       </c>
       <c r="F631" s="4">
-        <v>2.50371978</v>
+        <v>1.001487912</v>
       </c>
     </row>
     <row r="632" spans="1:6" x14ac:dyDescent="0.3">
@@ -13122,7 +13122,7 @@
         <v>23</v>
       </c>
       <c r="F632" s="4">
-        <v>15.170143879999999</v>
+        <v>6.068057552</v>
       </c>
     </row>
     <row r="633" spans="1:6" x14ac:dyDescent="0.3">
@@ -13142,7 +13142,7 @@
         <v>11</v>
       </c>
       <c r="F633" s="4">
-        <v>7.7980825999999999</v>
+        <v>3.1192330400000001</v>
       </c>
     </row>
     <row r="634" spans="1:6" x14ac:dyDescent="0.3">
@@ -13162,7 +13162,7 @@
         <v>13</v>
       </c>
       <c r="F634" s="4">
-        <v>-2.5598360499999999</v>
+        <v>-1.02393442</v>
       </c>
     </row>
     <row r="635" spans="1:6" x14ac:dyDescent="0.3">
@@ -13182,7 +13182,7 @@
         <v>27</v>
       </c>
       <c r="F635" s="4">
-        <v>24.497485749999999</v>
+        <v>9.7989943000000004</v>
       </c>
     </row>
     <row r="636" spans="1:6" x14ac:dyDescent="0.3">
@@ -13202,7 +13202,7 @@
         <v>14</v>
       </c>
       <c r="F636" s="4">
-        <v>40.26744308</v>
+        <v>16.106977232000002</v>
       </c>
     </row>
     <row r="637" spans="1:6" x14ac:dyDescent="0.3">
@@ -13222,7 +13222,7 @@
         <v>27</v>
       </c>
       <c r="F637" s="4">
-        <v>13.599779099999999</v>
+        <v>5.43991164</v>
       </c>
     </row>
     <row r="638" spans="1:6" x14ac:dyDescent="0.3">
@@ -13242,7 +13242,7 @@
         <v>14</v>
       </c>
       <c r="F638" s="4">
-        <v>75.967633219999996</v>
+        <v>30.387053288000001</v>
       </c>
     </row>
     <row r="639" spans="1:6" x14ac:dyDescent="0.3">
@@ -13262,7 +13262,7 @@
         <v>13</v>
       </c>
       <c r="F639" s="4">
-        <v>2.201204E-2</v>
+        <v>8.804816E-3</v>
       </c>
     </row>
     <row r="640" spans="1:6" x14ac:dyDescent="0.3">
@@ -13282,7 +13282,7 @@
         <v>13</v>
       </c>
       <c r="F640" s="4">
-        <v>-0.30025081999999997</v>
+        <v>-0.12010032799999999</v>
       </c>
     </row>
     <row r="641" spans="1:6" x14ac:dyDescent="0.3">
@@ -13302,7 +13302,7 @@
         <v>23</v>
       </c>
       <c r="F641" s="4">
-        <v>18.415653509999999</v>
+        <v>7.3662614039999994</v>
       </c>
     </row>
     <row r="642" spans="1:6" x14ac:dyDescent="0.3">
@@ -13322,7 +13322,7 @@
         <v>20</v>
       </c>
       <c r="F642" s="4">
-        <v>370.14482509999999</v>
+        <v>148.05793004</v>
       </c>
     </row>
     <row r="643" spans="1:6" x14ac:dyDescent="0.3">
@@ -13342,7 +13342,7 @@
         <v>19</v>
       </c>
       <c r="F643" s="4">
-        <v>-0.28681265</v>
+        <v>-0.11472506</v>
       </c>
     </row>
     <row r="644" spans="1:6" x14ac:dyDescent="0.3">
@@ -13362,7 +13362,7 @@
         <v>23</v>
       </c>
       <c r="F644" s="4">
-        <v>46.875534129999998</v>
+        <v>18.750213651999999</v>
       </c>
     </row>
     <row r="645" spans="1:6" x14ac:dyDescent="0.3">
@@ -13382,7 +13382,7 @@
         <v>21</v>
       </c>
       <c r="F645" s="4">
-        <v>1.33306335</v>
+        <v>0.53322533999999999</v>
       </c>
     </row>
     <row r="646" spans="1:6" x14ac:dyDescent="0.3">
@@ -13422,7 +13422,7 @@
         <v>19</v>
       </c>
       <c r="F647" s="4">
-        <v>-6.7662990000000006E-2</v>
+        <v>-2.7065196000000003E-2</v>
       </c>
     </row>
     <row r="648" spans="1:6" x14ac:dyDescent="0.3">
@@ -13442,7 +13442,7 @@
         <v>21</v>
       </c>
       <c r="F648" s="4">
-        <v>1.6169568299999999</v>
+        <v>0.64678273200000003</v>
       </c>
     </row>
     <row r="649" spans="1:6" x14ac:dyDescent="0.3">
@@ -13462,7 +13462,7 @@
         <v>23</v>
       </c>
       <c r="F649" s="4">
-        <v>9.7151968800000006</v>
+        <v>3.8860787520000004</v>
       </c>
     </row>
     <row r="650" spans="1:6" x14ac:dyDescent="0.3">
@@ -13482,7 +13482,7 @@
         <v>11</v>
       </c>
       <c r="F650" s="4">
-        <v>11.493744469999999</v>
+        <v>4.5974977880000001</v>
       </c>
     </row>
     <row r="651" spans="1:6" x14ac:dyDescent="0.3">
@@ -13502,7 +13502,7 @@
         <v>26</v>
       </c>
       <c r="F651" s="4">
-        <v>58.49861516</v>
+        <v>23.399446064000003</v>
       </c>
     </row>
     <row r="652" spans="1:6" x14ac:dyDescent="0.3">
@@ -13522,7 +13522,7 @@
         <v>14</v>
       </c>
       <c r="F652" s="4">
-        <v>38.431937300000001</v>
+        <v>15.372774920000001</v>
       </c>
     </row>
     <row r="653" spans="1:6" x14ac:dyDescent="0.3">
@@ -13542,7 +13542,7 @@
         <v>11</v>
       </c>
       <c r="F653" s="4">
-        <v>17.861221889999999</v>
+        <v>7.1444887560000003</v>
       </c>
     </row>
     <row r="654" spans="1:6" x14ac:dyDescent="0.3">
@@ -13562,7 +13562,7 @@
         <v>15</v>
       </c>
       <c r="F654" s="4">
-        <v>0.68677655000000004</v>
+        <v>0.27471062000000002</v>
       </c>
     </row>
     <row r="655" spans="1:6" x14ac:dyDescent="0.3">
@@ -13622,7 +13622,7 @@
         <v>20</v>
       </c>
       <c r="F657" s="4">
-        <v>90.345092550000004</v>
+        <v>36.138037020000006</v>
       </c>
     </row>
     <row r="658" spans="1:6" x14ac:dyDescent="0.3">
@@ -13642,7 +13642,7 @@
         <v>23</v>
       </c>
       <c r="F658" s="4">
-        <v>18.530083730000001</v>
+        <v>7.4120334920000008</v>
       </c>
     </row>
     <row r="659" spans="1:6" x14ac:dyDescent="0.3">
@@ -13662,7 +13662,7 @@
         <v>14</v>
       </c>
       <c r="F659" s="4">
-        <v>78.265309009999996</v>
+        <v>31.306123604</v>
       </c>
     </row>
     <row r="660" spans="1:6" x14ac:dyDescent="0.3">
@@ -13682,7 +13682,7 @@
         <v>13</v>
       </c>
       <c r="F660" s="4">
-        <v>-2.1191994200000002</v>
+        <v>-0.84767976800000011</v>
       </c>
     </row>
     <row r="661" spans="1:6" x14ac:dyDescent="0.3">
@@ -13702,7 +13702,7 @@
         <v>20</v>
       </c>
       <c r="F661" s="4">
-        <v>42.128632189999998</v>
+        <v>16.851452876</v>
       </c>
     </row>
     <row r="662" spans="1:6" x14ac:dyDescent="0.3">
@@ -13722,7 +13722,7 @@
         <v>20</v>
       </c>
       <c r="F662" s="4">
-        <v>73.134859329999998</v>
+        <v>29.253943732</v>
       </c>
     </row>
     <row r="663" spans="1:6" x14ac:dyDescent="0.3">
@@ -13742,7 +13742,7 @@
         <v>13</v>
       </c>
       <c r="F663" s="4">
-        <v>-0.58220373000000003</v>
+        <v>-0.23288149200000002</v>
       </c>
     </row>
     <row r="664" spans="1:6" x14ac:dyDescent="0.3">
@@ -13782,7 +13782,7 @@
         <v>14</v>
       </c>
       <c r="F665" s="4">
-        <v>60.690788869999999</v>
+        <v>24.276315547999999</v>
       </c>
     </row>
     <row r="666" spans="1:6" x14ac:dyDescent="0.3">
@@ -13802,7 +13802,7 @@
         <v>19</v>
       </c>
       <c r="F666" s="4">
-        <v>-0.11833206</v>
+        <v>-4.7332824000000003E-2</v>
       </c>
     </row>
     <row r="667" spans="1:6" x14ac:dyDescent="0.3">
@@ -13842,7 +13842,7 @@
         <v>14</v>
       </c>
       <c r="F668" s="4">
-        <v>69.673022840000002</v>
+        <v>27.869209136000002</v>
       </c>
     </row>
     <row r="669" spans="1:6" x14ac:dyDescent="0.3">
@@ -13862,7 +13862,7 @@
         <v>21</v>
       </c>
       <c r="F669" s="4">
-        <v>1.61145962</v>
+        <v>0.64458384800000001</v>
       </c>
     </row>
     <row r="670" spans="1:6" x14ac:dyDescent="0.3">
@@ -13882,7 +13882,7 @@
         <v>21</v>
       </c>
       <c r="F670" s="4">
-        <v>1.1172118</v>
+        <v>0.44688472000000001</v>
       </c>
     </row>
     <row r="671" spans="1:6" x14ac:dyDescent="0.3">
@@ -13922,7 +13922,7 @@
         <v>24</v>
       </c>
       <c r="F672" s="4">
-        <v>5.1885789300000003</v>
+        <v>2.0754315720000003</v>
       </c>
     </row>
     <row r="673" spans="1:6" x14ac:dyDescent="0.3">
@@ -13942,7 +13942,7 @@
         <v>14</v>
       </c>
       <c r="F673" s="4">
-        <v>63.328390429999999</v>
+        <v>25.331356172</v>
       </c>
     </row>
     <row r="674" spans="1:6" x14ac:dyDescent="0.3">
@@ -13982,7 +13982,7 @@
         <v>23</v>
       </c>
       <c r="F675" s="4">
-        <v>16.18429896</v>
+        <v>6.4737195840000004</v>
       </c>
     </row>
     <row r="676" spans="1:6" x14ac:dyDescent="0.3">
@@ -14022,7 +14022,7 @@
         <v>13</v>
       </c>
       <c r="F677" s="4">
-        <v>0.12105008</v>
+        <v>4.8420032000000002E-2</v>
       </c>
     </row>
     <row r="678" spans="1:6" x14ac:dyDescent="0.3">
@@ -14042,7 +14042,7 @@
         <v>14</v>
       </c>
       <c r="F678" s="4">
-        <v>57.036192870000001</v>
+        <v>22.814477148000002</v>
       </c>
     </row>
     <row r="679" spans="1:6" x14ac:dyDescent="0.3">
@@ -14062,7 +14062,7 @@
         <v>24</v>
       </c>
       <c r="F679" s="4">
-        <v>18.638755710000002</v>
+        <v>7.4555022840000014</v>
       </c>
     </row>
     <row r="680" spans="1:6" x14ac:dyDescent="0.3">
@@ -14082,7 +14082,7 @@
         <v>15</v>
       </c>
       <c r="F680" s="4">
-        <v>0.34880438000000002</v>
+        <v>0.13952175200000003</v>
       </c>
     </row>
     <row r="681" spans="1:6" x14ac:dyDescent="0.3">
@@ -14102,7 +14102,7 @@
         <v>18</v>
       </c>
       <c r="F681" s="4">
-        <v>267.16647219999999</v>
+        <v>106.86658887999999</v>
       </c>
     </row>
     <row r="682" spans="1:6" x14ac:dyDescent="0.3">
@@ -14142,7 +14142,7 @@
         <v>13</v>
       </c>
       <c r="F683" s="4">
-        <v>-2.3201996399999998</v>
+        <v>-0.92807985599999998</v>
       </c>
     </row>
     <row r="684" spans="1:6" x14ac:dyDescent="0.3">
@@ -14162,7 +14162,7 @@
         <v>8</v>
       </c>
       <c r="F684" s="4">
-        <v>80.932212789999994</v>
+        <v>32.372885115999999</v>
       </c>
     </row>
     <row r="685" spans="1:6" x14ac:dyDescent="0.3">
@@ -14182,7 +14182,7 @@
         <v>23</v>
       </c>
       <c r="F685" s="4">
-        <v>18.992078230000001</v>
+        <v>7.596831292000001</v>
       </c>
     </row>
     <row r="686" spans="1:6" x14ac:dyDescent="0.3">
@@ -14202,7 +14202,7 @@
         <v>15</v>
       </c>
       <c r="F686" s="4">
-        <v>2.5947814299999998</v>
+        <v>1.037912572</v>
       </c>
     </row>
     <row r="687" spans="1:6" x14ac:dyDescent="0.3">
@@ -14222,7 +14222,7 @@
         <v>23</v>
       </c>
       <c r="F687" s="4">
-        <v>9.2599083899999997</v>
+        <v>3.703963356</v>
       </c>
     </row>
     <row r="688" spans="1:6" x14ac:dyDescent="0.3">
@@ -14262,7 +14262,7 @@
         <v>23</v>
       </c>
       <c r="F689" s="4">
-        <v>15.068088400000001</v>
+        <v>6.0272353600000006</v>
       </c>
     </row>
     <row r="690" spans="1:6" x14ac:dyDescent="0.3">
@@ -14282,7 +14282,7 @@
         <v>21</v>
       </c>
       <c r="F690" s="4">
-        <v>9.0388030300000004</v>
+        <v>3.6155212120000004</v>
       </c>
     </row>
     <row r="691" spans="1:6" x14ac:dyDescent="0.3">
@@ -14302,7 +14302,7 @@
         <v>8</v>
       </c>
       <c r="F691" s="4">
-        <v>55.446046170000002</v>
+        <v>22.178418468000004</v>
       </c>
     </row>
     <row r="692" spans="1:6" x14ac:dyDescent="0.3">
@@ -14322,7 +14322,7 @@
         <v>21</v>
       </c>
       <c r="F692" s="4">
-        <v>1.5791703399999999</v>
+        <v>0.63166813600000005</v>
       </c>
     </row>
     <row r="693" spans="1:6" x14ac:dyDescent="0.3">
@@ -14342,7 +14342,7 @@
         <v>24</v>
       </c>
       <c r="F693" s="4">
-        <v>1.51197947</v>
+        <v>0.604791788</v>
       </c>
     </row>
     <row r="694" spans="1:6" x14ac:dyDescent="0.3">
@@ -14362,7 +14362,7 @@
         <v>14</v>
       </c>
       <c r="F694" s="4">
-        <v>71.135159349999995</v>
+        <v>28.454063739999999</v>
       </c>
     </row>
     <row r="695" spans="1:6" x14ac:dyDescent="0.3">
@@ -14382,7 +14382,7 @@
         <v>8</v>
       </c>
       <c r="F695" s="4">
-        <v>82.121814400000005</v>
+        <v>32.848725760000001</v>
       </c>
     </row>
     <row r="696" spans="1:6" x14ac:dyDescent="0.3">
@@ -14442,7 +14442,7 @@
         <v>23</v>
       </c>
       <c r="F698" s="4">
-        <v>32.5357664</v>
+        <v>13.014306560000001</v>
       </c>
     </row>
     <row r="699" spans="1:6" x14ac:dyDescent="0.3">
@@ -14462,7 +14462,7 @@
         <v>26</v>
       </c>
       <c r="F699" s="4">
-        <v>51.321729959999999</v>
+        <v>20.528691984000002</v>
       </c>
     </row>
     <row r="700" spans="1:6" x14ac:dyDescent="0.3">
@@ -14482,7 +14482,7 @@
         <v>23</v>
       </c>
       <c r="F700" s="4">
-        <v>16.527102939999999</v>
+        <v>6.6108411760000001</v>
       </c>
     </row>
     <row r="701" spans="1:6" x14ac:dyDescent="0.3">
@@ -14502,7 +14502,7 @@
         <v>19</v>
       </c>
       <c r="F701" s="4">
-        <v>-7.6719979999999993E-2</v>
+        <v>-3.0687991999999997E-2</v>
       </c>
     </row>
     <row r="702" spans="1:6" x14ac:dyDescent="0.3">
@@ -14522,7 +14522,7 @@
         <v>15</v>
       </c>
       <c r="F702" s="4">
-        <v>2.3365838600000002</v>
+        <v>0.93463354400000009</v>
       </c>
     </row>
     <row r="703" spans="1:6" x14ac:dyDescent="0.3">
@@ -14542,7 +14542,7 @@
         <v>14</v>
       </c>
       <c r="F703" s="4">
-        <v>79.71496286</v>
+        <v>31.885985144000003</v>
       </c>
     </row>
     <row r="704" spans="1:6" x14ac:dyDescent="0.3">
@@ -14562,7 +14562,7 @@
         <v>15</v>
       </c>
       <c r="F704" s="4">
-        <v>0.33385883</v>
+        <v>0.13354353199999999</v>
       </c>
     </row>
     <row r="705" spans="1:6" x14ac:dyDescent="0.3">
@@ -14582,7 +14582,7 @@
         <v>15</v>
       </c>
       <c r="F705" s="4">
-        <v>0.62165033000000003</v>
+        <v>0.24866013200000003</v>
       </c>
     </row>
     <row r="706" spans="1:6" x14ac:dyDescent="0.3">
@@ -14622,7 +14622,7 @@
         <v>13</v>
       </c>
       <c r="F707" s="4">
-        <v>-2.3201996399999998</v>
+        <v>-0.92807985599999998</v>
       </c>
     </row>
     <row r="708" spans="1:6" x14ac:dyDescent="0.3">
@@ -14682,7 +14682,7 @@
         <v>14</v>
       </c>
       <c r="F710" s="4">
-        <v>79.71496286</v>
+        <v>31.885985144000003</v>
       </c>
     </row>
     <row r="711" spans="1:6" x14ac:dyDescent="0.3">
@@ -14702,7 +14702,7 @@
         <v>21</v>
       </c>
       <c r="F711" s="4">
-        <v>1.63411306</v>
+        <v>0.65364522400000002</v>
       </c>
     </row>
     <row r="712" spans="1:6" x14ac:dyDescent="0.3">
@@ -14722,7 +14722,7 @@
         <v>13</v>
       </c>
       <c r="F712" s="4">
-        <v>-0.65467841999999998</v>
+        <v>-0.26187136799999999</v>
       </c>
     </row>
     <row r="713" spans="1:6" x14ac:dyDescent="0.3">
@@ -14742,7 +14742,7 @@
         <v>21</v>
       </c>
       <c r="F713" s="4">
-        <v>2.7565175900000001</v>
+        <v>1.102607036</v>
       </c>
     </row>
     <row r="714" spans="1:6" x14ac:dyDescent="0.3">
@@ -14762,7 +14762,7 @@
         <v>13</v>
       </c>
       <c r="F714" s="4">
-        <v>-0.62224003999999999</v>
+        <v>-0.248896016</v>
       </c>
     </row>
     <row r="715" spans="1:6" x14ac:dyDescent="0.3">
@@ -14782,7 +14782,7 @@
         <v>26</v>
       </c>
       <c r="F715" s="4">
-        <v>58.67920505</v>
+        <v>23.471682020000003</v>
       </c>
     </row>
     <row r="716" spans="1:6" x14ac:dyDescent="0.3">
@@ -14802,7 +14802,7 @@
         <v>11</v>
       </c>
       <c r="F716" s="4">
-        <v>11.65247695</v>
+        <v>4.6609907800000006</v>
       </c>
     </row>
     <row r="717" spans="1:6" x14ac:dyDescent="0.3">
@@ -14822,7 +14822,7 @@
         <v>21</v>
       </c>
       <c r="F717" s="4">
-        <v>9.8907276999999993</v>
+        <v>3.9562910799999997</v>
       </c>
     </row>
     <row r="718" spans="1:6" x14ac:dyDescent="0.3">
@@ -14842,7 +14842,7 @@
         <v>18</v>
       </c>
       <c r="F718" s="4">
-        <v>283.20313745999999</v>
+        <v>113.281254984</v>
       </c>
     </row>
     <row r="719" spans="1:6" x14ac:dyDescent="0.3">
@@ -14882,7 +14882,7 @@
         <v>11</v>
       </c>
       <c r="F720" s="4">
-        <v>8.2924631299999998</v>
+        <v>3.3169852520000003</v>
       </c>
     </row>
     <row r="721" spans="1:6" x14ac:dyDescent="0.3">
@@ -14902,7 +14902,7 @@
         <v>24</v>
       </c>
       <c r="F721" s="4">
-        <v>1.2475402499999999</v>
+        <v>0.49901609999999996</v>
       </c>
     </row>
     <row r="722" spans="1:6" x14ac:dyDescent="0.3">
@@ -14922,7 +14922,7 @@
         <v>13</v>
       </c>
       <c r="F722" s="4">
-        <v>-0.56339899000000004</v>
+        <v>-0.22535959600000002</v>
       </c>
     </row>
     <row r="723" spans="1:6" x14ac:dyDescent="0.3">
@@ -14962,7 +14962,7 @@
         <v>13</v>
       </c>
       <c r="F724" s="4">
-        <v>-0.62725737999999998</v>
+        <v>-0.25090295200000001</v>
       </c>
     </row>
     <row r="725" spans="1:6" x14ac:dyDescent="0.3">
@@ -14982,7 +14982,7 @@
         <v>8</v>
       </c>
       <c r="F725" s="4">
-        <v>45.860165629999997</v>
+        <v>18.344066252000001</v>
       </c>
     </row>
     <row r="726" spans="1:6" x14ac:dyDescent="0.3">
@@ -15022,7 +15022,7 @@
         <v>11</v>
       </c>
       <c r="F727" s="4">
-        <v>10.956028359999999</v>
+        <v>4.3824113440000003</v>
       </c>
     </row>
     <row r="728" spans="1:6" x14ac:dyDescent="0.3">
@@ -15062,7 +15062,7 @@
         <v>15</v>
       </c>
       <c r="F729" s="4">
-        <v>0.57339744999999998</v>
+        <v>0.22935897999999999</v>
       </c>
     </row>
     <row r="730" spans="1:6" x14ac:dyDescent="0.3">
@@ -15162,7 +15162,7 @@
         <v>15</v>
       </c>
       <c r="F734" s="4">
-        <v>0.69177763999999997</v>
+        <v>0.27671105600000001</v>
       </c>
     </row>
     <row r="735" spans="1:6" x14ac:dyDescent="0.3">
@@ -15182,7 +15182,7 @@
         <v>21</v>
       </c>
       <c r="F735" s="4">
-        <v>1.3698860500000001</v>
+        <v>0.54795442000000005</v>
       </c>
     </row>
     <row r="736" spans="1:6" x14ac:dyDescent="0.3">
@@ -15202,7 +15202,7 @@
         <v>21</v>
       </c>
       <c r="F736" s="4">
-        <v>8.0760034300000001</v>
+        <v>3.2304013720000002</v>
       </c>
     </row>
     <row r="737" spans="1:6" x14ac:dyDescent="0.3">
@@ -15242,7 +15242,7 @@
         <v>18</v>
       </c>
       <c r="F738" s="4">
-        <v>52.450759480000002</v>
+        <v>20.980303792000001</v>
       </c>
     </row>
     <row r="739" spans="1:6" x14ac:dyDescent="0.3">
@@ -15262,7 +15262,7 @@
         <v>21</v>
       </c>
       <c r="F739" s="4">
-        <v>1.3858958299999999</v>
+        <v>0.55435833199999995</v>
       </c>
     </row>
     <row r="740" spans="1:6" x14ac:dyDescent="0.3">
@@ -15342,7 +15342,7 @@
         <v>27</v>
       </c>
       <c r="F743" s="4">
-        <v>16.29674017</v>
+        <v>6.5186960680000006</v>
       </c>
     </row>
     <row r="744" spans="1:6" x14ac:dyDescent="0.3">
@@ -15362,7 +15362,7 @@
         <v>23</v>
       </c>
       <c r="F744" s="4">
-        <v>18.25543064</v>
+        <v>7.3021722560000004</v>
       </c>
     </row>
     <row r="745" spans="1:6" x14ac:dyDescent="0.3">
@@ -15382,7 +15382,7 @@
         <v>18</v>
       </c>
       <c r="F745" s="4">
-        <v>78.534377359999993</v>
+        <v>31.413750944</v>
       </c>
     </row>
     <row r="746" spans="1:6" x14ac:dyDescent="0.3">
@@ -15422,7 +15422,7 @@
         <v>14</v>
       </c>
       <c r="F747" s="4">
-        <v>78.940247990000003</v>
+        <v>31.576099196000001</v>
       </c>
     </row>
     <row r="748" spans="1:6" x14ac:dyDescent="0.3">
@@ -15442,7 +15442,7 @@
         <v>20</v>
       </c>
       <c r="F748" s="4">
-        <v>94.1740846</v>
+        <v>37.669633840000003</v>
       </c>
     </row>
     <row r="749" spans="1:6" x14ac:dyDescent="0.3">
@@ -15462,7 +15462,7 @@
         <v>23</v>
       </c>
       <c r="F749" s="4">
-        <v>15.378275439999999</v>
+        <v>6.151310176</v>
       </c>
     </row>
     <row r="750" spans="1:6" x14ac:dyDescent="0.3">
@@ -15482,7 +15482,7 @@
         <v>18</v>
       </c>
       <c r="F750" s="4">
-        <v>87.948322250000004</v>
+        <v>35.179328900000002</v>
       </c>
     </row>
     <row r="751" spans="1:6" x14ac:dyDescent="0.3">
@@ -15502,7 +15502,7 @@
         <v>20</v>
       </c>
       <c r="F751" s="4">
-        <v>261.79537131000001</v>
+        <v>104.71814852400001</v>
       </c>
     </row>
     <row r="752" spans="1:6" x14ac:dyDescent="0.3">
@@ -15542,7 +15542,7 @@
         <v>20</v>
       </c>
       <c r="F753" s="4">
-        <v>46.497795549999999</v>
+        <v>18.599118220000001</v>
       </c>
     </row>
     <row r="754" spans="1:6" x14ac:dyDescent="0.3">
@@ -15582,7 +15582,7 @@
         <v>15</v>
       </c>
       <c r="F755" s="4">
-        <v>0.69354992999999998</v>
+        <v>0.27741997200000001</v>
       </c>
     </row>
     <row r="756" spans="1:6" x14ac:dyDescent="0.3">
@@ -15602,7 +15602,7 @@
         <v>18</v>
       </c>
       <c r="F756" s="4">
-        <v>291.31291309</v>
+        <v>116.52516523600001</v>
       </c>
     </row>
     <row r="757" spans="1:6" x14ac:dyDescent="0.3">
@@ -15622,7 +15622,7 @@
         <v>20</v>
       </c>
       <c r="F757" s="4">
-        <v>41.695893249999997</v>
+        <v>16.678357299999998</v>
       </c>
     </row>
     <row r="758" spans="1:6" x14ac:dyDescent="0.3">
@@ -15642,7 +15642,7 @@
         <v>27</v>
       </c>
       <c r="F758" s="4">
-        <v>7.2225244699999998</v>
+        <v>2.8890097880000001</v>
       </c>
     </row>
     <row r="759" spans="1:6" x14ac:dyDescent="0.3">
@@ -15662,7 +15662,7 @@
         <v>15</v>
       </c>
       <c r="F759" s="4">
-        <v>2.45676206</v>
+        <v>0.98270482400000003</v>
       </c>
     </row>
     <row r="760" spans="1:6" x14ac:dyDescent="0.3">
@@ -15702,7 +15702,7 @@
         <v>19</v>
       </c>
       <c r="F761" s="4">
-        <v>-6.6508200000000003E-2</v>
+        <v>-2.6603280000000003E-2</v>
       </c>
     </row>
     <row r="762" spans="1:6" x14ac:dyDescent="0.3">
@@ -15722,7 +15722,7 @@
         <v>8</v>
       </c>
       <c r="F762" s="4">
-        <v>31.101048089999999</v>
+        <v>12.440419236</v>
       </c>
     </row>
     <row r="763" spans="1:6" x14ac:dyDescent="0.3">
@@ -15782,7 +15782,7 @@
         <v>24</v>
       </c>
       <c r="F765" s="4">
-        <v>259.51052024000001</v>
+        <v>103.80420809600001</v>
       </c>
     </row>
     <row r="766" spans="1:6" x14ac:dyDescent="0.3">
@@ -15802,7 +15802,7 @@
         <v>13</v>
       </c>
       <c r="F766" s="4">
-        <v>-2.4243323399999999</v>
+        <v>-0.96973293599999999</v>
       </c>
     </row>
     <row r="767" spans="1:6" x14ac:dyDescent="0.3">
@@ -15822,7 +15822,7 @@
         <v>14</v>
       </c>
       <c r="F767" s="4">
-        <v>37.829045690000001</v>
+        <v>15.131618276000001</v>
       </c>
     </row>
     <row r="768" spans="1:6" x14ac:dyDescent="0.3">
@@ -15842,7 +15842,7 @@
         <v>24</v>
       </c>
       <c r="F768" s="4">
-        <v>-0.49624332999999998</v>
+        <v>-0.198497332</v>
       </c>
     </row>
     <row r="769" spans="1:6" x14ac:dyDescent="0.3">
@@ -15862,7 +15862,7 @@
         <v>11</v>
       </c>
       <c r="F769" s="4">
-        <v>11.564049109999999</v>
+        <v>4.6256196439999995</v>
       </c>
     </row>
     <row r="770" spans="1:6" x14ac:dyDescent="0.3">
@@ -15902,7 +15902,7 @@
         <v>27</v>
       </c>
       <c r="F771" s="4">
-        <v>3.4925938599999999</v>
+        <v>1.397037544</v>
       </c>
     </row>
     <row r="772" spans="1:6" x14ac:dyDescent="0.3">
@@ -15922,7 +15922,7 @@
         <v>11</v>
       </c>
       <c r="F772" s="4">
-        <v>8.0097135700000006</v>
+        <v>3.2038854280000004</v>
       </c>
     </row>
     <row r="773" spans="1:6" x14ac:dyDescent="0.3">
@@ -15942,7 +15942,7 @@
         <v>23</v>
       </c>
       <c r="F773" s="4">
-        <v>32.466938880000001</v>
+        <v>12.986775552000001</v>
       </c>
     </row>
     <row r="774" spans="1:6" x14ac:dyDescent="0.3">
@@ -15962,7 +15962,7 @@
         <v>15</v>
       </c>
       <c r="F774" s="4">
-        <v>0.57827194000000004</v>
+        <v>0.23130877600000002</v>
       </c>
     </row>
     <row r="775" spans="1:6" x14ac:dyDescent="0.3">
@@ -15982,7 +15982,7 @@
         <v>23</v>
       </c>
       <c r="F775" s="4">
-        <v>16.564967750000001</v>
+        <v>6.6259871000000006</v>
       </c>
     </row>
     <row r="776" spans="1:6" x14ac:dyDescent="0.3">
@@ -16002,7 +16002,7 @@
         <v>11</v>
       </c>
       <c r="F776" s="4">
-        <v>8.2921507200000004</v>
+        <v>3.3168602880000004</v>
       </c>
     </row>
     <row r="777" spans="1:6" x14ac:dyDescent="0.3">
@@ -16022,7 +16022,7 @@
         <v>15</v>
       </c>
       <c r="F777" s="4">
-        <v>2.5232459700000001</v>
+        <v>1.0092983880000002</v>
       </c>
     </row>
     <row r="778" spans="1:6" x14ac:dyDescent="0.3">
@@ -16042,7 +16042,7 @@
         <v>19</v>
       </c>
       <c r="F778" s="4">
-        <v>-6.8833519999999995E-2</v>
+        <v>-2.7533407999999999E-2</v>
       </c>
     </row>
     <row r="779" spans="1:6" x14ac:dyDescent="0.3">
@@ -16082,7 +16082,7 @@
         <v>23</v>
       </c>
       <c r="F780" s="4">
-        <v>35.834332979999999</v>
+        <v>14.333733192</v>
       </c>
     </row>
     <row r="781" spans="1:6" x14ac:dyDescent="0.3">
@@ -16142,7 +16142,7 @@
         <v>23</v>
       </c>
       <c r="F783" s="4">
-        <v>15.27457961</v>
+        <v>6.1098318440000003</v>
       </c>
     </row>
     <row r="784" spans="1:6" x14ac:dyDescent="0.3">
@@ -16162,7 +16162,7 @@
         <v>14</v>
       </c>
       <c r="F784" s="4">
-        <v>36.285697890000002</v>
+        <v>14.514279156000001</v>
       </c>
     </row>
     <row r="785" spans="1:6" x14ac:dyDescent="0.3">
@@ -16182,7 +16182,7 @@
         <v>24</v>
       </c>
       <c r="F785" s="4">
-        <v>-2.7413277900000002</v>
+        <v>-1.0965311160000002</v>
       </c>
     </row>
     <row r="786" spans="1:6" x14ac:dyDescent="0.3">
@@ -16222,7 +16222,7 @@
         <v>8</v>
       </c>
       <c r="F787" s="4">
-        <v>76.858796470000001</v>
+        <v>30.743518588000001</v>
       </c>
     </row>
     <row r="788" spans="1:6" x14ac:dyDescent="0.3">
@@ -16262,7 +16262,7 @@
         <v>21</v>
       </c>
       <c r="F789" s="4">
-        <v>1.4116477599999999</v>
+        <v>0.56465910399999997</v>
       </c>
     </row>
     <row r="790" spans="1:6" x14ac:dyDescent="0.3">
@@ -16282,7 +16282,7 @@
         <v>11</v>
       </c>
       <c r="F790" s="4">
-        <v>17.164722009999998</v>
+        <v>6.8658888039999999</v>
       </c>
     </row>
     <row r="791" spans="1:6" x14ac:dyDescent="0.3">
@@ -16302,7 +16302,7 @@
         <v>15</v>
       </c>
       <c r="F791" s="4">
-        <v>0.40360943999999999</v>
+        <v>0.16144377600000001</v>
       </c>
     </row>
     <row r="792" spans="1:6" x14ac:dyDescent="0.3">
@@ -16322,7 +16322,7 @@
         <v>15</v>
       </c>
       <c r="F792" s="4">
-        <v>2.3527095500000001</v>
+        <v>0.94108382000000013</v>
       </c>
     </row>
     <row r="793" spans="1:6" x14ac:dyDescent="0.3">
@@ -16342,7 +16342,7 @@
         <v>14</v>
       </c>
       <c r="F793" s="4">
-        <v>76.134591920000005</v>
+        <v>30.453836768000002</v>
       </c>
     </row>
     <row r="794" spans="1:6" x14ac:dyDescent="0.3">
@@ -16362,7 +16362,7 @@
         <v>15</v>
       </c>
       <c r="F794" s="4">
-        <v>0.69070398</v>
+        <v>0.27628159200000002</v>
       </c>
     </row>
     <row r="795" spans="1:6" x14ac:dyDescent="0.3">
@@ -16382,7 +16382,7 @@
         <v>23</v>
       </c>
       <c r="F795" s="4">
-        <v>12.6868657</v>
+        <v>5.0747462800000003</v>
       </c>
     </row>
     <row r="796" spans="1:6" x14ac:dyDescent="0.3">
@@ -16402,7 +16402,7 @@
         <v>15</v>
       </c>
       <c r="F796" s="4">
-        <v>0.69830451999999998</v>
+        <v>0.279321808</v>
       </c>
     </row>
     <row r="797" spans="1:6" x14ac:dyDescent="0.3">
@@ -16422,7 +16422,7 @@
         <v>23</v>
       </c>
       <c r="F797" s="4">
-        <v>39.022477510000002</v>
+        <v>15.608991004000002</v>
       </c>
     </row>
     <row r="798" spans="1:6" x14ac:dyDescent="0.3">
@@ -16462,7 +16462,7 @@
         <v>11</v>
       </c>
       <c r="F799" s="4">
-        <v>7.7735143100000004</v>
+        <v>3.1094057240000001</v>
       </c>
     </row>
     <row r="800" spans="1:6" x14ac:dyDescent="0.3">
@@ -16482,7 +16482,7 @@
         <v>14</v>
       </c>
       <c r="F800" s="4">
-        <v>40.895413980000001</v>
+        <v>16.358165592000002</v>
       </c>
     </row>
     <row r="801" spans="1:6" x14ac:dyDescent="0.3">
@@ -16502,7 +16502,7 @@
         <v>24</v>
       </c>
       <c r="F801" s="4">
-        <v>79.007727259999996</v>
+        <v>31.603090903999998</v>
       </c>
     </row>
     <row r="802" spans="1:6" x14ac:dyDescent="0.3">
@@ -16522,7 +16522,7 @@
         <v>18</v>
       </c>
       <c r="F802" s="4">
-        <v>278.55342392</v>
+        <v>111.421369568</v>
       </c>
     </row>
     <row r="803" spans="1:6" x14ac:dyDescent="0.3">
@@ -16542,7 +16542,7 @@
         <v>14</v>
       </c>
       <c r="F803" s="4">
-        <v>37.343307619999997</v>
+        <v>14.937323048</v>
       </c>
     </row>
     <row r="804" spans="1:6" x14ac:dyDescent="0.3">
@@ -16582,11 +16582,12 @@
         <v>23</v>
       </c>
       <c r="F805" s="4">
-        <v>14.93751994</v>
+        <v>5.9750079760000006</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/sample_data1.xlsx
+++ b/data/sample_data1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MALIFE\Documents\Actuarial-Report\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\00.디혁\04.대시보드\3.운영\5.개발\2023.03.13_actuarial Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -522,7 +522,7 @@
         <v>8</v>
       </c>
       <c r="F2" s="4">
-        <v>18.983948844</v>
+        <v>47.459872109999999</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -562,7 +562,7 @@
         <v>13</v>
       </c>
       <c r="F4" s="4">
-        <v>-0.98240273600000005</v>
+        <v>-2.4560068400000001</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -582,7 +582,7 @@
         <v>14</v>
       </c>
       <c r="F5" s="4">
-        <v>16.583121708</v>
+        <v>41.457804269999997</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -602,7 +602,7 @@
         <v>11</v>
       </c>
       <c r="F6" s="4">
-        <v>3.0813232920000004</v>
+        <v>7.7033082300000002</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -622,7 +622,7 @@
         <v>14</v>
       </c>
       <c r="F7" s="4">
-        <v>15.605094520000002</v>
+        <v>39.0127363</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -642,7 +642,7 @@
         <v>15</v>
       </c>
       <c r="F8" s="4">
-        <v>0.96515779599999996</v>
+        <v>2.4128944899999998</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -662,7 +662,7 @@
         <v>13</v>
       </c>
       <c r="F9" s="4">
-        <v>-1.0069064600000002</v>
+        <v>-2.5172661500000002</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -702,7 +702,7 @@
         <v>11</v>
       </c>
       <c r="F11" s="4">
-        <v>4.6556267880000002</v>
+        <v>11.63906697</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -722,7 +722,7 @@
         <v>13</v>
       </c>
       <c r="F12" s="4">
-        <v>-0.57391584000000007</v>
+        <v>-1.4347896</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -742,7 +742,7 @@
         <v>13</v>
       </c>
       <c r="F13" s="4">
-        <v>-0.89859348800000005</v>
+        <v>-2.2464837200000001</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -802,7 +802,7 @@
         <v>8</v>
       </c>
       <c r="F16" s="4">
-        <v>18.88020208</v>
+        <v>47.200505200000002</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -842,7 +842,7 @@
         <v>15</v>
       </c>
       <c r="F18" s="4">
-        <v>0.22236397200000002</v>
+        <v>0.55590993</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -862,7 +862,7 @@
         <v>11</v>
       </c>
       <c r="F19" s="4">
-        <v>4.7096889119999998</v>
+        <v>11.77422228</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -882,7 +882,7 @@
         <v>18</v>
       </c>
       <c r="F20" s="4">
-        <v>18.482211943999999</v>
+        <v>46.205529859999999</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -902,7 +902,7 @@
         <v>19</v>
       </c>
       <c r="F21" s="4">
-        <v>0.18652882800000001</v>
+        <v>0.46632206999999998</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -922,7 +922,7 @@
         <v>15</v>
       </c>
       <c r="F22" s="4">
-        <v>0.226938636</v>
+        <v>0.56734658999999998</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -962,7 +962,7 @@
         <v>20</v>
       </c>
       <c r="F24" s="4">
-        <v>18.189397184000001</v>
+        <v>45.473492960000002</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -982,7 +982,7 @@
         <v>21</v>
       </c>
       <c r="F25" s="4">
-        <v>3.2599693000000003</v>
+        <v>8.1499232500000005</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
@@ -1022,7 +1022,7 @@
         <v>14</v>
       </c>
       <c r="F27" s="4">
-        <v>16.583121708</v>
+        <v>41.457804269999997</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -1042,7 +1042,7 @@
         <v>19</v>
       </c>
       <c r="F28" s="4">
-        <v>-5.2232488000000001E-2</v>
+        <v>-0.13058122</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
@@ -1082,7 +1082,7 @@
         <v>23</v>
       </c>
       <c r="F30" s="4">
-        <v>13.925552828000001</v>
+        <v>34.813882069999998</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
@@ -1122,7 +1122,7 @@
         <v>21</v>
       </c>
       <c r="F32" s="4">
-        <v>0.567325564</v>
+        <v>1.41831391</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
@@ -1142,7 +1142,7 @@
         <v>13</v>
       </c>
       <c r="F33" s="4">
-        <v>7.9526904000000009E-2</v>
+        <v>0.19881726</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -1162,7 +1162,7 @@
         <v>11</v>
       </c>
       <c r="F34" s="4">
-        <v>4.6114257920000004</v>
+        <v>11.52856448</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
@@ -1182,7 +1182,7 @@
         <v>24</v>
       </c>
       <c r="F35" s="4">
-        <v>-0.62021230800000005</v>
+        <v>-1.5505307699999999</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
@@ -1202,7 +1202,7 @@
         <v>11</v>
       </c>
       <c r="F36" s="4">
-        <v>3.2730967680000003</v>
+        <v>8.1827419199999998</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -1222,7 +1222,7 @@
         <v>23</v>
       </c>
       <c r="F37" s="4">
-        <v>14.829423739999999</v>
+        <v>37.073559349999996</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
@@ -1242,7 +1242,7 @@
         <v>21</v>
       </c>
       <c r="F38" s="4">
-        <v>0.52180720800000002</v>
+        <v>1.3045180199999999</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -1262,7 +1262,7 @@
         <v>21</v>
       </c>
       <c r="F39" s="4">
-        <v>3.3227418120000003</v>
+        <v>8.3068545300000007</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
@@ -1282,7 +1282,7 @@
         <v>21</v>
       </c>
       <c r="F40" s="4">
-        <v>0.50238160799999998</v>
+        <v>1.2559540199999999</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -1302,7 +1302,7 @@
         <v>21</v>
       </c>
       <c r="F41" s="4">
-        <v>3.4098768079999999</v>
+        <v>8.5246920199999998</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
@@ -1322,7 +1322,7 @@
         <v>14</v>
       </c>
       <c r="F42" s="4">
-        <v>16.106977232000002</v>
+        <v>40.26744308</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
@@ -1342,7 +1342,7 @@
         <v>24</v>
       </c>
       <c r="F43" s="4">
-        <v>-7.619409664</v>
+        <v>-19.048524159999999</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -1362,7 +1362,7 @@
         <v>15</v>
       </c>
       <c r="F44" s="4">
-        <v>0.27445993600000002</v>
+        <v>0.68614984000000001</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -1382,7 +1382,7 @@
         <v>15</v>
       </c>
       <c r="F45" s="4">
-        <v>0.135077948</v>
+        <v>0.33769486999999998</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -1402,7 +1402,7 @@
         <v>21</v>
       </c>
       <c r="F46" s="4">
-        <v>0.62960024800000003</v>
+        <v>1.5740006200000001</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -1442,7 +1442,7 @@
         <v>26</v>
       </c>
       <c r="F48" s="4">
-        <v>16.882406024000002</v>
+        <v>42.206015059999999</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
@@ -1462,7 +1462,7 @@
         <v>21</v>
       </c>
       <c r="F49" s="4">
-        <v>3.7557602920000002</v>
+        <v>9.3894007300000002</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
@@ -1482,7 +1482,7 @@
         <v>14</v>
       </c>
       <c r="F50" s="4">
-        <v>22.814477148000002</v>
+        <v>57.036192870000001</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
@@ -1522,7 +1522,7 @@
         <v>21</v>
       </c>
       <c r="F52" s="4">
-        <v>0.54544207599999994</v>
+        <v>1.3636051899999999</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
@@ -1542,7 +1542,7 @@
         <v>13</v>
       </c>
       <c r="F53" s="4">
-        <v>-1.02393442</v>
+        <v>-2.5598360499999999</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
@@ -1562,7 +1562,7 @@
         <v>14</v>
       </c>
       <c r="F54" s="4">
-        <v>30.757476816000004</v>
+        <v>76.893692040000005</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
@@ -1582,7 +1582,7 @@
         <v>27</v>
       </c>
       <c r="F55" s="4">
-        <v>0.23234676799999998</v>
+        <v>0.58086691999999995</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
@@ -1622,7 +1622,7 @@
         <v>21</v>
       </c>
       <c r="F57" s="4">
-        <v>3.2419999120000003</v>
+        <v>8.10499978</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
@@ -1642,7 +1642,7 @@
         <v>19</v>
       </c>
       <c r="F58" s="4">
-        <v>-6.4571760000000006E-2</v>
+        <v>-0.1614294</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
@@ -1662,7 +1662,7 @@
         <v>27</v>
       </c>
       <c r="F59" s="4">
-        <v>1.6505894320000001</v>
+        <v>4.1264735799999999</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
@@ -1682,7 +1682,7 @@
         <v>19</v>
       </c>
       <c r="F60" s="4">
-        <v>-5.5736400000000008E-4</v>
+        <v>-1.3934100000000001E-3</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
@@ -1702,7 +1702,7 @@
         <v>13</v>
       </c>
       <c r="F61" s="4">
-        <v>-0.83518093199999999</v>
+        <v>-2.0879523299999998</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
@@ -1722,7 +1722,7 @@
         <v>8</v>
       </c>
       <c r="F62" s="4">
-        <v>18.697415595999999</v>
+        <v>46.743538989999998</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
@@ -1742,7 +1742,7 @@
         <v>8</v>
       </c>
       <c r="F63" s="4">
-        <v>22.264294464000002</v>
+        <v>55.660736159999999</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
@@ -1762,7 +1762,7 @@
         <v>24</v>
       </c>
       <c r="F64" s="4">
-        <v>6.3007957000000001</v>
+        <v>15.751989249999999</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
@@ -1782,7 +1782,7 @@
         <v>13</v>
       </c>
       <c r="F65" s="4">
-        <v>0.68430051200000008</v>
+        <v>1.71075128</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
@@ -1802,7 +1802,7 @@
         <v>18</v>
       </c>
       <c r="F66" s="4">
-        <v>18.324954872000003</v>
+        <v>45.812387180000002</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
@@ -1822,7 +1822,7 @@
         <v>23</v>
       </c>
       <c r="F67" s="4">
-        <v>6.2460615520000005</v>
+        <v>15.615153879999999</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
@@ -1842,7 +1842,7 @@
         <v>20</v>
       </c>
       <c r="F68" s="4">
-        <v>122.914911496</v>
+        <v>307.28727873999998</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
@@ -1862,7 +1862,7 @@
         <v>18</v>
       </c>
       <c r="F69" s="4">
-        <v>33.643241635999999</v>
+        <v>84.108104089999998</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
@@ -1882,7 +1882,7 @@
         <v>13</v>
       </c>
       <c r="F70" s="4">
-        <v>-0.93481371200000007</v>
+        <v>-2.3370342800000001</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
@@ -1902,7 +1902,7 @@
         <v>8</v>
       </c>
       <c r="F71" s="4">
-        <v>18.050536068</v>
+        <v>45.126340169999999</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
@@ -1922,7 +1922,7 @@
         <v>21</v>
       </c>
       <c r="F72" s="4">
-        <v>0.55180365200000003</v>
+        <v>1.37950913</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
@@ -1942,7 +1942,7 @@
         <v>19</v>
       </c>
       <c r="F73" s="4">
-        <v>-3.6513408000000004E-2</v>
+        <v>-9.1283520000000007E-2</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
@@ -1962,7 +1962,7 @@
         <v>13</v>
       </c>
       <c r="F74" s="4">
-        <v>-0.84897371600000016</v>
+        <v>-2.1224342900000002</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
@@ -1982,7 +1982,7 @@
         <v>11</v>
       </c>
       <c r="F75" s="4">
-        <v>3.1347637760000002</v>
+        <v>7.8369094400000003</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
@@ -2002,7 +2002,7 @@
         <v>23</v>
       </c>
       <c r="F76" s="4">
-        <v>6.254856740000001</v>
+        <v>15.637141850000001</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
@@ -2042,7 +2042,7 @@
         <v>21</v>
       </c>
       <c r="F78" s="4">
-        <v>0.95236753600000013</v>
+        <v>2.3809188400000001</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
@@ -2062,7 +2062,7 @@
         <v>23</v>
       </c>
       <c r="F79" s="4">
-        <v>6.315140596</v>
+        <v>15.78785149</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
@@ -2082,7 +2082,7 @@
         <v>11</v>
       </c>
       <c r="F80" s="4">
-        <v>3.1916031880000002</v>
+        <v>7.9790079699999996</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
@@ -2162,7 +2162,7 @@
         <v>20</v>
       </c>
       <c r="F84" s="4">
-        <v>41.190732536000006</v>
+        <v>102.97683134</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
@@ -2202,7 +2202,7 @@
         <v>27</v>
       </c>
       <c r="F86" s="4">
-        <v>0.54720019200000003</v>
+        <v>1.3680004800000001</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
@@ -2222,7 +2222,7 @@
         <v>23</v>
       </c>
       <c r="F87" s="4">
-        <v>14.545413864</v>
+        <v>36.363534659999999</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
@@ -2242,7 +2242,7 @@
         <v>23</v>
       </c>
       <c r="F88" s="4">
-        <v>14.970894812000001</v>
+        <v>37.427237030000001</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
@@ -2262,7 +2262,7 @@
         <v>14</v>
       </c>
       <c r="F89" s="4">
-        <v>29.186625624000001</v>
+        <v>72.966564059999996</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
@@ -2302,7 +2302,7 @@
         <v>13</v>
       </c>
       <c r="F91" s="4">
-        <v>-3.9028620000000007E-2</v>
+        <v>-9.7571550000000007E-2</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
@@ -2322,7 +2322,7 @@
         <v>27</v>
       </c>
       <c r="F92" s="4">
-        <v>9.7596772600000001</v>
+        <v>24.399193149999999</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
@@ -2342,7 +2342,7 @@
         <v>13</v>
       </c>
       <c r="F93" s="4">
-        <v>-0.93481371200000007</v>
+        <v>-2.3370342800000001</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
@@ -2362,7 +2362,7 @@
         <v>14</v>
       </c>
       <c r="F94" s="4">
-        <v>36.312628172000004</v>
+        <v>90.781570430000002</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
@@ -2382,7 +2382,7 @@
         <v>23</v>
       </c>
       <c r="F95" s="4">
-        <v>12.736743532</v>
+        <v>31.84185883</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
@@ -2402,7 +2402,7 @@
         <v>23</v>
       </c>
       <c r="F96" s="4">
-        <v>5.067235116</v>
+        <v>12.66808779</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
@@ -2422,7 +2422,7 @@
         <v>13</v>
       </c>
       <c r="F97" s="4">
-        <v>-0.26187136799999999</v>
+        <v>-0.65467841999999998</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
@@ -2462,7 +2462,7 @@
         <v>8</v>
       </c>
       <c r="F99" s="4">
-        <v>31.743438312000002</v>
+        <v>79.358595780000002</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
@@ -2482,7 +2482,7 @@
         <v>13</v>
       </c>
       <c r="F100" s="4">
-        <v>-1.0069064600000002</v>
+        <v>-2.5172661500000002</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
@@ -2522,7 +2522,7 @@
         <v>13</v>
       </c>
       <c r="F102" s="4">
-        <v>-0.29878964000000002</v>
+        <v>-0.74697409999999997</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
@@ -2562,7 +2562,7 @@
         <v>8</v>
       </c>
       <c r="F104" s="4">
-        <v>33.878820316000002</v>
+        <v>84.697050790000006</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
@@ -2582,7 +2582,7 @@
         <v>23</v>
       </c>
       <c r="F105" s="4">
-        <v>6.3781643639999999</v>
+        <v>15.94541091</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
@@ -2602,7 +2602,7 @@
         <v>23</v>
       </c>
       <c r="F106" s="4">
-        <v>6.3897312280000005</v>
+        <v>15.97432807</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
@@ -2622,7 +2622,7 @@
         <v>23</v>
       </c>
       <c r="F107" s="4">
-        <v>14.208407059999999</v>
+        <v>35.521017649999997</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
@@ -2642,7 +2642,7 @@
         <v>11</v>
       </c>
       <c r="F108" s="4">
-        <v>7.4924892040000008</v>
+        <v>18.731223010000001</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
@@ -2682,7 +2682,7 @@
         <v>11</v>
       </c>
       <c r="F110" s="4">
-        <v>3.119974096</v>
+        <v>7.7999352399999999</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
@@ -2702,7 +2702,7 @@
         <v>14</v>
       </c>
       <c r="F111" s="4">
-        <v>32.597477208000001</v>
+        <v>81.493693019999995</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
@@ -2722,7 +2722,7 @@
         <v>14</v>
       </c>
       <c r="F112" s="4">
-        <v>27.011482216000005</v>
+        <v>67.528705540000004</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
@@ -2742,7 +2742,7 @@
         <v>20</v>
       </c>
       <c r="F113" s="4">
-        <v>125.41866671600002</v>
+        <v>313.54666679000002</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
@@ -2782,7 +2782,7 @@
         <v>14</v>
       </c>
       <c r="F115" s="4">
-        <v>30.528294391999999</v>
+        <v>76.320735979999995</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
@@ -2802,7 +2802,7 @@
         <v>15</v>
       </c>
       <c r="F116" s="4">
-        <v>0.9815578800000001</v>
+        <v>2.4538947000000002</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
@@ -2822,7 +2822,7 @@
         <v>13</v>
       </c>
       <c r="F117" s="4">
-        <v>-0.12010032799999999</v>
+        <v>-0.30025081999999997</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
@@ -2842,7 +2842,7 @@
         <v>14</v>
       </c>
       <c r="F118" s="4">
-        <v>32.597477208000001</v>
+        <v>81.493693019999995</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
@@ -2862,7 +2862,7 @@
         <v>14</v>
       </c>
       <c r="F119" s="4">
-        <v>25.331356172</v>
+        <v>63.328390429999999</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
@@ -2882,7 +2882,7 @@
         <v>24</v>
       </c>
       <c r="F120" s="4">
-        <v>0.58855682399999998</v>
+        <v>1.4713920599999999</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
@@ -2922,7 +2922,7 @@
         <v>18</v>
       </c>
       <c r="F122" s="4">
-        <v>114.59135192799999</v>
+        <v>286.47837981999999</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
@@ -2942,7 +2942,7 @@
         <v>26</v>
       </c>
       <c r="F123" s="4">
-        <v>29.189486520000003</v>
+        <v>72.973716300000007</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
@@ -2962,7 +2962,7 @@
         <v>21</v>
       </c>
       <c r="F124" s="4">
-        <v>0.63745102400000009</v>
+        <v>1.5936275600000001</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
@@ -2982,7 +2982,7 @@
         <v>15</v>
       </c>
       <c r="F125" s="4">
-        <v>0.22328722400000001</v>
+        <v>0.55821805999999996</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
@@ -3002,7 +3002,7 @@
         <v>24</v>
       </c>
       <c r="F126" s="4">
-        <v>-7.6138626480000005</v>
+        <v>-19.03465662</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
@@ -3042,7 +3042,7 @@
         <v>24</v>
       </c>
       <c r="F128" s="4">
-        <v>13.147468348000002</v>
+        <v>32.868670870000003</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
@@ -3062,7 +3062,7 @@
         <v>21</v>
       </c>
       <c r="F129" s="4">
-        <v>0.64253001600000004</v>
+        <v>1.60632504</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
@@ -3102,7 +3102,7 @@
         <v>8</v>
       </c>
       <c r="F131" s="4">
-        <v>18.930218252</v>
+        <v>47.325545630000001</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
@@ -3142,7 +3142,7 @@
         <v>13</v>
       </c>
       <c r="F133" s="4">
-        <v>-0.93361642000000011</v>
+        <v>-2.3340410500000002</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
@@ -3182,7 +3182,7 @@
         <v>23</v>
       </c>
       <c r="F135" s="4">
-        <v>6.3843427159999999</v>
+        <v>15.960856789999999</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
@@ -3202,7 +3202,7 @@
         <v>19</v>
       </c>
       <c r="F136" s="4">
-        <v>-2.6833627999999998E-2</v>
+        <v>-6.7084069999999996E-2</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
@@ -3242,7 +3242,7 @@
         <v>23</v>
       </c>
       <c r="F138" s="4">
-        <v>14.600993616</v>
+        <v>36.502484039999999</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
@@ -3262,7 +3262,7 @@
         <v>19</v>
       </c>
       <c r="F139" s="4">
-        <v>2.3652472000000001E-2</v>
+        <v>5.9131179999999998E-2</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
@@ -3282,7 +3282,7 @@
         <v>27</v>
       </c>
       <c r="F140" s="4">
-        <v>0.83902590799999999</v>
+        <v>2.09756477</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
@@ -3302,7 +3302,7 @@
         <v>20</v>
       </c>
       <c r="F141" s="4">
-        <v>14.234925656</v>
+        <v>35.587314139999997</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
@@ -3322,7 +3322,7 @@
         <v>20</v>
       </c>
       <c r="F142" s="4">
-        <v>33.195215296000001</v>
+        <v>82.988038239999995</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
@@ -3342,7 +3342,7 @@
         <v>13</v>
       </c>
       <c r="F143" s="4">
-        <v>-0.26391484400000004</v>
+        <v>-0.65978711000000001</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
@@ -3362,7 +3362,7 @@
         <v>21</v>
       </c>
       <c r="F144" s="4">
-        <v>0.53071961600000006</v>
+        <v>1.32679904</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
@@ -3382,7 +3382,7 @@
         <v>11</v>
       </c>
       <c r="F145" s="4">
-        <v>3.1791610000000001</v>
+        <v>7.9479024999999996</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
@@ -3402,7 +3402,7 @@
         <v>21</v>
       </c>
       <c r="F146" s="4">
-        <v>0.37775136800000003</v>
+        <v>0.94437842000000005</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
@@ -3442,7 +3442,7 @@
         <v>20</v>
       </c>
       <c r="F148" s="4">
-        <v>32.465744036000004</v>
+        <v>81.164360090000002</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
@@ -3462,7 +3462,7 @@
         <v>27</v>
       </c>
       <c r="F149" s="4">
-        <v>2.5329009039999999</v>
+        <v>6.3322522599999997</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
@@ -3502,7 +3502,7 @@
         <v>11</v>
       </c>
       <c r="F151" s="4">
-        <v>4.5704134000000005</v>
+        <v>11.426033500000001</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
@@ -3522,7 +3522,7 @@
         <v>14</v>
       </c>
       <c r="F152" s="4">
-        <v>28.454063739999999</v>
+        <v>71.135159349999995</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.3">
@@ -3542,7 +3542,7 @@
         <v>21</v>
       </c>
       <c r="F153" s="4">
-        <v>3.325481452</v>
+        <v>8.3137036299999991</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.3">
@@ -3562,7 +3562,7 @@
         <v>24</v>
       </c>
       <c r="F154" s="4">
-        <v>9.1667432760000001</v>
+        <v>22.916858189999999</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.3">
@@ -3582,7 +3582,7 @@
         <v>14</v>
       </c>
       <c r="F155" s="4">
-        <v>14.303051864</v>
+        <v>35.757629659999999</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.3">
@@ -3602,7 +3602,7 @@
         <v>15</v>
       </c>
       <c r="F156" s="4">
-        <v>0.25766709200000004</v>
+        <v>0.64416773000000005</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.3">
@@ -3622,7 +3622,7 @@
         <v>13</v>
       </c>
       <c r="F157" s="4">
-        <v>0.12255477200000001</v>
+        <v>0.30638693</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.3">
@@ -3642,7 +3642,7 @@
         <v>19</v>
       </c>
       <c r="F158" s="4">
-        <v>-1.7455892000000001E-2</v>
+        <v>-4.3639730000000002E-2</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.3">
@@ -3662,7 +3662,7 @@
         <v>19</v>
       </c>
       <c r="F159" s="4">
-        <v>-0.110040948</v>
+        <v>-0.27510236999999998</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.3">
@@ -3702,7 +3702,7 @@
         <v>13</v>
       </c>
       <c r="F161" s="4">
-        <v>-0.22535959600000002</v>
+        <v>-0.56339899000000004</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.3">
@@ -3742,7 +3742,7 @@
         <v>21</v>
       </c>
       <c r="F163" s="4">
-        <v>0.56062157199999996</v>
+        <v>1.4015539299999999</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.3">
@@ -3762,7 +3762,7 @@
         <v>15</v>
       </c>
       <c r="F164" s="4">
-        <v>1.0850523320000001</v>
+        <v>2.7126308300000002</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.3">
@@ -3782,7 +3782,7 @@
         <v>13</v>
       </c>
       <c r="F165" s="4">
-        <v>-0.28215344000000003</v>
+        <v>-0.7053836</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.3">
@@ -3802,7 +3802,7 @@
         <v>26</v>
       </c>
       <c r="F166" s="4">
-        <v>18.662814239999999</v>
+        <v>46.6570356</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.3">
@@ -3842,7 +3842,7 @@
         <v>14</v>
       </c>
       <c r="F168" s="4">
-        <v>30.528294391999999</v>
+        <v>76.320735979999995</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.3">
@@ -3862,7 +3862,7 @@
         <v>11</v>
       </c>
       <c r="F169" s="4">
-        <v>3.142476228</v>
+        <v>7.8561905699999999</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.3">
@@ -3882,7 +3882,7 @@
         <v>15</v>
       </c>
       <c r="F170" s="4">
-        <v>0.13809505600000002</v>
+        <v>0.34523764000000001</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.3">
@@ -3942,7 +3942,7 @@
         <v>21</v>
       </c>
       <c r="F173" s="4">
-        <v>0.51209107200000004</v>
+        <v>1.2802276800000001</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.3">
@@ -3982,7 +3982,7 @@
         <v>18</v>
       </c>
       <c r="F175" s="4">
-        <v>30.841968187999999</v>
+        <v>77.104920469999996</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.3">
@@ -4002,7 +4002,7 @@
         <v>14</v>
       </c>
       <c r="F176" s="4">
-        <v>30.422739116000002</v>
+        <v>76.056847790000006</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.3">
@@ -4022,7 +4022,7 @@
         <v>15</v>
       </c>
       <c r="F177" s="4">
-        <v>0.23139043199999998</v>
+        <v>0.57847607999999995</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.3">
@@ -4042,7 +4042,7 @@
         <v>23</v>
       </c>
       <c r="F178" s="4">
-        <v>15.436865280000001</v>
+        <v>38.592163200000002</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.3">
@@ -4102,7 +4102,7 @@
         <v>19</v>
       </c>
       <c r="F181" s="4">
-        <v>-0.22613530000000004</v>
+        <v>-0.56533825000000004</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.3">
@@ -4122,7 +4122,7 @@
         <v>18</v>
       </c>
       <c r="F182" s="4">
-        <v>119.049728096</v>
+        <v>297.62432023999997</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.3">
@@ -4142,7 +4142,7 @@
         <v>15</v>
       </c>
       <c r="F183" s="4">
-        <v>0.99249623200000014</v>
+        <v>2.4812405800000001</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.3">
@@ -4162,7 +4162,7 @@
         <v>23</v>
       </c>
       <c r="F184" s="4">
-        <v>6.736046408</v>
+        <v>16.84011602</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.3">
@@ -4182,7 +4182,7 @@
         <v>18</v>
       </c>
       <c r="F185" s="4">
-        <v>103.02408320400001</v>
+        <v>257.56020801</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.3">
@@ -4202,7 +4202,7 @@
         <v>13</v>
       </c>
       <c r="F186" s="4">
-        <v>-0.24842334400000002</v>
+        <v>-0.62105836000000003</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.3">
@@ -4222,7 +4222,7 @@
         <v>26</v>
       </c>
       <c r="F187" s="4">
-        <v>26.579079284000002</v>
+        <v>66.447698209999999</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.3">
@@ -4282,7 +4282,7 @@
         <v>21</v>
       </c>
       <c r="F190" s="4">
-        <v>0.63528135600000013</v>
+        <v>1.5882033900000001</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.3">
@@ -4302,7 +4302,7 @@
         <v>11</v>
       </c>
       <c r="F191" s="4">
-        <v>6.5204347040000004</v>
+        <v>16.30108676</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.3">
@@ -4322,7 +4322,7 @@
         <v>13</v>
       </c>
       <c r="F192" s="4">
-        <v>-0.23131691200000001</v>
+        <v>-0.57829227999999999</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.3">
@@ -4342,7 +4342,7 @@
         <v>23</v>
       </c>
       <c r="F193" s="4">
-        <v>6.4568716080000002</v>
+        <v>16.14217902</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.3">
@@ -4362,7 +4362,7 @@
         <v>19</v>
       </c>
       <c r="F194" s="4">
-        <v>-0.84331843600000012</v>
+        <v>-2.1082960900000001</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.3">
@@ -4382,7 +4382,7 @@
         <v>23</v>
       </c>
       <c r="F195" s="4">
-        <v>6.4144484559999997</v>
+        <v>16.036121139999999</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.3">
@@ -4402,7 +4402,7 @@
         <v>15</v>
       </c>
       <c r="F196" s="4">
-        <v>0.27599144000000003</v>
+        <v>0.6899786</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.3">
@@ -4422,7 +4422,7 @@
         <v>21</v>
       </c>
       <c r="F197" s="4">
-        <v>3.4041134999999998</v>
+        <v>8.5102837499999993</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.3">
@@ -4442,7 +4442,7 @@
         <v>14</v>
       </c>
       <c r="F198" s="4">
-        <v>29.186625624000001</v>
+        <v>72.966564059999996</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.3">
@@ -4462,7 +4462,7 @@
         <v>15</v>
       </c>
       <c r="F199" s="4">
-        <v>0.23028575200000001</v>
+        <v>0.57571437999999997</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.3">
@@ -4482,7 +4482,7 @@
         <v>15</v>
       </c>
       <c r="F200" s="4">
-        <v>0.253909512</v>
+        <v>0.63477377999999995</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.3">
@@ -4502,7 +4502,7 @@
         <v>15</v>
       </c>
       <c r="F201" s="4">
-        <v>0.24031684800000003</v>
+        <v>0.60079212000000004</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.3">
@@ -4522,7 +4522,7 @@
         <v>21</v>
       </c>
       <c r="F202" s="4">
-        <v>0.51610682800000007</v>
+        <v>1.2902670700000001</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.3">
@@ -4542,7 +4542,7 @@
         <v>11</v>
       </c>
       <c r="F203" s="4">
-        <v>6.9419558839999995</v>
+        <v>17.354889709999998</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.3">
@@ -4562,7 +4562,7 @@
         <v>27</v>
       </c>
       <c r="F204" s="4">
-        <v>-2.1808592000000002E-2</v>
+        <v>-5.4521479999999997E-2</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.3">
@@ -4582,7 +4582,7 @@
         <v>21</v>
       </c>
       <c r="F205" s="4">
-        <v>3.8032165120000005</v>
+        <v>9.5080412800000005</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.3">
@@ -4602,7 +4602,7 @@
         <v>13</v>
       </c>
       <c r="F206" s="4">
-        <v>-0.26544453600000001</v>
+        <v>-0.66361133999999999</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.3">
@@ -4642,7 +4642,7 @@
         <v>23</v>
       </c>
       <c r="F208" s="4">
-        <v>14.209615736000002</v>
+        <v>35.524039340000002</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.3">
@@ -4682,7 +4682,7 @@
         <v>23</v>
       </c>
       <c r="F210" s="4">
-        <v>3.4918877080000001</v>
+        <v>8.7297192700000004</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.3">
@@ -4722,7 +4722,7 @@
         <v>14</v>
       </c>
       <c r="F212" s="4">
-        <v>24.741930556</v>
+        <v>61.854826389999999</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.3">
@@ -4742,7 +4742,7 @@
         <v>8</v>
       </c>
       <c r="F213" s="4">
-        <v>18.437814832000001</v>
+        <v>46.094537080000002</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.3">
@@ -4802,7 +4802,7 @@
         <v>15</v>
       </c>
       <c r="F216" s="4">
-        <v>1.1619752200000002</v>
+        <v>2.9049380500000002</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.3">
@@ -4822,7 +4822,7 @@
         <v>11</v>
       </c>
       <c r="F217" s="4">
-        <v>6.6288444640000002</v>
+        <v>16.572111159999999</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.3">
@@ -4842,7 +4842,7 @@
         <v>13</v>
       </c>
       <c r="F218" s="4">
-        <v>-4.5045072000000005E-2</v>
+        <v>-0.11261268000000001</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.3">
@@ -4862,7 +4862,7 @@
         <v>24</v>
       </c>
       <c r="F219" s="4">
-        <v>12.624505272</v>
+        <v>31.561263180000001</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.3">
@@ -4902,7 +4902,7 @@
         <v>15</v>
       </c>
       <c r="F221" s="4">
-        <v>0.22571085200000002</v>
+        <v>0.56427713000000002</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.3">
@@ -4922,7 +4922,7 @@
         <v>8</v>
       </c>
       <c r="F222" s="4">
-        <v>21.768448364000001</v>
+        <v>54.421120909999999</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.3">
@@ -4942,7 +4942,7 @@
         <v>8</v>
       </c>
       <c r="F223" s="4">
-        <v>22.646185248000002</v>
+        <v>56.615463120000001</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.3">
@@ -4962,7 +4962,7 @@
         <v>21</v>
       </c>
       <c r="F224" s="4">
-        <v>0.841258952</v>
+        <v>2.1031473799999998</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.3">
@@ -5002,7 +5002,7 @@
         <v>15</v>
       </c>
       <c r="F226" s="4">
-        <v>0.22592024400000002</v>
+        <v>0.56480061000000004</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.3">
@@ -5022,7 +5022,7 @@
         <v>23</v>
       </c>
       <c r="F227" s="4">
-        <v>6.1524388280000002</v>
+        <v>15.381097069999999</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.3">
@@ -5042,7 +5042,7 @@
         <v>21</v>
       </c>
       <c r="F228" s="4">
-        <v>3.7646581880000003</v>
+        <v>9.4116454699999998</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.3">
@@ -5062,7 +5062,7 @@
         <v>23</v>
       </c>
       <c r="F229" s="4">
-        <v>9.6432102880000006</v>
+        <v>24.108025720000001</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.3">
@@ -5082,7 +5082,7 @@
         <v>15</v>
       </c>
       <c r="F230" s="4">
-        <v>0.28048250400000002</v>
+        <v>0.70120625999999997</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.3">
@@ -5122,7 +5122,7 @@
         <v>14</v>
       </c>
       <c r="F232" s="4">
-        <v>26.170820636000002</v>
+        <v>65.427051590000005</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.3">
@@ -5142,7 +5142,7 @@
         <v>19</v>
       </c>
       <c r="F233" s="4">
-        <v>-5.8876128000000007E-2</v>
+        <v>-0.14719032000000001</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.3">
@@ -5162,7 +5162,7 @@
         <v>21</v>
       </c>
       <c r="F234" s="4">
-        <v>0.63953542399999996</v>
+        <v>1.5988385599999999</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.3">
@@ -5182,7 +5182,7 @@
         <v>14</v>
       </c>
       <c r="F235" s="4">
-        <v>14.733198196000002</v>
+        <v>36.832995490000002</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.3">
@@ -5222,7 +5222,7 @@
         <v>14</v>
       </c>
       <c r="F237" s="4">
-        <v>14.733198196000002</v>
+        <v>36.832995490000002</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.3">
@@ -5242,7 +5242,7 @@
         <v>21</v>
       </c>
       <c r="F238" s="4">
-        <v>0.46768510000000002</v>
+        <v>1.16921275</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.3">
@@ -5262,7 +5262,7 @@
         <v>27</v>
       </c>
       <c r="F239" s="4">
-        <v>1.5878532480000001</v>
+        <v>3.9696331200000001</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.3">
@@ -5282,7 +5282,7 @@
         <v>13</v>
       </c>
       <c r="F240" s="4">
-        <v>-0.24842334400000002</v>
+        <v>-0.62105836000000003</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.3">
@@ -5302,7 +5302,7 @@
         <v>21</v>
       </c>
       <c r="F241" s="4">
-        <v>0.55036080399999998</v>
+        <v>1.3759020099999999</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.3">
@@ -5322,7 +5322,7 @@
         <v>14</v>
       </c>
       <c r="F242" s="4">
-        <v>15.872561511999999</v>
+        <v>39.681403779999997</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.3">
@@ -5342,7 +5342,7 @@
         <v>13</v>
       </c>
       <c r="F243" s="4">
-        <v>-0.248896016</v>
+        <v>-0.62224003999999999</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.3">
@@ -5362,7 +5362,7 @@
         <v>20</v>
       </c>
       <c r="F244" s="4">
-        <v>130.139650012</v>
+        <v>325.34912502999998</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.3">
@@ -5422,7 +5422,7 @@
         <v>23</v>
       </c>
       <c r="F247" s="4">
-        <v>13.435882784</v>
+        <v>33.589706960000001</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.3">
@@ -5442,7 +5442,7 @@
         <v>18</v>
       </c>
       <c r="F248" s="4">
-        <v>34.440204512000001</v>
+        <v>86.100511280000006</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.3">
@@ -5462,7 +5462,7 @@
         <v>19</v>
       </c>
       <c r="F249" s="4">
-        <v>-3.1198508000000003E-2</v>
+        <v>-7.7996270000000006E-2</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.3">
@@ -5482,7 +5482,7 @@
         <v>21</v>
       </c>
       <c r="F250" s="4">
-        <v>3.6244383520000003</v>
+        <v>9.0610958799999999</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.3">
@@ -5502,7 +5502,7 @@
         <v>15</v>
       </c>
       <c r="F251" s="4">
-        <v>0.92088969600000015</v>
+        <v>2.3022242400000001</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.3">
@@ -5522,7 +5522,7 @@
         <v>19</v>
       </c>
       <c r="F252" s="4">
-        <v>1.2025292E-2</v>
+        <v>3.006323E-2</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.3">
@@ -5542,7 +5542,7 @@
         <v>21</v>
       </c>
       <c r="F253" s="4">
-        <v>3.5076117400000002</v>
+        <v>8.7690293500000003</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.3">
@@ -5582,7 +5582,7 @@
         <v>14</v>
       </c>
       <c r="F255" s="4">
-        <v>30.122786567999999</v>
+        <v>75.306966419999995</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.3">
@@ -5602,7 +5602,7 @@
         <v>15</v>
       </c>
       <c r="F256" s="4">
-        <v>0.27566444400000001</v>
+        <v>0.68916111000000002</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.3">
@@ -5622,7 +5622,7 @@
         <v>24</v>
       </c>
       <c r="F257" s="4">
-        <v>8.7400052319999997</v>
+        <v>21.85001308</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.3">
@@ -5662,7 +5662,7 @@
         <v>13</v>
       </c>
       <c r="F259" s="4">
-        <v>-0.96973293599999999</v>
+        <v>-2.4243323399999999</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.3">
@@ -5682,7 +5682,7 @@
         <v>23</v>
       </c>
       <c r="F260" s="4">
-        <v>6.9303177840000005</v>
+        <v>17.325794460000001</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.3">
@@ -5702,7 +5702,7 @@
         <v>21</v>
       </c>
       <c r="F261" s="4">
-        <v>0.48770241199999997</v>
+        <v>1.2192560299999999</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.3">
@@ -5722,7 +5722,7 @@
         <v>13</v>
       </c>
       <c r="F262" s="4">
-        <v>-3.9028620000000007E-2</v>
+        <v>-9.7571550000000007E-2</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.3">
@@ -5742,7 +5742,7 @@
         <v>13</v>
       </c>
       <c r="F263" s="4">
-        <v>-0.84897371600000016</v>
+        <v>-2.1224342900000002</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.3">
@@ -5762,7 +5762,7 @@
         <v>14</v>
       </c>
       <c r="F264" s="4">
-        <v>16.336701196000003</v>
+        <v>40.841752990000003</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.3">
@@ -5782,7 +5782,7 @@
         <v>23</v>
       </c>
       <c r="F265" s="4">
-        <v>3.6070977319999997</v>
+        <v>9.0177443299999993</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.3">
@@ -5822,7 +5822,7 @@
         <v>18</v>
       </c>
       <c r="F267" s="4">
-        <v>101.984280824</v>
+        <v>254.96070205999999</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.3">
@@ -5842,7 +5842,7 @@
         <v>23</v>
       </c>
       <c r="F268" s="4">
-        <v>6.3556256920000003</v>
+        <v>15.889064230000001</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.3">
@@ -5862,7 +5862,7 @@
         <v>18</v>
       </c>
       <c r="F269" s="4">
-        <v>104.481574808</v>
+        <v>261.20393702000001</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.3">
@@ -5902,7 +5902,7 @@
         <v>19</v>
       </c>
       <c r="F271" s="4">
-        <v>-4.0017960000000002E-3</v>
+        <v>-1.000449E-2</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.3">
@@ -5922,7 +5922,7 @@
         <v>13</v>
       </c>
       <c r="F272" s="4">
-        <v>-0.98240273600000005</v>
+        <v>-2.4560068400000001</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.3">
@@ -5942,7 +5942,7 @@
         <v>15</v>
       </c>
       <c r="F273" s="4">
-        <v>0.25244178</v>
+        <v>0.63110445000000004</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.3">
@@ -5962,7 +5962,7 @@
         <v>14</v>
       </c>
       <c r="F274" s="4">
-        <v>31.024573623999999</v>
+        <v>77.561434059999996</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.3">
@@ -5982,7 +5982,7 @@
         <v>14</v>
       </c>
       <c r="F275" s="4">
-        <v>27.869209136000002</v>
+        <v>69.673022840000002</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.3">
@@ -6002,7 +6002,7 @@
         <v>23</v>
       </c>
       <c r="F276" s="4">
-        <v>7.7741057920000003</v>
+        <v>19.435264480000001</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.3">
@@ -6022,7 +6022,7 @@
         <v>20</v>
       </c>
       <c r="F277" s="4">
-        <v>18.474579259999999</v>
+        <v>46.186448149999997</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.3">
@@ -6082,7 +6082,7 @@
         <v>15</v>
       </c>
       <c r="F280" s="4">
-        <v>0.14451775600000002</v>
+        <v>0.36129439000000002</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.3">
@@ -6102,7 +6102,7 @@
         <v>24</v>
       </c>
       <c r="F281" s="4">
-        <v>0.76724835200000008</v>
+        <v>1.91812088</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.3">
@@ -6122,7 +6122,7 @@
         <v>27</v>
       </c>
       <c r="F282" s="4">
-        <v>5.553210988</v>
+        <v>13.88302747</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.3">
@@ -6142,7 +6142,7 @@
         <v>20</v>
       </c>
       <c r="F283" s="4">
-        <v>37.048821060000002</v>
+        <v>92.622052650000001</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.3">
@@ -6162,7 +6162,7 @@
         <v>27</v>
       </c>
       <c r="F284" s="4">
-        <v>3.9747384760000006</v>
+        <v>9.9368461900000007</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.3">
@@ -6182,7 +6182,7 @@
         <v>15</v>
       </c>
       <c r="F285" s="4">
-        <v>0.15187051200000001</v>
+        <v>0.37967627999999998</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.3">
@@ -6202,7 +6202,7 @@
         <v>19</v>
       </c>
       <c r="F286" s="4">
-        <v>-5.8415728E-2</v>
+        <v>-0.14603932</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.3">
@@ -6222,7 +6222,7 @@
         <v>13</v>
       </c>
       <c r="F287" s="4">
-        <v>-0.57391584000000007</v>
+        <v>-1.4347896</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.3">
@@ -6242,7 +6242,7 @@
         <v>23</v>
       </c>
       <c r="F288" s="4">
-        <v>13.129265708</v>
+        <v>32.823164269999999</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.3">
@@ -6262,7 +6262,7 @@
         <v>21</v>
       </c>
       <c r="F289" s="4">
-        <v>0.69886165200000006</v>
+        <v>1.74715413</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.3">
@@ -6302,7 +6302,7 @@
         <v>18</v>
       </c>
       <c r="F291" s="4">
-        <v>18.366150600000001</v>
+        <v>45.915376500000001</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.3">
@@ -6322,7 +6322,7 @@
         <v>11</v>
       </c>
       <c r="F292" s="4">
-        <v>4.6281184719999997</v>
+        <v>11.57029618</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.3">
@@ -6342,7 +6342,7 @@
         <v>24</v>
       </c>
       <c r="F293" s="4">
-        <v>6.8435444039999993</v>
+        <v>17.108861009999998</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.3">
@@ -6362,7 +6362,7 @@
         <v>14</v>
       </c>
       <c r="F294" s="4">
-        <v>22.312607424000003</v>
+        <v>55.781518560000002</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.3">
@@ -6382,7 +6382,7 @@
         <v>21</v>
       </c>
       <c r="F295" s="4">
-        <v>3.6256818080000004</v>
+        <v>9.0642045200000005</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.3">
@@ -6422,7 +6422,7 @@
         <v>15</v>
       </c>
       <c r="F297" s="4">
-        <v>0.22598679599999999</v>
+        <v>0.56496698999999995</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.3">
@@ -6442,7 +6442,7 @@
         <v>13</v>
       </c>
       <c r="F298" s="4">
-        <v>8.804816E-3</v>
+        <v>2.201204E-2</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.3">
@@ -6462,7 +6462,7 @@
         <v>13</v>
       </c>
       <c r="F299" s="4">
-        <v>-4.5045072000000005E-2</v>
+        <v>-0.11261268000000001</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.3">
@@ -6482,7 +6482,7 @@
         <v>14</v>
       </c>
       <c r="F300" s="4">
-        <v>27.011482216000005</v>
+        <v>67.528705540000004</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.3">
@@ -6502,7 +6502,7 @@
         <v>13</v>
       </c>
       <c r="F301" s="4">
-        <v>-0.26391484400000004</v>
+        <v>-0.65978711000000001</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.3">
@@ -6542,7 +6542,7 @@
         <v>18</v>
       </c>
       <c r="F303" s="4">
-        <v>18.357901772000002</v>
+        <v>45.894754429999999</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.3">
@@ -6562,7 +6562,7 @@
         <v>23</v>
       </c>
       <c r="F304" s="4">
-        <v>19.234449084000001</v>
+        <v>48.086122709999998</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.3">
@@ -6602,7 +6602,7 @@
         <v>15</v>
       </c>
       <c r="F306" s="4">
-        <v>0.98995867600000009</v>
+        <v>2.47489669</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.3">
@@ -6642,7 +6642,7 @@
         <v>8</v>
       </c>
       <c r="F308" s="4">
-        <v>16.215259876000001</v>
+        <v>40.538149689999997</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.3">
@@ -6682,7 +6682,7 @@
         <v>24</v>
       </c>
       <c r="F310" s="4">
-        <v>9.5133321960000004</v>
+        <v>23.783330490000001</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.3">
@@ -6702,7 +6702,7 @@
         <v>13</v>
       </c>
       <c r="F311" s="4">
-        <v>-0.28215344000000003</v>
+        <v>-0.7053836</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.3">
@@ -6742,7 +6742,7 @@
         <v>19</v>
       </c>
       <c r="F313" s="4">
-        <v>-3.6788592000000002E-2</v>
+        <v>-9.1971479999999994E-2</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.3">
@@ -6782,7 +6782,7 @@
         <v>13</v>
       </c>
       <c r="F315" s="4">
-        <v>7.9526904000000009E-2</v>
+        <v>0.19881726</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.3">
@@ -6802,7 +6802,7 @@
         <v>8</v>
       </c>
       <c r="F316" s="4">
-        <v>18.498225439999999</v>
+        <v>46.245563599999997</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.3">
@@ -6822,7 +6822,7 @@
         <v>27</v>
       </c>
       <c r="F317" s="4">
-        <v>1.8758227519999999</v>
+        <v>4.6895568799999996</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.3">
@@ -6842,7 +6842,7 @@
         <v>13</v>
       </c>
       <c r="F318" s="4">
-        <v>-0.25188475199999999</v>
+        <v>-0.62971188</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.3">
@@ -6862,7 +6862,7 @@
         <v>21</v>
       </c>
       <c r="F319" s="4">
-        <v>3.5449316120000001</v>
+        <v>8.8623290299999997</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.3">
@@ -6882,7 +6882,7 @@
         <v>26</v>
       </c>
       <c r="F320" s="4">
-        <v>18.840770320000001</v>
+        <v>47.101925799999997</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.3">
@@ -6902,7 +6902,7 @@
         <v>15</v>
       </c>
       <c r="F321" s="4">
-        <v>0.248619908</v>
+        <v>0.62154977</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.3">
@@ -6942,7 +6942,7 @@
         <v>8</v>
       </c>
       <c r="F323" s="4">
-        <v>35.682099352000002</v>
+        <v>89.20524838</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.3">
@@ -6962,7 +6962,7 @@
         <v>14</v>
       </c>
       <c r="F324" s="4">
-        <v>26.170820636000002</v>
+        <v>65.427051590000005</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.3">
@@ -6982,7 +6982,7 @@
         <v>23</v>
       </c>
       <c r="F325" s="4">
-        <v>15.145625472000001</v>
+        <v>37.864063680000001</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.3">
@@ -7002,7 +7002,7 @@
         <v>21</v>
       </c>
       <c r="F326" s="4">
-        <v>3.397047616</v>
+        <v>8.4926190399999992</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.3">
@@ -7022,7 +7022,7 @@
         <v>8</v>
       </c>
       <c r="F327" s="4">
-        <v>25.517549696000003</v>
+        <v>63.793874240000001</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.3">
@@ -7042,7 +7042,7 @@
         <v>23</v>
       </c>
       <c r="F328" s="4">
-        <v>6.5367555240000002</v>
+        <v>16.34188881</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.3">
@@ -7062,7 +7062,7 @@
         <v>27</v>
       </c>
       <c r="F329" s="4">
-        <v>-0.29524081200000002</v>
+        <v>-0.73810202999999996</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.3">
@@ -7082,7 +7082,7 @@
         <v>14</v>
       </c>
       <c r="F330" s="4">
-        <v>30.289629731999998</v>
+        <v>75.724074329999993</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.3">
@@ -7102,7 +7102,7 @@
         <v>27</v>
       </c>
       <c r="F331" s="4">
-        <v>1.0904923639999999</v>
+        <v>2.72623091</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.3">
@@ -7122,7 +7122,7 @@
         <v>15</v>
       </c>
       <c r="F332" s="4">
-        <v>1.0607455760000002</v>
+        <v>2.6518639400000001</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.3">
@@ -7142,7 +7142,7 @@
         <v>21</v>
       </c>
       <c r="F333" s="4">
-        <v>0.49897349999999996</v>
+        <v>1.2474337499999999</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.3">
@@ -7162,7 +7162,7 @@
         <v>26</v>
       </c>
       <c r="F334" s="4">
-        <v>20.809573924000002</v>
+        <v>52.02393481</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.3">
@@ -7182,7 +7182,7 @@
         <v>23</v>
       </c>
       <c r="F335" s="4">
-        <v>15.879458528000001</v>
+        <v>39.698646320000002</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.3">
@@ -7202,7 +7202,7 @@
         <v>23</v>
       </c>
       <c r="F336" s="4">
-        <v>6.5457145120000009</v>
+        <v>16.364286280000002</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.3">
@@ -7242,7 +7242,7 @@
         <v>27</v>
       </c>
       <c r="F338" s="4">
-        <v>9.5125341120000009</v>
+        <v>23.78133528</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.3">
@@ -7262,7 +7262,7 @@
         <v>27</v>
       </c>
       <c r="F339" s="4">
-        <v>11.543073192000001</v>
+        <v>28.85768298</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.3">
@@ -7282,7 +7282,7 @@
         <v>13</v>
       </c>
       <c r="F340" s="4">
-        <v>-0.93361642000000011</v>
+        <v>-2.3340410500000002</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.3">
@@ -7342,7 +7342,7 @@
         <v>19</v>
       </c>
       <c r="F343" s="4">
-        <v>-1.2388240000000001E-3</v>
+        <v>-3.09706E-3</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.3">
@@ -7362,7 +7362,7 @@
         <v>20</v>
       </c>
       <c r="F344" s="4">
-        <v>13.403693880000001</v>
+        <v>33.5092347</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.3">
@@ -7382,7 +7382,7 @@
         <v>23</v>
       </c>
       <c r="F345" s="4">
-        <v>6.2114863200000006</v>
+        <v>15.528715800000001</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.3">
@@ -7402,7 +7402,7 @@
         <v>13</v>
       </c>
       <c r="F346" s="4">
-        <v>-0.89859348800000005</v>
+        <v>-2.2464837200000001</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.3">
@@ -7422,7 +7422,7 @@
         <v>13</v>
       </c>
       <c r="F347" s="4">
-        <v>-0.25188475199999999</v>
+        <v>-0.62971188</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.3">
@@ -7462,7 +7462,7 @@
         <v>18</v>
       </c>
       <c r="F349" s="4">
-        <v>22.550334488000001</v>
+        <v>56.375836219999997</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.3">
@@ -7482,7 +7482,7 @@
         <v>24</v>
       </c>
       <c r="F350" s="4">
-        <v>6.0839924000000004E-2</v>
+        <v>0.15209981</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.3">
@@ -7502,7 +7502,7 @@
         <v>19</v>
       </c>
       <c r="F351" s="4">
-        <v>-4.8547920000000001E-3</v>
+        <v>-1.213698E-2</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.3">
@@ -7522,7 +7522,7 @@
         <v>20</v>
       </c>
       <c r="F352" s="4">
-        <v>38.405082668000006</v>
+        <v>96.01270667</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.3">
@@ -7542,7 +7542,7 @@
         <v>24</v>
       </c>
       <c r="F353" s="4">
-        <v>10.810204336</v>
+        <v>27.025510839999999</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.3">
@@ -7562,7 +7562,7 @@
         <v>27</v>
       </c>
       <c r="F354" s="4">
-        <v>0.93571462400000005</v>
+        <v>2.3392865600000001</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.3">
@@ -7582,7 +7582,7 @@
         <v>24</v>
       </c>
       <c r="F355" s="4">
-        <v>-15.296769716</v>
+        <v>-38.24192429</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.3">
@@ -7602,7 +7602,7 @@
         <v>13</v>
       </c>
       <c r="F356" s="4">
-        <v>-0.83518093199999999</v>
+        <v>-2.0879523299999998</v>
       </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.3">
@@ -7622,7 +7622,7 @@
         <v>13</v>
       </c>
       <c r="F357" s="4">
-        <v>-0.23288149200000002</v>
+        <v>-0.58220373000000003</v>
       </c>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.3">
@@ -7682,7 +7682,7 @@
         <v>8</v>
       </c>
       <c r="F360" s="4">
-        <v>18.685421012000003</v>
+        <v>46.713552530000001</v>
       </c>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.3">
@@ -7702,7 +7702,7 @@
         <v>21</v>
       </c>
       <c r="F361" s="4">
-        <v>0.44456505600000001</v>
+        <v>1.11141264</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.3">
@@ -7742,7 +7742,7 @@
         <v>14</v>
       </c>
       <c r="F363" s="4">
-        <v>14.937323048</v>
+        <v>37.343307619999997</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.3">
@@ -7762,7 +7762,7 @@
         <v>8</v>
       </c>
       <c r="F364" s="4">
-        <v>32.722002112000006</v>
+        <v>81.805005280000003</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.3">
@@ -7782,7 +7782,7 @@
         <v>15</v>
       </c>
       <c r="F365" s="4">
-        <v>1.272167048</v>
+        <v>3.1804176200000001</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.3">
@@ -7802,7 +7802,7 @@
         <v>21</v>
       </c>
       <c r="F366" s="4">
-        <v>0.55691785999999999</v>
+        <v>1.39229465</v>
       </c>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.3">
@@ -7842,7 +7842,7 @@
         <v>23</v>
       </c>
       <c r="F368" s="4">
-        <v>6.3849881400000008</v>
+        <v>15.96247035</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.3">
@@ -7862,7 +7862,7 @@
         <v>21</v>
       </c>
       <c r="F369" s="4">
-        <v>0.6507509680000001</v>
+        <v>1.62687742</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.3">
@@ -7882,7 +7882,7 @@
         <v>21</v>
       </c>
       <c r="F370" s="4">
-        <v>0.7369681400000001</v>
+        <v>1.84242035</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.3">
@@ -7902,7 +7902,7 @@
         <v>15</v>
       </c>
       <c r="F371" s="4">
-        <v>0.23636914400000003</v>
+        <v>0.59092286000000005</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.3">
@@ -7922,7 +7922,7 @@
         <v>15</v>
       </c>
       <c r="F372" s="4">
-        <v>0.91129587600000006</v>
+        <v>2.2782396899999999</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.3">
@@ -7942,7 +7942,7 @@
         <v>23</v>
       </c>
       <c r="F373" s="4">
-        <v>6.7322531000000003</v>
+        <v>16.830632749999999</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.3">
@@ -7982,7 +7982,7 @@
         <v>15</v>
       </c>
       <c r="F375" s="4">
-        <v>0.9517421960000001</v>
+        <v>2.37935549</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.3">
@@ -8022,7 +8022,7 @@
         <v>20</v>
       </c>
       <c r="F377" s="4">
-        <v>17.3906654</v>
+        <v>43.476663500000001</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.3">
@@ -8042,7 +8042,7 @@
         <v>23</v>
       </c>
       <c r="F378" s="4">
-        <v>4.5188717040000004</v>
+        <v>11.29717926</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.3">
@@ -8102,7 +8102,7 @@
         <v>27</v>
       </c>
       <c r="F381" s="4">
-        <v>1.776310284</v>
+        <v>4.4407757099999996</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.3">
@@ -8122,7 +8122,7 @@
         <v>8</v>
       </c>
       <c r="F382" s="4">
-        <v>19.734377512000002</v>
+        <v>49.335943780000001</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.3">
@@ -8162,7 +8162,7 @@
         <v>20</v>
       </c>
       <c r="F384" s="4">
-        <v>120.86052330400001</v>
+        <v>302.15130826000001</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.3">
@@ -8182,7 +8182,7 @@
         <v>14</v>
       </c>
       <c r="F385" s="4">
-        <v>24.276315547999999</v>
+        <v>60.690788869999999</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.3">
@@ -8222,7 +8222,7 @@
         <v>14</v>
       </c>
       <c r="F387" s="4">
-        <v>22.312607424000003</v>
+        <v>55.781518560000002</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.3">
@@ -8242,7 +8242,7 @@
         <v>15</v>
       </c>
       <c r="F388" s="4">
-        <v>0.28519742400000003</v>
+        <v>0.71299356000000003</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.3">
@@ -8262,7 +8262,7 @@
         <v>13</v>
       </c>
       <c r="F389" s="4">
-        <v>-0.54690623599999999</v>
+        <v>-1.3672655899999999</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.3">
@@ -8282,7 +8282,7 @@
         <v>15</v>
       </c>
       <c r="F390" s="4">
-        <v>0.174263784</v>
+        <v>0.43565946</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.3">
@@ -8302,7 +8302,7 @@
         <v>19</v>
       </c>
       <c r="F391" s="4">
-        <v>2.4648660000000003E-2</v>
+        <v>6.162165E-2</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.3">
@@ -8322,7 +8322,7 @@
         <v>21</v>
       </c>
       <c r="F392" s="4">
-        <v>3.3095124040000004</v>
+        <v>8.2737810100000004</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.3">
@@ -8342,7 +8342,7 @@
         <v>21</v>
       </c>
       <c r="F393" s="4">
-        <v>0.65663802800000004</v>
+        <v>1.6415950699999999</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.3">
@@ -8382,7 +8382,7 @@
         <v>21</v>
       </c>
       <c r="F395" s="4">
-        <v>0.56103224799999996</v>
+        <v>1.4025806199999999</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.3">
@@ -8402,7 +8402,7 @@
         <v>8</v>
       </c>
       <c r="F396" s="4">
-        <v>34.892739604000006</v>
+        <v>87.231849010000005</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.3">
@@ -8422,7 +8422,7 @@
         <v>13</v>
       </c>
       <c r="F397" s="4">
-        <v>-1.0268706000000001</v>
+        <v>-2.5671765</v>
       </c>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.3">
@@ -8442,7 +8442,7 @@
         <v>27</v>
       </c>
       <c r="F398" s="4">
-        <v>0.320451708</v>
+        <v>0.80112927</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.3">
@@ -8462,7 +8462,7 @@
         <v>27</v>
       </c>
       <c r="F399" s="4">
-        <v>5.1708432000000006E-2</v>
+        <v>0.12927108000000001</v>
       </c>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.3">
@@ -8482,7 +8482,7 @@
         <v>13</v>
       </c>
       <c r="F400" s="4">
-        <v>-0.29416971200000003</v>
+        <v>-0.73542428000000004</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.3">
@@ -8522,7 +8522,7 @@
         <v>21</v>
       </c>
       <c r="F402" s="4">
-        <v>0.62322762000000009</v>
+        <v>1.5580690500000001</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.3">
@@ -8542,7 +8542,7 @@
         <v>18</v>
       </c>
       <c r="F403" s="4">
-        <v>18.998006128</v>
+        <v>47.49501532</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.3">
@@ -8582,7 +8582,7 @@
         <v>24</v>
       </c>
       <c r="F405" s="4">
-        <v>1.1508041520000001</v>
+        <v>2.8770103800000002</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.3">
@@ -8602,7 +8602,7 @@
         <v>24</v>
       </c>
       <c r="F406" s="4">
-        <v>5.8695094880000003</v>
+        <v>14.67377372</v>
       </c>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.3">
@@ -8622,7 +8622,7 @@
         <v>20</v>
       </c>
       <c r="F407" s="4">
-        <v>35.636479164000001</v>
+        <v>89.091197910000005</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.3">
@@ -8662,7 +8662,7 @@
         <v>11</v>
       </c>
       <c r="F409" s="4">
-        <v>4.4133543560000001</v>
+        <v>11.03338589</v>
       </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.3">
@@ -8722,7 +8722,7 @@
         <v>13</v>
       </c>
       <c r="F412" s="4">
-        <v>0.12255477200000001</v>
+        <v>0.30638693</v>
       </c>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.3">
@@ -8742,7 +8742,7 @@
         <v>15</v>
       </c>
       <c r="F413" s="4">
-        <v>0.14694016000000001</v>
+        <v>0.36735040000000002</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.3">
@@ -8762,7 +8762,7 @@
         <v>15</v>
       </c>
       <c r="F414" s="4">
-        <v>0.15645293600000001</v>
+        <v>0.39113234000000002</v>
       </c>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.3">
@@ -8782,7 +8782,7 @@
         <v>8</v>
       </c>
       <c r="F415" s="4">
-        <v>18.049363980000003</v>
+        <v>45.123409950000003</v>
       </c>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.3">
@@ -8822,7 +8822,7 @@
         <v>23</v>
       </c>
       <c r="F417" s="4">
-        <v>6.9623330400000008</v>
+        <v>17.4058326</v>
       </c>
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.3">
@@ -8842,7 +8842,7 @@
         <v>19</v>
       </c>
       <c r="F418" s="4">
-        <v>-3.8476528000000003E-2</v>
+        <v>-9.6191319999999997E-2</v>
       </c>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.3">
@@ -8862,7 +8862,7 @@
         <v>11</v>
       </c>
       <c r="F419" s="4">
-        <v>6.4833801080000004</v>
+        <v>16.20845027</v>
       </c>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.3">
@@ -8882,7 +8882,7 @@
         <v>15</v>
       </c>
       <c r="F420" s="4">
-        <v>0.23854608000000002</v>
+        <v>0.59636520000000004</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.3">
@@ -8902,7 +8902,7 @@
         <v>15</v>
       </c>
       <c r="F421" s="4">
-        <v>1.0687020840000001</v>
+        <v>2.6717552100000002</v>
       </c>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.3">
@@ -8922,7 +8922,7 @@
         <v>13</v>
       </c>
       <c r="F422" s="4">
-        <v>-0.29878964000000002</v>
+        <v>-0.74697409999999997</v>
       </c>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.3">
@@ -8942,7 +8942,7 @@
         <v>21</v>
       </c>
       <c r="F423" s="4">
-        <v>0.427718184</v>
+        <v>1.06929546</v>
       </c>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.3">
@@ -8962,7 +8962,7 @@
         <v>19</v>
       </c>
       <c r="F424" s="4">
-        <v>2.2369816000000001E-2</v>
+        <v>5.5924540000000002E-2</v>
       </c>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.3">
@@ -8982,7 +8982,7 @@
         <v>13</v>
       </c>
       <c r="F425" s="4">
-        <v>-0.54690623599999999</v>
+        <v>-1.3672655899999999</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.3">
@@ -9002,7 +9002,7 @@
         <v>21</v>
       </c>
       <c r="F426" s="4">
-        <v>4.4073380680000005</v>
+        <v>11.01834517</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.3">
@@ -9022,7 +9022,7 @@
         <v>11</v>
       </c>
       <c r="F427" s="4">
-        <v>7.1051295000000003</v>
+        <v>17.762823749999999</v>
       </c>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.3">
@@ -9042,7 +9042,7 @@
         <v>19</v>
       </c>
       <c r="F428" s="4">
-        <v>-4.1837764E-2</v>
+        <v>-0.10459441</v>
       </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.3">
@@ -9062,7 +9062,7 @@
         <v>11</v>
       </c>
       <c r="F429" s="4">
-        <v>6.5967251759999996</v>
+        <v>16.491812939999999</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.3">
@@ -9082,7 +9082,7 @@
         <v>19</v>
       </c>
       <c r="F430" s="4">
-        <v>-0.37996378400000003</v>
+        <v>-0.94990945999999998</v>
       </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.3">
@@ -9102,7 +9102,7 @@
         <v>27</v>
       </c>
       <c r="F431" s="4">
-        <v>2.04908782</v>
+        <v>5.1227195500000002</v>
       </c>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.3">
@@ -9142,7 +9142,7 @@
         <v>13</v>
       </c>
       <c r="F433" s="4">
-        <v>-0.23131691200000001</v>
+        <v>-0.57829227999999999</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.3">
@@ -9162,7 +9162,7 @@
         <v>13</v>
       </c>
       <c r="F434" s="4">
-        <v>-0.25090295200000001</v>
+        <v>-0.62725737999999998</v>
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.3">
@@ -9182,7 +9182,7 @@
         <v>14</v>
       </c>
       <c r="F435" s="4">
-        <v>23.769290928000004</v>
+        <v>59.423227320000002</v>
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.3">
@@ -9242,7 +9242,7 @@
         <v>8</v>
       </c>
       <c r="F438" s="4">
-        <v>34.299208487999998</v>
+        <v>85.748021219999998</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.3">
@@ -9262,7 +9262,7 @@
         <v>18</v>
       </c>
       <c r="F439" s="4">
-        <v>105.695889032</v>
+        <v>264.23972257999998</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.3">
@@ -9322,7 +9322,7 @@
         <v>21</v>
       </c>
       <c r="F442" s="4">
-        <v>3.5338418120000004</v>
+        <v>8.83460453</v>
       </c>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.3">
@@ -9342,7 +9342,7 @@
         <v>8</v>
       </c>
       <c r="F443" s="4">
-        <v>13.812997404000001</v>
+        <v>34.532493510000002</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.3">
@@ -9362,7 +9362,7 @@
         <v>27</v>
       </c>
       <c r="F444" s="4">
-        <v>5.5423814040000003</v>
+        <v>13.855953510000001</v>
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.3">
@@ -9382,7 +9382,7 @@
         <v>18</v>
       </c>
       <c r="F445" s="4">
-        <v>109.63404571200002</v>
+        <v>274.08511428000003</v>
       </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.3">
@@ -9402,7 +9402,7 @@
         <v>24</v>
       </c>
       <c r="F446" s="4">
-        <v>-10.548063768</v>
+        <v>-26.37015942</v>
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.3">
@@ -9562,7 +9562,7 @@
         <v>19</v>
       </c>
       <c r="F454" s="4">
-        <v>-5.4735515999999998E-2</v>
+        <v>-0.13683878999999999</v>
       </c>
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.3">
@@ -9582,7 +9582,7 @@
         <v>15</v>
       </c>
       <c r="F455" s="4">
-        <v>0.281105612</v>
+        <v>0.70276402999999998</v>
       </c>
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.3">
@@ -9622,7 +9622,7 @@
         <v>18</v>
       </c>
       <c r="F457" s="4">
-        <v>18.48210942</v>
+        <v>46.205273550000001</v>
       </c>
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.3">
@@ -9642,7 +9642,7 @@
         <v>14</v>
       </c>
       <c r="F458" s="4">
-        <v>24.741930556</v>
+        <v>61.854826389999999</v>
       </c>
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.3">
@@ -9662,7 +9662,7 @@
         <v>24</v>
       </c>
       <c r="F459" s="4">
-        <v>5.1853074680000004</v>
+        <v>12.96326867</v>
       </c>
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.3">
@@ -9762,7 +9762,7 @@
         <v>14</v>
       </c>
       <c r="F464" s="4">
-        <v>30.122786567999999</v>
+        <v>75.306966419999995</v>
       </c>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.3">
@@ -9782,7 +9782,7 @@
         <v>26</v>
       </c>
       <c r="F465" s="4">
-        <v>21.234764912000003</v>
+        <v>53.08691228</v>
       </c>
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.3">
@@ -9802,7 +9802,7 @@
         <v>11</v>
       </c>
       <c r="F466" s="4">
-        <v>6.735465348</v>
+        <v>16.838663369999999</v>
       </c>
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.3">
@@ -9842,7 +9842,7 @@
         <v>18</v>
       </c>
       <c r="F468" s="4">
-        <v>18.345357068000002</v>
+        <v>45.863392670000003</v>
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.3">
@@ -9862,7 +9862,7 @@
         <v>27</v>
       </c>
       <c r="F469" s="4">
-        <v>1.7148180239999999</v>
+        <v>4.2870450599999996</v>
       </c>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.3">
@@ -9882,7 +9882,7 @@
         <v>27</v>
       </c>
       <c r="F470" s="4">
-        <v>-0.59093188400000007</v>
+        <v>-1.47732971</v>
       </c>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.3">
@@ -9902,7 +9902,7 @@
         <v>14</v>
       </c>
       <c r="F471" s="4">
-        <v>15.131618276000001</v>
+        <v>37.829045690000001</v>
       </c>
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.3">
@@ -9922,7 +9922,7 @@
         <v>14</v>
       </c>
       <c r="F472" s="4">
-        <v>31.306123604</v>
+        <v>78.265309009999996</v>
       </c>
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.3">
@@ -9942,7 +9942,7 @@
         <v>18</v>
       </c>
       <c r="F473" s="4">
-        <v>34.439842036000002</v>
+        <v>86.099605089999997</v>
       </c>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.3">
@@ -9962,7 +9962,7 @@
         <v>8</v>
       </c>
       <c r="F474" s="4">
-        <v>17.738249292000003</v>
+        <v>44.345623230000001</v>
       </c>
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.3">
@@ -9982,7 +9982,7 @@
         <v>15</v>
       </c>
       <c r="F475" s="4">
-        <v>0.27977488</v>
+        <v>0.69943719999999998</v>
       </c>
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.3">
@@ -10002,7 +10002,7 @@
         <v>15</v>
       </c>
       <c r="F476" s="4">
-        <v>1.192207936</v>
+        <v>2.9805198399999999</v>
       </c>
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.3">
@@ -10022,7 +10022,7 @@
         <v>18</v>
       </c>
       <c r="F477" s="4">
-        <v>31.526965688000004</v>
+        <v>78.817414220000003</v>
       </c>
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.3">
@@ -10042,7 +10042,7 @@
         <v>14</v>
       </c>
       <c r="F478" s="4">
-        <v>15.872561511999999</v>
+        <v>39.681403779999997</v>
       </c>
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.3">
@@ -10062,7 +10062,7 @@
         <v>20</v>
       </c>
       <c r="F479" s="4">
-        <v>115.138265332</v>
+        <v>287.84566332999998</v>
       </c>
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.3">
@@ -10082,7 +10082,7 @@
         <v>23</v>
       </c>
       <c r="F480" s="4">
-        <v>14.704149480000002</v>
+        <v>36.760373700000002</v>
       </c>
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.3">
@@ -10102,7 +10102,7 @@
         <v>19</v>
       </c>
       <c r="F481" s="4">
-        <v>-1.9282952000000003E-2</v>
+        <v>-4.8207380000000001E-2</v>
       </c>
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.3">
@@ -10142,7 +10142,7 @@
         <v>13</v>
       </c>
       <c r="F483" s="4">
-        <v>-0.84767976800000011</v>
+        <v>-2.1191994200000002</v>
       </c>
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.3">
@@ -10162,7 +10162,7 @@
         <v>18</v>
       </c>
       <c r="F484" s="4">
-        <v>21.748105644000002</v>
+        <v>54.370264110000001</v>
       </c>
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.3">
@@ -10182,7 +10182,7 @@
         <v>15</v>
       </c>
       <c r="F485" s="4">
-        <v>0.222722908</v>
+        <v>0.55680726999999997</v>
       </c>
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.3">
@@ -10202,7 +10202,7 @@
         <v>24</v>
       </c>
       <c r="F486" s="4">
-        <v>4.7892515119999999</v>
+        <v>11.97312878</v>
       </c>
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.3">
@@ -10222,7 +10222,7 @@
         <v>13</v>
       </c>
       <c r="F487" s="4">
-        <v>-0.26525026000000002</v>
+        <v>-0.66312565000000001</v>
       </c>
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.3">
@@ -10262,7 +10262,7 @@
         <v>20</v>
       </c>
       <c r="F489" s="4">
-        <v>14.096839092</v>
+        <v>35.242097729999998</v>
       </c>
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.3">
@@ -10282,7 +10282,7 @@
         <v>19</v>
       </c>
       <c r="F490" s="4">
-        <v>-5.0563024000000005E-2</v>
+        <v>-0.12640756</v>
       </c>
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.3">
@@ -10302,7 +10302,7 @@
         <v>23</v>
       </c>
       <c r="F491" s="4">
-        <v>3.6119690520000001</v>
+        <v>9.0299226299999997</v>
       </c>
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.3">
@@ -10322,7 +10322,7 @@
         <v>24</v>
       </c>
       <c r="F492" s="4">
-        <v>-4.5263485719999998</v>
+        <v>-11.31587143</v>
       </c>
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.3">
@@ -10342,7 +10342,7 @@
         <v>19</v>
       </c>
       <c r="F493" s="4">
-        <v>4.2548596000000001E-2</v>
+        <v>0.10637149</v>
       </c>
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.3">
@@ -10382,7 +10382,7 @@
         <v>27</v>
       </c>
       <c r="F495" s="4">
-        <v>0.51175573200000002</v>
+        <v>1.2793893300000001</v>
       </c>
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.3">
@@ -10402,7 +10402,7 @@
         <v>24</v>
       </c>
       <c r="F496" s="4">
-        <v>73.484301724000005</v>
+        <v>183.71075431</v>
       </c>
     </row>
     <row r="497" spans="1:6" x14ac:dyDescent="0.3">
@@ -10422,7 +10422,7 @@
         <v>21</v>
       </c>
       <c r="F497" s="4">
-        <v>0.55801291200000003</v>
+        <v>1.3950322799999999</v>
       </c>
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.3">
@@ -10442,7 +10442,7 @@
         <v>15</v>
       </c>
       <c r="F498" s="4">
-        <v>0.27443198400000002</v>
+        <v>0.68607996000000004</v>
       </c>
     </row>
     <row r="499" spans="1:6" x14ac:dyDescent="0.3">
@@ -10482,7 +10482,7 @@
         <v>11</v>
       </c>
       <c r="F500" s="4">
-        <v>7.2933062880000001</v>
+        <v>18.233265719999999</v>
       </c>
     </row>
     <row r="501" spans="1:6" x14ac:dyDescent="0.3">
@@ -10502,7 +10502,7 @@
         <v>20</v>
       </c>
       <c r="F501" s="4">
-        <v>103.20159232399999</v>
+        <v>258.00398080999997</v>
       </c>
     </row>
     <row r="502" spans="1:6" x14ac:dyDescent="0.3">
@@ -10522,7 +10522,7 @@
         <v>20</v>
       </c>
       <c r="F502" s="4">
-        <v>146.67635780400002</v>
+        <v>366.69089451000002</v>
       </c>
     </row>
     <row r="503" spans="1:6" x14ac:dyDescent="0.3">
@@ -10542,7 +10542,7 @@
         <v>21</v>
       </c>
       <c r="F503" s="4">
-        <v>3.1662216760000002</v>
+        <v>7.9155541899999999</v>
       </c>
     </row>
     <row r="504" spans="1:6" x14ac:dyDescent="0.3">
@@ -10562,7 +10562,7 @@
         <v>27</v>
       </c>
       <c r="F504" s="4">
-        <v>0.14478655600000001</v>
+        <v>0.36196639000000003</v>
       </c>
     </row>
     <row r="505" spans="1:6" x14ac:dyDescent="0.3">
@@ -10582,7 +10582,7 @@
         <v>21</v>
       </c>
       <c r="F505" s="4">
-        <v>0.46247888799999998</v>
+        <v>1.1561972199999999</v>
       </c>
     </row>
     <row r="506" spans="1:6" x14ac:dyDescent="0.3">
@@ -10622,7 +10622,7 @@
         <v>20</v>
       </c>
       <c r="F507" s="4">
-        <v>33.092684900000002</v>
+        <v>82.731712250000001</v>
       </c>
     </row>
     <row r="508" spans="1:6" x14ac:dyDescent="0.3">
@@ -10642,7 +10642,7 @@
         <v>21</v>
       </c>
       <c r="F508" s="4">
-        <v>0.57002008400000004</v>
+        <v>1.42505021</v>
       </c>
     </row>
     <row r="509" spans="1:6" x14ac:dyDescent="0.3">
@@ -10662,7 +10662,7 @@
         <v>24</v>
       </c>
       <c r="F509" s="4">
-        <v>-6.6322271240000008</v>
+        <v>-16.580567810000002</v>
       </c>
     </row>
     <row r="510" spans="1:6" x14ac:dyDescent="0.3">
@@ -10682,7 +10682,7 @@
         <v>8</v>
       </c>
       <c r="F510" s="4">
-        <v>33.360062431999999</v>
+        <v>83.400156080000002</v>
       </c>
     </row>
     <row r="511" spans="1:6" x14ac:dyDescent="0.3">
@@ -10702,7 +10702,7 @@
         <v>15</v>
       </c>
       <c r="F511" s="4">
-        <v>0.99227752000000002</v>
+        <v>2.4806938000000001</v>
       </c>
     </row>
     <row r="512" spans="1:6" x14ac:dyDescent="0.3">
@@ -10722,7 +10722,7 @@
         <v>14</v>
       </c>
       <c r="F512" s="4">
-        <v>16.336701196000003</v>
+        <v>40.841752990000003</v>
       </c>
     </row>
     <row r="513" spans="1:6" x14ac:dyDescent="0.3">
@@ -10742,7 +10742,7 @@
         <v>24</v>
       </c>
       <c r="F513" s="4">
-        <v>-4.7089315960000002</v>
+        <v>-11.77232899</v>
       </c>
     </row>
     <row r="514" spans="1:6" x14ac:dyDescent="0.3">
@@ -10782,7 +10782,7 @@
         <v>20</v>
       </c>
       <c r="F515" s="4">
-        <v>31.245669016000001</v>
+        <v>78.114172539999998</v>
       </c>
     </row>
     <row r="516" spans="1:6" x14ac:dyDescent="0.3">
@@ -10802,7 +10802,7 @@
         <v>18</v>
       </c>
       <c r="F516" s="4">
-        <v>18.74804924</v>
+        <v>46.870123100000001</v>
       </c>
     </row>
     <row r="517" spans="1:6" x14ac:dyDescent="0.3">
@@ -10822,7 +10822,7 @@
         <v>19</v>
       </c>
       <c r="F517" s="4">
-        <v>5.3994024000000002E-2</v>
+        <v>0.13498505999999999</v>
       </c>
     </row>
     <row r="518" spans="1:6" x14ac:dyDescent="0.3">
@@ -10842,7 +10842,7 @@
         <v>14</v>
       </c>
       <c r="F518" s="4">
-        <v>31.576099196000001</v>
+        <v>78.940247990000003</v>
       </c>
     </row>
     <row r="519" spans="1:6" x14ac:dyDescent="0.3">
@@ -10862,7 +10862,7 @@
         <v>15</v>
       </c>
       <c r="F519" s="4">
-        <v>0.25220234800000002</v>
+        <v>0.63050587000000002</v>
       </c>
     </row>
     <row r="520" spans="1:6" x14ac:dyDescent="0.3">
@@ -10882,7 +10882,7 @@
         <v>21</v>
       </c>
       <c r="F520" s="4">
-        <v>0.57212074400000001</v>
+        <v>1.4303018599999999</v>
       </c>
     </row>
     <row r="521" spans="1:6" x14ac:dyDescent="0.3">
@@ -10902,7 +10902,7 @@
         <v>27</v>
       </c>
       <c r="F521" s="4">
-        <v>3.5278893600000005</v>
+        <v>8.8197234000000009</v>
       </c>
     </row>
     <row r="522" spans="1:6" x14ac:dyDescent="0.3">
@@ -10922,7 +10922,7 @@
         <v>24</v>
       </c>
       <c r="F522" s="4">
-        <v>-0.28280912400000002</v>
+        <v>-0.70702281</v>
       </c>
     </row>
     <row r="523" spans="1:6" x14ac:dyDescent="0.3">
@@ -10942,7 +10942,7 @@
         <v>23</v>
       </c>
       <c r="F523" s="4">
-        <v>7.6735906880000009</v>
+        <v>19.18397672</v>
       </c>
     </row>
     <row r="524" spans="1:6" x14ac:dyDescent="0.3">
@@ -10962,7 +10962,7 @@
         <v>21</v>
       </c>
       <c r="F524" s="4">
-        <v>3.741769884</v>
+        <v>9.35442471</v>
       </c>
     </row>
     <row r="525" spans="1:6" x14ac:dyDescent="0.3">
@@ -11002,7 +11002,7 @@
         <v>13</v>
       </c>
       <c r="F526" s="4">
-        <v>0.68430051200000008</v>
+        <v>1.71075128</v>
       </c>
     </row>
     <row r="527" spans="1:6" x14ac:dyDescent="0.3">
@@ -11022,7 +11022,7 @@
         <v>23</v>
       </c>
       <c r="F527" s="4">
-        <v>15.352542952</v>
+        <v>38.381357379999997</v>
       </c>
     </row>
     <row r="528" spans="1:6" x14ac:dyDescent="0.3">
@@ -11062,7 +11062,7 @@
         <v>18</v>
       </c>
       <c r="F529" s="4">
-        <v>34.519374144000004</v>
+        <v>86.298435359999999</v>
       </c>
     </row>
     <row r="530" spans="1:6" x14ac:dyDescent="0.3">
@@ -11082,7 +11082,7 @@
         <v>14</v>
       </c>
       <c r="F530" s="4">
-        <v>30.289629731999998</v>
+        <v>75.724074329999993</v>
       </c>
     </row>
     <row r="531" spans="1:6" x14ac:dyDescent="0.3">
@@ -11102,7 +11102,7 @@
         <v>8</v>
       </c>
       <c r="F531" s="4">
-        <v>13.82151064</v>
+        <v>34.553776599999999</v>
       </c>
     </row>
     <row r="532" spans="1:6" x14ac:dyDescent="0.3">
@@ -11122,7 +11122,7 @@
         <v>18</v>
       </c>
       <c r="F532" s="4">
-        <v>32.968028451999999</v>
+        <v>82.420071129999997</v>
       </c>
     </row>
     <row r="533" spans="1:6" x14ac:dyDescent="0.3">
@@ -11162,7 +11162,7 @@
         <v>8</v>
       </c>
       <c r="F534" s="4">
-        <v>30.493306619999998</v>
+        <v>76.233266549999996</v>
       </c>
     </row>
     <row r="535" spans="1:6" x14ac:dyDescent="0.3">
@@ -11182,7 +11182,7 @@
         <v>19</v>
       </c>
       <c r="F535" s="4">
-        <v>-6.5254268000000004E-2</v>
+        <v>-0.16313567000000001</v>
       </c>
     </row>
     <row r="536" spans="1:6" x14ac:dyDescent="0.3">
@@ -11202,7 +11202,7 @@
         <v>14</v>
       </c>
       <c r="F536" s="4">
-        <v>30.757476816000004</v>
+        <v>76.893692040000005</v>
       </c>
     </row>
     <row r="537" spans="1:6" x14ac:dyDescent="0.3">
@@ -11222,7 +11222,7 @@
         <v>21</v>
       </c>
       <c r="F537" s="4">
-        <v>0.56329505600000007</v>
+        <v>1.4082376400000001</v>
       </c>
     </row>
     <row r="538" spans="1:6" x14ac:dyDescent="0.3">
@@ -11242,7 +11242,7 @@
         <v>13</v>
       </c>
       <c r="F538" s="4">
-        <v>-0.26544453600000001</v>
+        <v>-0.66361133999999999</v>
       </c>
     </row>
     <row r="539" spans="1:6" x14ac:dyDescent="0.3">
@@ -11262,7 +11262,7 @@
         <v>20</v>
       </c>
       <c r="F539" s="4">
-        <v>98.387554051999999</v>
+        <v>245.96888512999999</v>
       </c>
     </row>
     <row r="540" spans="1:6" x14ac:dyDescent="0.3">
@@ -11282,7 +11282,7 @@
         <v>21</v>
       </c>
       <c r="F540" s="4">
-        <v>0.63397104800000004</v>
+        <v>1.58492762</v>
       </c>
     </row>
     <row r="541" spans="1:6" x14ac:dyDescent="0.3">
@@ -11302,7 +11302,7 @@
         <v>18</v>
       </c>
       <c r="F541" s="4">
-        <v>18.697339600000003</v>
+        <v>46.743349000000002</v>
       </c>
     </row>
     <row r="542" spans="1:6" x14ac:dyDescent="0.3">
@@ -11322,7 +11322,7 @@
         <v>24</v>
       </c>
       <c r="F542" s="4">
-        <v>5.5358291080000006</v>
+        <v>13.83957277</v>
       </c>
     </row>
     <row r="543" spans="1:6" x14ac:dyDescent="0.3">
@@ -11362,7 +11362,7 @@
         <v>21</v>
       </c>
       <c r="F544" s="4">
-        <v>3.5194568680000007</v>
+        <v>8.7986421700000008</v>
       </c>
     </row>
     <row r="545" spans="1:6" x14ac:dyDescent="0.3">
@@ -11422,7 +11422,7 @@
         <v>11</v>
       </c>
       <c r="F547" s="4">
-        <v>6.7606221959999999</v>
+        <v>16.90155549</v>
       </c>
     </row>
     <row r="548" spans="1:6" x14ac:dyDescent="0.3">
@@ -11462,7 +11462,7 @@
         <v>24</v>
       </c>
       <c r="F549" s="4">
-        <v>0.66934192400000003</v>
+        <v>1.67335481</v>
       </c>
     </row>
     <row r="550" spans="1:6" x14ac:dyDescent="0.3">
@@ -11482,7 +11482,7 @@
         <v>23</v>
       </c>
       <c r="F550" s="4">
-        <v>8.796785916000001</v>
+        <v>21.991964790000001</v>
       </c>
     </row>
     <row r="551" spans="1:6" x14ac:dyDescent="0.3">
@@ -11502,7 +11502,7 @@
         <v>14</v>
       </c>
       <c r="F551" s="4">
-        <v>14.514279156000001</v>
+        <v>36.285697890000002</v>
       </c>
     </row>
     <row r="552" spans="1:6" x14ac:dyDescent="0.3">
@@ -11542,7 +11542,7 @@
         <v>11</v>
       </c>
       <c r="F553" s="4">
-        <v>4.7237974720000002</v>
+        <v>11.809493679999999</v>
       </c>
     </row>
     <row r="554" spans="1:6" x14ac:dyDescent="0.3">
@@ -11582,7 +11582,7 @@
         <v>21</v>
       </c>
       <c r="F555" s="4">
-        <v>0.63331923200000007</v>
+        <v>1.5832980800000001</v>
       </c>
     </row>
     <row r="556" spans="1:6" x14ac:dyDescent="0.3">
@@ -11602,7 +11602,7 @@
         <v>26</v>
       </c>
       <c r="F556" s="4">
-        <v>18.641530616000001</v>
+        <v>46.60382654</v>
       </c>
     </row>
     <row r="557" spans="1:6" x14ac:dyDescent="0.3">
@@ -11642,7 +11642,7 @@
         <v>15</v>
       </c>
       <c r="F558" s="4">
-        <v>0.97635532000000014</v>
+        <v>2.4408883000000001</v>
       </c>
     </row>
     <row r="559" spans="1:6" x14ac:dyDescent="0.3">
@@ -11662,7 +11662,7 @@
         <v>23</v>
       </c>
       <c r="F559" s="4">
-        <v>4.0220706360000005</v>
+        <v>10.05517659</v>
       </c>
     </row>
     <row r="560" spans="1:6" x14ac:dyDescent="0.3">
@@ -11682,7 +11682,7 @@
         <v>14</v>
       </c>
       <c r="F560" s="4">
-        <v>16.358165592000002</v>
+        <v>40.895413980000001</v>
       </c>
     </row>
     <row r="561" spans="1:6" x14ac:dyDescent="0.3">
@@ -11702,7 +11702,7 @@
         <v>15</v>
       </c>
       <c r="F561" s="4">
-        <v>0.23175657200000002</v>
+        <v>0.57939143000000004</v>
       </c>
     </row>
     <row r="562" spans="1:6" x14ac:dyDescent="0.3">
@@ -11722,7 +11722,7 @@
         <v>14</v>
       </c>
       <c r="F562" s="4">
-        <v>36.312628172000004</v>
+        <v>90.781570430000002</v>
       </c>
     </row>
     <row r="563" spans="1:6" x14ac:dyDescent="0.3">
@@ -11742,7 +11742,7 @@
         <v>23</v>
       </c>
       <c r="F563" s="4">
-        <v>26.688485415999999</v>
+        <v>66.721213539999994</v>
       </c>
     </row>
     <row r="564" spans="1:6" x14ac:dyDescent="0.3">
@@ -11762,7 +11762,7 @@
         <v>20</v>
       </c>
       <c r="F564" s="4">
-        <v>106.991863948</v>
+        <v>267.47965986999998</v>
       </c>
     </row>
     <row r="565" spans="1:6" x14ac:dyDescent="0.3">
@@ -11782,7 +11782,7 @@
         <v>15</v>
       </c>
       <c r="F565" s="4">
-        <v>0.26159244799999998</v>
+        <v>0.65398111999999997</v>
       </c>
     </row>
     <row r="566" spans="1:6" x14ac:dyDescent="0.3">
@@ -11802,7 +11802,7 @@
         <v>23</v>
       </c>
       <c r="F566" s="4">
-        <v>3.7644148080000002</v>
+        <v>9.4110370200000002</v>
       </c>
     </row>
     <row r="567" spans="1:6" x14ac:dyDescent="0.3">
@@ -11822,7 +11822,7 @@
         <v>27</v>
       </c>
       <c r="F567" s="4">
-        <v>0.25460265199999998</v>
+        <v>0.63650662999999996</v>
       </c>
     </row>
     <row r="568" spans="1:6" x14ac:dyDescent="0.3">
@@ -11842,7 +11842,7 @@
         <v>15</v>
       </c>
       <c r="F568" s="4">
-        <v>1.4303818640000001</v>
+        <v>3.5759546599999998</v>
       </c>
     </row>
     <row r="569" spans="1:6" x14ac:dyDescent="0.3">
@@ -11922,7 +11922,7 @@
         <v>8</v>
       </c>
       <c r="F572" s="4">
-        <v>13.879278132</v>
+        <v>34.698195329999997</v>
       </c>
     </row>
     <row r="573" spans="1:6" x14ac:dyDescent="0.3">
@@ -11942,7 +11942,7 @@
         <v>8</v>
       </c>
       <c r="F573" s="4">
-        <v>18.190242692000002</v>
+        <v>45.475606730000003</v>
       </c>
     </row>
     <row r="574" spans="1:6" x14ac:dyDescent="0.3">
@@ -12002,7 +12002,7 @@
         <v>23</v>
       </c>
       <c r="F576" s="4">
-        <v>6.629256968</v>
+        <v>16.57314242</v>
       </c>
     </row>
     <row r="577" spans="1:6" x14ac:dyDescent="0.3">
@@ -12022,7 +12022,7 @@
         <v>18</v>
       </c>
       <c r="F577" s="4">
-        <v>33.71587968</v>
+        <v>84.289699200000001</v>
       </c>
     </row>
     <row r="578" spans="1:6" x14ac:dyDescent="0.3">
@@ -12062,7 +12062,7 @@
         <v>14</v>
       </c>
       <c r="F579" s="4">
-        <v>30.422739116000002</v>
+        <v>76.056847790000006</v>
       </c>
     </row>
     <row r="580" spans="1:6" x14ac:dyDescent="0.3">
@@ -12082,7 +12082,7 @@
         <v>23</v>
       </c>
       <c r="F580" s="4">
-        <v>4.0523203240000001</v>
+        <v>10.13080081</v>
       </c>
     </row>
     <row r="581" spans="1:6" x14ac:dyDescent="0.3">
@@ -12102,7 +12102,7 @@
         <v>13</v>
       </c>
       <c r="F581" s="4">
-        <v>4.8420032000000002E-2</v>
+        <v>0.12105008</v>
       </c>
     </row>
     <row r="582" spans="1:6" x14ac:dyDescent="0.3">
@@ -12122,7 +12122,7 @@
         <v>27</v>
       </c>
       <c r="F582" s="4">
-        <v>2.5378601520000004</v>
+        <v>6.34465038</v>
       </c>
     </row>
     <row r="583" spans="1:6" x14ac:dyDescent="0.3">
@@ -12142,7 +12142,7 @@
         <v>20</v>
       </c>
       <c r="F583" s="4">
-        <v>21.439179492000001</v>
+        <v>53.597948729999999</v>
       </c>
     </row>
     <row r="584" spans="1:6" x14ac:dyDescent="0.3">
@@ -12162,7 +12162,7 @@
         <v>24</v>
       </c>
       <c r="F584" s="4">
-        <v>4.6946896440000003</v>
+        <v>11.736724110000001</v>
       </c>
     </row>
     <row r="585" spans="1:6" x14ac:dyDescent="0.3">
@@ -12202,7 +12202,7 @@
         <v>14</v>
       </c>
       <c r="F586" s="4">
-        <v>30.387053288000001</v>
+        <v>75.967633219999996</v>
       </c>
     </row>
     <row r="587" spans="1:6" x14ac:dyDescent="0.3">
@@ -12242,7 +12242,7 @@
         <v>26</v>
       </c>
       <c r="F588" s="4">
-        <v>21.112837052000003</v>
+        <v>52.782092630000001</v>
       </c>
     </row>
     <row r="589" spans="1:6" x14ac:dyDescent="0.3">
@@ -12262,7 +12262,7 @@
         <v>15</v>
       </c>
       <c r="F589" s="4">
-        <v>0.16041251200000001</v>
+        <v>0.40103127999999999</v>
       </c>
     </row>
     <row r="590" spans="1:6" x14ac:dyDescent="0.3">
@@ -12282,7 +12282,7 @@
         <v>20</v>
       </c>
       <c r="F590" s="4">
-        <v>16.26074998</v>
+        <v>40.65187495</v>
       </c>
     </row>
     <row r="591" spans="1:6" x14ac:dyDescent="0.3">
@@ -12302,7 +12302,7 @@
         <v>8</v>
       </c>
       <c r="F591" s="4">
-        <v>15.998361552</v>
+        <v>39.99590388</v>
       </c>
     </row>
     <row r="592" spans="1:6" x14ac:dyDescent="0.3">
@@ -12342,7 +12342,7 @@
         <v>18</v>
       </c>
       <c r="F593" s="4">
-        <v>108.352425544</v>
+        <v>270.88106385999998</v>
       </c>
     </row>
     <row r="594" spans="1:6" x14ac:dyDescent="0.3">
@@ -12362,7 +12362,7 @@
         <v>15</v>
       </c>
       <c r="F594" s="4">
-        <v>1.0832026160000001</v>
+        <v>2.70800654</v>
       </c>
     </row>
     <row r="595" spans="1:6" x14ac:dyDescent="0.3">
@@ -12382,7 +12382,7 @@
         <v>18</v>
       </c>
       <c r="F595" s="4">
-        <v>31.265773648</v>
+        <v>78.164434119999996</v>
       </c>
     </row>
     <row r="596" spans="1:6" x14ac:dyDescent="0.3">
@@ -12402,7 +12402,7 @@
         <v>23</v>
       </c>
       <c r="F596" s="4">
-        <v>9.3596629160000013</v>
+        <v>23.399157290000002</v>
       </c>
     </row>
     <row r="597" spans="1:6" x14ac:dyDescent="0.3">
@@ -12422,7 +12422,7 @@
         <v>13</v>
       </c>
       <c r="F597" s="4">
-        <v>-1.0268706000000001</v>
+        <v>-2.5671765</v>
       </c>
     </row>
     <row r="598" spans="1:6" x14ac:dyDescent="0.3">
@@ -12442,7 +12442,7 @@
         <v>21</v>
       </c>
       <c r="F598" s="4">
-        <v>3.2492725040000003</v>
+        <v>8.1231812600000008</v>
       </c>
     </row>
     <row r="599" spans="1:6" x14ac:dyDescent="0.3">
@@ -12462,7 +12462,7 @@
         <v>27</v>
       </c>
       <c r="F599" s="4">
-        <v>1.9775879400000003</v>
+        <v>4.9439698500000002</v>
       </c>
     </row>
     <row r="600" spans="1:6" x14ac:dyDescent="0.3">
@@ -12482,7 +12482,7 @@
         <v>13</v>
       </c>
       <c r="F600" s="4">
-        <v>-0.29416971200000003</v>
+        <v>-0.73542428000000004</v>
       </c>
     </row>
     <row r="601" spans="1:6" x14ac:dyDescent="0.3">
@@ -12502,7 +12502,7 @@
         <v>11</v>
       </c>
       <c r="F601" s="4">
-        <v>4.4716628759999999</v>
+        <v>11.17915719</v>
       </c>
     </row>
     <row r="602" spans="1:6" x14ac:dyDescent="0.3">
@@ -12522,7 +12522,7 @@
         <v>14</v>
       </c>
       <c r="F602" s="4">
-        <v>14.303051864</v>
+        <v>35.757629659999999</v>
       </c>
     </row>
     <row r="603" spans="1:6" x14ac:dyDescent="0.3">
@@ -12542,7 +12542,7 @@
         <v>27</v>
       </c>
       <c r="F603" s="4">
-        <v>3.459429144</v>
+        <v>8.6485728599999998</v>
       </c>
     </row>
     <row r="604" spans="1:6" x14ac:dyDescent="0.3">
@@ -12562,7 +12562,7 @@
         <v>20</v>
       </c>
       <c r="F604" s="4">
-        <v>15.465396916000001</v>
+        <v>38.663492290000001</v>
       </c>
     </row>
     <row r="605" spans="1:6" x14ac:dyDescent="0.3">
@@ -12622,7 +12622,7 @@
         <v>23</v>
       </c>
       <c r="F607" s="4">
-        <v>12.052425108000001</v>
+        <v>30.13106277</v>
       </c>
     </row>
     <row r="608" spans="1:6" x14ac:dyDescent="0.3">
@@ -12662,7 +12662,7 @@
         <v>8</v>
       </c>
       <c r="F609" s="4">
-        <v>18.526323428000001</v>
+        <v>46.315808570000002</v>
       </c>
     </row>
     <row r="610" spans="1:6" x14ac:dyDescent="0.3">
@@ -12682,7 +12682,7 @@
         <v>23</v>
       </c>
       <c r="F610" s="4">
-        <v>19.035912419999999</v>
+        <v>47.589781049999999</v>
       </c>
     </row>
     <row r="611" spans="1:6" x14ac:dyDescent="0.3">
@@ -12702,7 +12702,7 @@
         <v>20</v>
       </c>
       <c r="F611" s="4">
-        <v>120.68317023600001</v>
+        <v>301.70792559</v>
       </c>
     </row>
     <row r="612" spans="1:6" x14ac:dyDescent="0.3">
@@ -12742,7 +12742,7 @@
         <v>14</v>
       </c>
       <c r="F613" s="4">
-        <v>23.769290928000004</v>
+        <v>59.423227320000002</v>
       </c>
     </row>
     <row r="614" spans="1:6" x14ac:dyDescent="0.3">
@@ -12762,7 +12762,7 @@
         <v>15</v>
       </c>
       <c r="F614" s="4">
-        <v>1.0204613280000001</v>
+        <v>2.5511533200000001</v>
       </c>
     </row>
     <row r="615" spans="1:6" x14ac:dyDescent="0.3">
@@ -12782,7 +12782,7 @@
         <v>14</v>
       </c>
       <c r="F615" s="4">
-        <v>15.605094520000002</v>
+        <v>39.0127363</v>
       </c>
     </row>
     <row r="616" spans="1:6" x14ac:dyDescent="0.3">
@@ -12802,7 +12802,7 @@
         <v>15</v>
       </c>
       <c r="F616" s="4">
-        <v>0.146961708</v>
+        <v>0.36740426999999998</v>
       </c>
     </row>
     <row r="617" spans="1:6" x14ac:dyDescent="0.3">
@@ -12822,7 +12822,7 @@
         <v>14</v>
       </c>
       <c r="F617" s="4">
-        <v>31.024573623999999</v>
+        <v>77.561434059999996</v>
       </c>
     </row>
     <row r="618" spans="1:6" x14ac:dyDescent="0.3">
@@ -12842,7 +12842,7 @@
         <v>13</v>
       </c>
       <c r="F618" s="4">
-        <v>-0.26525026000000002</v>
+        <v>-0.66312565000000001</v>
       </c>
     </row>
     <row r="619" spans="1:6" x14ac:dyDescent="0.3">
@@ -12882,7 +12882,7 @@
         <v>14</v>
       </c>
       <c r="F620" s="4">
-        <v>15.372774920000001</v>
+        <v>38.431937300000001</v>
       </c>
     </row>
     <row r="621" spans="1:6" x14ac:dyDescent="0.3">
@@ -12902,7 +12902,7 @@
         <v>27</v>
       </c>
       <c r="F621" s="4">
-        <v>8.9806698560000005</v>
+        <v>22.45167464</v>
       </c>
     </row>
     <row r="622" spans="1:6" x14ac:dyDescent="0.3">
@@ -12942,7 +12942,7 @@
         <v>18</v>
       </c>
       <c r="F623" s="4">
-        <v>32.969705840000003</v>
+        <v>82.424264600000001</v>
       </c>
     </row>
     <row r="624" spans="1:6" x14ac:dyDescent="0.3">
@@ -12962,7 +12962,7 @@
         <v>20</v>
       </c>
       <c r="F624" s="4">
-        <v>29.130054632000004</v>
+        <v>72.825136580000006</v>
       </c>
     </row>
     <row r="625" spans="1:6" x14ac:dyDescent="0.3">
@@ -12982,7 +12982,7 @@
         <v>14</v>
       </c>
       <c r="F625" s="4">
-        <v>30.453836768000002</v>
+        <v>76.134591920000005</v>
       </c>
     </row>
     <row r="626" spans="1:6" x14ac:dyDescent="0.3">
@@ -13002,7 +13002,7 @@
         <v>23</v>
       </c>
       <c r="F626" s="4">
-        <v>7.341526408</v>
+        <v>18.35381602</v>
       </c>
     </row>
     <row r="627" spans="1:6" x14ac:dyDescent="0.3">
@@ -13022,7 +13022,7 @@
         <v>21</v>
       </c>
       <c r="F627" s="4">
-        <v>0.87039620000000006</v>
+        <v>2.1759905000000002</v>
       </c>
     </row>
     <row r="628" spans="1:6" x14ac:dyDescent="0.3">
@@ -13042,7 +13042,7 @@
         <v>15</v>
       </c>
       <c r="F628" s="4">
-        <v>0.27683987999999998</v>
+        <v>0.69209969999999998</v>
       </c>
     </row>
     <row r="629" spans="1:6" x14ac:dyDescent="0.3">
@@ -13102,7 +13102,7 @@
         <v>15</v>
       </c>
       <c r="F631" s="4">
-        <v>1.001487912</v>
+        <v>2.50371978</v>
       </c>
     </row>
     <row r="632" spans="1:6" x14ac:dyDescent="0.3">
@@ -13122,7 +13122,7 @@
         <v>23</v>
       </c>
       <c r="F632" s="4">
-        <v>6.068057552</v>
+        <v>15.170143879999999</v>
       </c>
     </row>
     <row r="633" spans="1:6" x14ac:dyDescent="0.3">
@@ -13142,7 +13142,7 @@
         <v>11</v>
       </c>
       <c r="F633" s="4">
-        <v>3.1192330400000001</v>
+        <v>7.7980825999999999</v>
       </c>
     </row>
     <row r="634" spans="1:6" x14ac:dyDescent="0.3">
@@ -13162,7 +13162,7 @@
         <v>13</v>
       </c>
       <c r="F634" s="4">
-        <v>-1.02393442</v>
+        <v>-2.5598360499999999</v>
       </c>
     </row>
     <row r="635" spans="1:6" x14ac:dyDescent="0.3">
@@ -13182,7 +13182,7 @@
         <v>27</v>
       </c>
       <c r="F635" s="4">
-        <v>9.7989943000000004</v>
+        <v>24.497485749999999</v>
       </c>
     </row>
     <row r="636" spans="1:6" x14ac:dyDescent="0.3">
@@ -13202,7 +13202,7 @@
         <v>14</v>
       </c>
       <c r="F636" s="4">
-        <v>16.106977232000002</v>
+        <v>40.26744308</v>
       </c>
     </row>
     <row r="637" spans="1:6" x14ac:dyDescent="0.3">
@@ -13222,7 +13222,7 @@
         <v>27</v>
       </c>
       <c r="F637" s="4">
-        <v>5.43991164</v>
+        <v>13.599779099999999</v>
       </c>
     </row>
     <row r="638" spans="1:6" x14ac:dyDescent="0.3">
@@ -13242,7 +13242,7 @@
         <v>14</v>
       </c>
       <c r="F638" s="4">
-        <v>30.387053288000001</v>
+        <v>75.967633219999996</v>
       </c>
     </row>
     <row r="639" spans="1:6" x14ac:dyDescent="0.3">
@@ -13262,7 +13262,7 @@
         <v>13</v>
       </c>
       <c r="F639" s="4">
-        <v>8.804816E-3</v>
+        <v>2.201204E-2</v>
       </c>
     </row>
     <row r="640" spans="1:6" x14ac:dyDescent="0.3">
@@ -13282,7 +13282,7 @@
         <v>13</v>
       </c>
       <c r="F640" s="4">
-        <v>-0.12010032799999999</v>
+        <v>-0.30025081999999997</v>
       </c>
     </row>
     <row r="641" spans="1:6" x14ac:dyDescent="0.3">
@@ -13302,7 +13302,7 @@
         <v>23</v>
       </c>
       <c r="F641" s="4">
-        <v>7.3662614039999994</v>
+        <v>18.415653509999999</v>
       </c>
     </row>
     <row r="642" spans="1:6" x14ac:dyDescent="0.3">
@@ -13322,7 +13322,7 @@
         <v>20</v>
       </c>
       <c r="F642" s="4">
-        <v>148.05793004</v>
+        <v>370.14482509999999</v>
       </c>
     </row>
     <row r="643" spans="1:6" x14ac:dyDescent="0.3">
@@ -13342,7 +13342,7 @@
         <v>19</v>
       </c>
       <c r="F643" s="4">
-        <v>-0.11472506</v>
+        <v>-0.28681265</v>
       </c>
     </row>
     <row r="644" spans="1:6" x14ac:dyDescent="0.3">
@@ -13362,7 +13362,7 @@
         <v>23</v>
       </c>
       <c r="F644" s="4">
-        <v>18.750213651999999</v>
+        <v>46.875534129999998</v>
       </c>
     </row>
     <row r="645" spans="1:6" x14ac:dyDescent="0.3">
@@ -13382,7 +13382,7 @@
         <v>21</v>
       </c>
       <c r="F645" s="4">
-        <v>0.53322533999999999</v>
+        <v>1.33306335</v>
       </c>
     </row>
     <row r="646" spans="1:6" x14ac:dyDescent="0.3">
@@ -13422,7 +13422,7 @@
         <v>19</v>
       </c>
       <c r="F647" s="4">
-        <v>-2.7065196000000003E-2</v>
+        <v>-6.7662990000000006E-2</v>
       </c>
     </row>
     <row r="648" spans="1:6" x14ac:dyDescent="0.3">
@@ -13442,7 +13442,7 @@
         <v>21</v>
       </c>
       <c r="F648" s="4">
-        <v>0.64678273200000003</v>
+        <v>1.6169568299999999</v>
       </c>
     </row>
     <row r="649" spans="1:6" x14ac:dyDescent="0.3">
@@ -13462,7 +13462,7 @@
         <v>23</v>
       </c>
       <c r="F649" s="4">
-        <v>3.8860787520000004</v>
+        <v>9.7151968800000006</v>
       </c>
     </row>
     <row r="650" spans="1:6" x14ac:dyDescent="0.3">
@@ -13482,7 +13482,7 @@
         <v>11</v>
       </c>
       <c r="F650" s="4">
-        <v>4.5974977880000001</v>
+        <v>11.493744469999999</v>
       </c>
     </row>
     <row r="651" spans="1:6" x14ac:dyDescent="0.3">
@@ -13502,7 +13502,7 @@
         <v>26</v>
       </c>
       <c r="F651" s="4">
-        <v>23.399446064000003</v>
+        <v>58.49861516</v>
       </c>
     </row>
     <row r="652" spans="1:6" x14ac:dyDescent="0.3">
@@ -13522,7 +13522,7 @@
         <v>14</v>
       </c>
       <c r="F652" s="4">
-        <v>15.372774920000001</v>
+        <v>38.431937300000001</v>
       </c>
     </row>
     <row r="653" spans="1:6" x14ac:dyDescent="0.3">
@@ -13542,7 +13542,7 @@
         <v>11</v>
       </c>
       <c r="F653" s="4">
-        <v>7.1444887560000003</v>
+        <v>17.861221889999999</v>
       </c>
     </row>
     <row r="654" spans="1:6" x14ac:dyDescent="0.3">
@@ -13562,7 +13562,7 @@
         <v>15</v>
       </c>
       <c r="F654" s="4">
-        <v>0.27471062000000002</v>
+        <v>0.68677655000000004</v>
       </c>
     </row>
     <row r="655" spans="1:6" x14ac:dyDescent="0.3">
@@ -13622,7 +13622,7 @@
         <v>20</v>
       </c>
       <c r="F657" s="4">
-        <v>36.138037020000006</v>
+        <v>90.345092550000004</v>
       </c>
     </row>
     <row r="658" spans="1:6" x14ac:dyDescent="0.3">
@@ -13642,7 +13642,7 @@
         <v>23</v>
       </c>
       <c r="F658" s="4">
-        <v>7.4120334920000008</v>
+        <v>18.530083730000001</v>
       </c>
     </row>
     <row r="659" spans="1:6" x14ac:dyDescent="0.3">
@@ -13662,7 +13662,7 @@
         <v>14</v>
       </c>
       <c r="F659" s="4">
-        <v>31.306123604</v>
+        <v>78.265309009999996</v>
       </c>
     </row>
     <row r="660" spans="1:6" x14ac:dyDescent="0.3">
@@ -13682,7 +13682,7 @@
         <v>13</v>
       </c>
       <c r="F660" s="4">
-        <v>-0.84767976800000011</v>
+        <v>-2.1191994200000002</v>
       </c>
     </row>
     <row r="661" spans="1:6" x14ac:dyDescent="0.3">
@@ -13702,7 +13702,7 @@
         <v>20</v>
       </c>
       <c r="F661" s="4">
-        <v>16.851452876</v>
+        <v>42.128632189999998</v>
       </c>
     </row>
     <row r="662" spans="1:6" x14ac:dyDescent="0.3">
@@ -13722,7 +13722,7 @@
         <v>20</v>
       </c>
       <c r="F662" s="4">
-        <v>29.253943732</v>
+        <v>73.134859329999998</v>
       </c>
     </row>
     <row r="663" spans="1:6" x14ac:dyDescent="0.3">
@@ -13742,7 +13742,7 @@
         <v>13</v>
       </c>
       <c r="F663" s="4">
-        <v>-0.23288149200000002</v>
+        <v>-0.58220373000000003</v>
       </c>
     </row>
     <row r="664" spans="1:6" x14ac:dyDescent="0.3">
@@ -13782,7 +13782,7 @@
         <v>14</v>
       </c>
       <c r="F665" s="4">
-        <v>24.276315547999999</v>
+        <v>60.690788869999999</v>
       </c>
     </row>
     <row r="666" spans="1:6" x14ac:dyDescent="0.3">
@@ -13802,7 +13802,7 @@
         <v>19</v>
       </c>
       <c r="F666" s="4">
-        <v>-4.7332824000000003E-2</v>
+        <v>-0.11833206</v>
       </c>
     </row>
     <row r="667" spans="1:6" x14ac:dyDescent="0.3">
@@ -13842,7 +13842,7 @@
         <v>14</v>
       </c>
       <c r="F668" s="4">
-        <v>27.869209136000002</v>
+        <v>69.673022840000002</v>
       </c>
     </row>
     <row r="669" spans="1:6" x14ac:dyDescent="0.3">
@@ -13862,7 +13862,7 @@
         <v>21</v>
       </c>
       <c r="F669" s="4">
-        <v>0.64458384800000001</v>
+        <v>1.61145962</v>
       </c>
     </row>
     <row r="670" spans="1:6" x14ac:dyDescent="0.3">
@@ -13882,7 +13882,7 @@
         <v>21</v>
       </c>
       <c r="F670" s="4">
-        <v>0.44688472000000001</v>
+        <v>1.1172118</v>
       </c>
     </row>
     <row r="671" spans="1:6" x14ac:dyDescent="0.3">
@@ -13922,7 +13922,7 @@
         <v>24</v>
       </c>
       <c r="F672" s="4">
-        <v>2.0754315720000003</v>
+        <v>5.1885789300000003</v>
       </c>
     </row>
     <row r="673" spans="1:6" x14ac:dyDescent="0.3">
@@ -13942,7 +13942,7 @@
         <v>14</v>
       </c>
       <c r="F673" s="4">
-        <v>25.331356172</v>
+        <v>63.328390429999999</v>
       </c>
     </row>
     <row r="674" spans="1:6" x14ac:dyDescent="0.3">
@@ -13982,7 +13982,7 @@
         <v>23</v>
       </c>
       <c r="F675" s="4">
-        <v>6.4737195840000004</v>
+        <v>16.18429896</v>
       </c>
     </row>
     <row r="676" spans="1:6" x14ac:dyDescent="0.3">
@@ -14022,7 +14022,7 @@
         <v>13</v>
       </c>
       <c r="F677" s="4">
-        <v>4.8420032000000002E-2</v>
+        <v>0.12105008</v>
       </c>
     </row>
     <row r="678" spans="1:6" x14ac:dyDescent="0.3">
@@ -14042,7 +14042,7 @@
         <v>14</v>
       </c>
       <c r="F678" s="4">
-        <v>22.814477148000002</v>
+        <v>57.036192870000001</v>
       </c>
     </row>
     <row r="679" spans="1:6" x14ac:dyDescent="0.3">
@@ -14062,7 +14062,7 @@
         <v>24</v>
       </c>
       <c r="F679" s="4">
-        <v>7.4555022840000014</v>
+        <v>18.638755710000002</v>
       </c>
     </row>
     <row r="680" spans="1:6" x14ac:dyDescent="0.3">
@@ -14082,7 +14082,7 @@
         <v>15</v>
       </c>
       <c r="F680" s="4">
-        <v>0.13952175200000003</v>
+        <v>0.34880438000000002</v>
       </c>
     </row>
     <row r="681" spans="1:6" x14ac:dyDescent="0.3">
@@ -14102,7 +14102,7 @@
         <v>18</v>
       </c>
       <c r="F681" s="4">
-        <v>106.86658887999999</v>
+        <v>267.16647219999999</v>
       </c>
     </row>
     <row r="682" spans="1:6" x14ac:dyDescent="0.3">
@@ -14142,7 +14142,7 @@
         <v>13</v>
       </c>
       <c r="F683" s="4">
-        <v>-0.92807985599999998</v>
+        <v>-2.3201996399999998</v>
       </c>
     </row>
     <row r="684" spans="1:6" x14ac:dyDescent="0.3">
@@ -14162,7 +14162,7 @@
         <v>8</v>
       </c>
       <c r="F684" s="4">
-        <v>32.372885115999999</v>
+        <v>80.932212789999994</v>
       </c>
     </row>
     <row r="685" spans="1:6" x14ac:dyDescent="0.3">
@@ -14182,7 +14182,7 @@
         <v>23</v>
       </c>
       <c r="F685" s="4">
-        <v>7.596831292000001</v>
+        <v>18.992078230000001</v>
       </c>
     </row>
     <row r="686" spans="1:6" x14ac:dyDescent="0.3">
@@ -14202,7 +14202,7 @@
         <v>15</v>
       </c>
       <c r="F686" s="4">
-        <v>1.037912572</v>
+        <v>2.5947814299999998</v>
       </c>
     </row>
     <row r="687" spans="1:6" x14ac:dyDescent="0.3">
@@ -14222,7 +14222,7 @@
         <v>23</v>
       </c>
       <c r="F687" s="4">
-        <v>3.703963356</v>
+        <v>9.2599083899999997</v>
       </c>
     </row>
     <row r="688" spans="1:6" x14ac:dyDescent="0.3">
@@ -14262,7 +14262,7 @@
         <v>23</v>
       </c>
       <c r="F689" s="4">
-        <v>6.0272353600000006</v>
+        <v>15.068088400000001</v>
       </c>
     </row>
     <row r="690" spans="1:6" x14ac:dyDescent="0.3">
@@ -14282,7 +14282,7 @@
         <v>21</v>
       </c>
       <c r="F690" s="4">
-        <v>3.6155212120000004</v>
+        <v>9.0388030300000004</v>
       </c>
     </row>
     <row r="691" spans="1:6" x14ac:dyDescent="0.3">
@@ -14302,7 +14302,7 @@
         <v>8</v>
       </c>
       <c r="F691" s="4">
-        <v>22.178418468000004</v>
+        <v>55.446046170000002</v>
       </c>
     </row>
     <row r="692" spans="1:6" x14ac:dyDescent="0.3">
@@ -14322,7 +14322,7 @@
         <v>21</v>
       </c>
       <c r="F692" s="4">
-        <v>0.63166813600000005</v>
+        <v>1.5791703399999999</v>
       </c>
     </row>
     <row r="693" spans="1:6" x14ac:dyDescent="0.3">
@@ -14342,7 +14342,7 @@
         <v>24</v>
       </c>
       <c r="F693" s="4">
-        <v>0.604791788</v>
+        <v>1.51197947</v>
       </c>
     </row>
     <row r="694" spans="1:6" x14ac:dyDescent="0.3">
@@ -14362,7 +14362,7 @@
         <v>14</v>
       </c>
       <c r="F694" s="4">
-        <v>28.454063739999999</v>
+        <v>71.135159349999995</v>
       </c>
     </row>
     <row r="695" spans="1:6" x14ac:dyDescent="0.3">
@@ -14382,7 +14382,7 @@
         <v>8</v>
       </c>
       <c r="F695" s="4">
-        <v>32.848725760000001</v>
+        <v>82.121814400000005</v>
       </c>
     </row>
     <row r="696" spans="1:6" x14ac:dyDescent="0.3">
@@ -14442,7 +14442,7 @@
         <v>23</v>
       </c>
       <c r="F698" s="4">
-        <v>13.014306560000001</v>
+        <v>32.5357664</v>
       </c>
     </row>
     <row r="699" spans="1:6" x14ac:dyDescent="0.3">
@@ -14462,7 +14462,7 @@
         <v>26</v>
       </c>
       <c r="F699" s="4">
-        <v>20.528691984000002</v>
+        <v>51.321729959999999</v>
       </c>
     </row>
     <row r="700" spans="1:6" x14ac:dyDescent="0.3">
@@ -14482,7 +14482,7 @@
         <v>23</v>
       </c>
       <c r="F700" s="4">
-        <v>6.6108411760000001</v>
+        <v>16.527102939999999</v>
       </c>
     </row>
     <row r="701" spans="1:6" x14ac:dyDescent="0.3">
@@ -14502,7 +14502,7 @@
         <v>19</v>
       </c>
       <c r="F701" s="4">
-        <v>-3.0687991999999997E-2</v>
+        <v>-7.6719979999999993E-2</v>
       </c>
     </row>
     <row r="702" spans="1:6" x14ac:dyDescent="0.3">
@@ -14522,7 +14522,7 @@
         <v>15</v>
       </c>
       <c r="F702" s="4">
-        <v>0.93463354400000009</v>
+        <v>2.3365838600000002</v>
       </c>
     </row>
     <row r="703" spans="1:6" x14ac:dyDescent="0.3">
@@ -14542,7 +14542,7 @@
         <v>14</v>
       </c>
       <c r="F703" s="4">
-        <v>31.885985144000003</v>
+        <v>79.71496286</v>
       </c>
     </row>
     <row r="704" spans="1:6" x14ac:dyDescent="0.3">
@@ -14562,7 +14562,7 @@
         <v>15</v>
       </c>
       <c r="F704" s="4">
-        <v>0.13354353199999999</v>
+        <v>0.33385883</v>
       </c>
     </row>
     <row r="705" spans="1:6" x14ac:dyDescent="0.3">
@@ -14582,7 +14582,7 @@
         <v>15</v>
       </c>
       <c r="F705" s="4">
-        <v>0.24866013200000003</v>
+        <v>0.62165033000000003</v>
       </c>
     </row>
     <row r="706" spans="1:6" x14ac:dyDescent="0.3">
@@ -14622,7 +14622,7 @@
         <v>13</v>
       </c>
       <c r="F707" s="4">
-        <v>-0.92807985599999998</v>
+        <v>-2.3201996399999998</v>
       </c>
     </row>
     <row r="708" spans="1:6" x14ac:dyDescent="0.3">
@@ -14682,7 +14682,7 @@
         <v>14</v>
       </c>
       <c r="F710" s="4">
-        <v>31.885985144000003</v>
+        <v>79.71496286</v>
       </c>
     </row>
     <row r="711" spans="1:6" x14ac:dyDescent="0.3">
@@ -14702,7 +14702,7 @@
         <v>21</v>
       </c>
       <c r="F711" s="4">
-        <v>0.65364522400000002</v>
+        <v>1.63411306</v>
       </c>
     </row>
     <row r="712" spans="1:6" x14ac:dyDescent="0.3">
@@ -14722,7 +14722,7 @@
         <v>13</v>
       </c>
       <c r="F712" s="4">
-        <v>-0.26187136799999999</v>
+        <v>-0.65467841999999998</v>
       </c>
     </row>
     <row r="713" spans="1:6" x14ac:dyDescent="0.3">
@@ -14742,7 +14742,7 @@
         <v>21</v>
       </c>
       <c r="F713" s="4">
-        <v>1.102607036</v>
+        <v>2.7565175900000001</v>
       </c>
     </row>
     <row r="714" spans="1:6" x14ac:dyDescent="0.3">
@@ -14762,7 +14762,7 @@
         <v>13</v>
       </c>
       <c r="F714" s="4">
-        <v>-0.248896016</v>
+        <v>-0.62224003999999999</v>
       </c>
     </row>
     <row r="715" spans="1:6" x14ac:dyDescent="0.3">
@@ -14782,7 +14782,7 @@
         <v>26</v>
       </c>
       <c r="F715" s="4">
-        <v>23.471682020000003</v>
+        <v>58.67920505</v>
       </c>
     </row>
     <row r="716" spans="1:6" x14ac:dyDescent="0.3">
@@ -14802,7 +14802,7 @@
         <v>11</v>
       </c>
       <c r="F716" s="4">
-        <v>4.6609907800000006</v>
+        <v>11.65247695</v>
       </c>
     </row>
     <row r="717" spans="1:6" x14ac:dyDescent="0.3">
@@ -14822,7 +14822,7 @@
         <v>21</v>
       </c>
       <c r="F717" s="4">
-        <v>3.9562910799999997</v>
+        <v>9.8907276999999993</v>
       </c>
     </row>
     <row r="718" spans="1:6" x14ac:dyDescent="0.3">
@@ -14842,7 +14842,7 @@
         <v>18</v>
       </c>
       <c r="F718" s="4">
-        <v>113.281254984</v>
+        <v>283.20313745999999</v>
       </c>
     </row>
     <row r="719" spans="1:6" x14ac:dyDescent="0.3">
@@ -14882,7 +14882,7 @@
         <v>11</v>
       </c>
       <c r="F720" s="4">
-        <v>3.3169852520000003</v>
+        <v>8.2924631299999998</v>
       </c>
     </row>
     <row r="721" spans="1:6" x14ac:dyDescent="0.3">
@@ -14902,7 +14902,7 @@
         <v>24</v>
       </c>
       <c r="F721" s="4">
-        <v>0.49901609999999996</v>
+        <v>1.2475402499999999</v>
       </c>
     </row>
     <row r="722" spans="1:6" x14ac:dyDescent="0.3">
@@ -14922,7 +14922,7 @@
         <v>13</v>
       </c>
       <c r="F722" s="4">
-        <v>-0.22535959600000002</v>
+        <v>-0.56339899000000004</v>
       </c>
     </row>
     <row r="723" spans="1:6" x14ac:dyDescent="0.3">
@@ -14962,7 +14962,7 @@
         <v>13</v>
       </c>
       <c r="F724" s="4">
-        <v>-0.25090295200000001</v>
+        <v>-0.62725737999999998</v>
       </c>
     </row>
     <row r="725" spans="1:6" x14ac:dyDescent="0.3">
@@ -14982,7 +14982,7 @@
         <v>8</v>
       </c>
       <c r="F725" s="4">
-        <v>18.344066252000001</v>
+        <v>45.860165629999997</v>
       </c>
     </row>
     <row r="726" spans="1:6" x14ac:dyDescent="0.3">
@@ -15022,7 +15022,7 @@
         <v>11</v>
       </c>
       <c r="F727" s="4">
-        <v>4.3824113440000003</v>
+        <v>10.956028359999999</v>
       </c>
     </row>
     <row r="728" spans="1:6" x14ac:dyDescent="0.3">
@@ -15062,7 +15062,7 @@
         <v>15</v>
       </c>
       <c r="F729" s="4">
-        <v>0.22935897999999999</v>
+        <v>0.57339744999999998</v>
       </c>
     </row>
     <row r="730" spans="1:6" x14ac:dyDescent="0.3">
@@ -15162,7 +15162,7 @@
         <v>15</v>
       </c>
       <c r="F734" s="4">
-        <v>0.27671105600000001</v>
+        <v>0.69177763999999997</v>
       </c>
     </row>
     <row r="735" spans="1:6" x14ac:dyDescent="0.3">
@@ -15182,7 +15182,7 @@
         <v>21</v>
       </c>
       <c r="F735" s="4">
-        <v>0.54795442000000005</v>
+        <v>1.3698860500000001</v>
       </c>
     </row>
     <row r="736" spans="1:6" x14ac:dyDescent="0.3">
@@ -15202,7 +15202,7 @@
         <v>21</v>
       </c>
       <c r="F736" s="4">
-        <v>3.2304013720000002</v>
+        <v>8.0760034300000001</v>
       </c>
     </row>
     <row r="737" spans="1:6" x14ac:dyDescent="0.3">
@@ -15242,7 +15242,7 @@
         <v>18</v>
       </c>
       <c r="F738" s="4">
-        <v>20.980303792000001</v>
+        <v>52.450759480000002</v>
       </c>
     </row>
     <row r="739" spans="1:6" x14ac:dyDescent="0.3">
@@ -15262,7 +15262,7 @@
         <v>21</v>
       </c>
       <c r="F739" s="4">
-        <v>0.55435833199999995</v>
+        <v>1.3858958299999999</v>
       </c>
     </row>
     <row r="740" spans="1:6" x14ac:dyDescent="0.3">
@@ -15342,7 +15342,7 @@
         <v>27</v>
       </c>
       <c r="F743" s="4">
-        <v>6.5186960680000006</v>
+        <v>16.29674017</v>
       </c>
     </row>
     <row r="744" spans="1:6" x14ac:dyDescent="0.3">
@@ -15362,7 +15362,7 @@
         <v>23</v>
       </c>
       <c r="F744" s="4">
-        <v>7.3021722560000004</v>
+        <v>18.25543064</v>
       </c>
     </row>
     <row r="745" spans="1:6" x14ac:dyDescent="0.3">
@@ -15382,7 +15382,7 @@
         <v>18</v>
       </c>
       <c r="F745" s="4">
-        <v>31.413750944</v>
+        <v>78.534377359999993</v>
       </c>
     </row>
     <row r="746" spans="1:6" x14ac:dyDescent="0.3">
@@ -15422,7 +15422,7 @@
         <v>14</v>
       </c>
       <c r="F747" s="4">
-        <v>31.576099196000001</v>
+        <v>78.940247990000003</v>
       </c>
     </row>
     <row r="748" spans="1:6" x14ac:dyDescent="0.3">
@@ -15442,7 +15442,7 @@
         <v>20</v>
       </c>
       <c r="F748" s="4">
-        <v>37.669633840000003</v>
+        <v>94.1740846</v>
       </c>
     </row>
     <row r="749" spans="1:6" x14ac:dyDescent="0.3">
@@ -15462,7 +15462,7 @@
         <v>23</v>
       </c>
       <c r="F749" s="4">
-        <v>6.151310176</v>
+        <v>15.378275439999999</v>
       </c>
     </row>
     <row r="750" spans="1:6" x14ac:dyDescent="0.3">
@@ -15482,7 +15482,7 @@
         <v>18</v>
       </c>
       <c r="F750" s="4">
-        <v>35.179328900000002</v>
+        <v>87.948322250000004</v>
       </c>
     </row>
     <row r="751" spans="1:6" x14ac:dyDescent="0.3">
@@ -15502,7 +15502,7 @@
         <v>20</v>
       </c>
       <c r="F751" s="4">
-        <v>104.71814852400001</v>
+        <v>261.79537131000001</v>
       </c>
     </row>
     <row r="752" spans="1:6" x14ac:dyDescent="0.3">
@@ -15542,7 +15542,7 @@
         <v>20</v>
       </c>
       <c r="F753" s="4">
-        <v>18.599118220000001</v>
+        <v>46.497795549999999</v>
       </c>
     </row>
     <row r="754" spans="1:6" x14ac:dyDescent="0.3">
@@ -15582,7 +15582,7 @@
         <v>15</v>
       </c>
       <c r="F755" s="4">
-        <v>0.27741997200000001</v>
+        <v>0.69354992999999998</v>
       </c>
     </row>
     <row r="756" spans="1:6" x14ac:dyDescent="0.3">
@@ -15602,7 +15602,7 @@
         <v>18</v>
       </c>
       <c r="F756" s="4">
-        <v>116.52516523600001</v>
+        <v>291.31291309</v>
       </c>
     </row>
     <row r="757" spans="1:6" x14ac:dyDescent="0.3">
@@ -15622,7 +15622,7 @@
         <v>20</v>
       </c>
       <c r="F757" s="4">
-        <v>16.678357299999998</v>
+        <v>41.695893249999997</v>
       </c>
     </row>
     <row r="758" spans="1:6" x14ac:dyDescent="0.3">
@@ -15642,7 +15642,7 @@
         <v>27</v>
       </c>
       <c r="F758" s="4">
-        <v>2.8890097880000001</v>
+        <v>7.2225244699999998</v>
       </c>
     </row>
     <row r="759" spans="1:6" x14ac:dyDescent="0.3">
@@ -15662,7 +15662,7 @@
         <v>15</v>
       </c>
       <c r="F759" s="4">
-        <v>0.98270482400000003</v>
+        <v>2.45676206</v>
       </c>
     </row>
     <row r="760" spans="1:6" x14ac:dyDescent="0.3">
@@ -15702,7 +15702,7 @@
         <v>19</v>
       </c>
       <c r="F761" s="4">
-        <v>-2.6603280000000003E-2</v>
+        <v>-6.6508200000000003E-2</v>
       </c>
     </row>
     <row r="762" spans="1:6" x14ac:dyDescent="0.3">
@@ -15722,7 +15722,7 @@
         <v>8</v>
       </c>
       <c r="F762" s="4">
-        <v>12.440419236</v>
+        <v>31.101048089999999</v>
       </c>
     </row>
     <row r="763" spans="1:6" x14ac:dyDescent="0.3">
@@ -15782,7 +15782,7 @@
         <v>24</v>
       </c>
       <c r="F765" s="4">
-        <v>103.80420809600001</v>
+        <v>259.51052024000001</v>
       </c>
     </row>
     <row r="766" spans="1:6" x14ac:dyDescent="0.3">
@@ -15802,7 +15802,7 @@
         <v>13</v>
       </c>
       <c r="F766" s="4">
-        <v>-0.96973293599999999</v>
+        <v>-2.4243323399999999</v>
       </c>
     </row>
     <row r="767" spans="1:6" x14ac:dyDescent="0.3">
@@ -15822,7 +15822,7 @@
         <v>14</v>
       </c>
       <c r="F767" s="4">
-        <v>15.131618276000001</v>
+        <v>37.829045690000001</v>
       </c>
     </row>
     <row r="768" spans="1:6" x14ac:dyDescent="0.3">
@@ -15842,7 +15842,7 @@
         <v>24</v>
       </c>
       <c r="F768" s="4">
-        <v>-0.198497332</v>
+        <v>-0.49624332999999998</v>
       </c>
     </row>
     <row r="769" spans="1:6" x14ac:dyDescent="0.3">
@@ -15862,7 +15862,7 @@
         <v>11</v>
       </c>
       <c r="F769" s="4">
-        <v>4.6256196439999995</v>
+        <v>11.564049109999999</v>
       </c>
     </row>
     <row r="770" spans="1:6" x14ac:dyDescent="0.3">
@@ -15902,7 +15902,7 @@
         <v>27</v>
       </c>
       <c r="F771" s="4">
-        <v>1.397037544</v>
+        <v>3.4925938599999999</v>
       </c>
     </row>
     <row r="772" spans="1:6" x14ac:dyDescent="0.3">
@@ -15922,7 +15922,7 @@
         <v>11</v>
       </c>
       <c r="F772" s="4">
-        <v>3.2038854280000004</v>
+        <v>8.0097135700000006</v>
       </c>
     </row>
     <row r="773" spans="1:6" x14ac:dyDescent="0.3">
@@ -15942,7 +15942,7 @@
         <v>23</v>
       </c>
       <c r="F773" s="4">
-        <v>12.986775552000001</v>
+        <v>32.466938880000001</v>
       </c>
     </row>
     <row r="774" spans="1:6" x14ac:dyDescent="0.3">
@@ -15962,7 +15962,7 @@
         <v>15</v>
       </c>
       <c r="F774" s="4">
-        <v>0.23130877600000002</v>
+        <v>0.57827194000000004</v>
       </c>
     </row>
     <row r="775" spans="1:6" x14ac:dyDescent="0.3">
@@ -15982,7 +15982,7 @@
         <v>23</v>
       </c>
       <c r="F775" s="4">
-        <v>6.6259871000000006</v>
+        <v>16.564967750000001</v>
       </c>
     </row>
     <row r="776" spans="1:6" x14ac:dyDescent="0.3">
@@ -16002,7 +16002,7 @@
         <v>11</v>
       </c>
       <c r="F776" s="4">
-        <v>3.3168602880000004</v>
+        <v>8.2921507200000004</v>
       </c>
     </row>
     <row r="777" spans="1:6" x14ac:dyDescent="0.3">
@@ -16022,7 +16022,7 @@
         <v>15</v>
       </c>
       <c r="F777" s="4">
-        <v>1.0092983880000002</v>
+        <v>2.5232459700000001</v>
       </c>
     </row>
     <row r="778" spans="1:6" x14ac:dyDescent="0.3">
@@ -16042,7 +16042,7 @@
         <v>19</v>
       </c>
       <c r="F778" s="4">
-        <v>-2.7533407999999999E-2</v>
+        <v>-6.8833519999999995E-2</v>
       </c>
     </row>
     <row r="779" spans="1:6" x14ac:dyDescent="0.3">
@@ -16082,7 +16082,7 @@
         <v>23</v>
       </c>
       <c r="F780" s="4">
-        <v>14.333733192</v>
+        <v>35.834332979999999</v>
       </c>
     </row>
     <row r="781" spans="1:6" x14ac:dyDescent="0.3">
@@ -16142,7 +16142,7 @@
         <v>23</v>
       </c>
       <c r="F783" s="4">
-        <v>6.1098318440000003</v>
+        <v>15.27457961</v>
       </c>
     </row>
     <row r="784" spans="1:6" x14ac:dyDescent="0.3">
@@ -16162,7 +16162,7 @@
         <v>14</v>
       </c>
       <c r="F784" s="4">
-        <v>14.514279156000001</v>
+        <v>36.285697890000002</v>
       </c>
     </row>
     <row r="785" spans="1:6" x14ac:dyDescent="0.3">
@@ -16182,7 +16182,7 @@
         <v>24</v>
       </c>
       <c r="F785" s="4">
-        <v>-1.0965311160000002</v>
+        <v>-2.7413277900000002</v>
       </c>
     </row>
     <row r="786" spans="1:6" x14ac:dyDescent="0.3">
@@ -16222,7 +16222,7 @@
         <v>8</v>
       </c>
       <c r="F787" s="4">
-        <v>30.743518588000001</v>
+        <v>76.858796470000001</v>
       </c>
     </row>
     <row r="788" spans="1:6" x14ac:dyDescent="0.3">
@@ -16262,7 +16262,7 @@
         <v>21</v>
       </c>
       <c r="F789" s="4">
-        <v>0.56465910399999997</v>
+        <v>1.4116477599999999</v>
       </c>
     </row>
     <row r="790" spans="1:6" x14ac:dyDescent="0.3">
@@ -16282,7 +16282,7 @@
         <v>11</v>
       </c>
       <c r="F790" s="4">
-        <v>6.8658888039999999</v>
+        <v>17.164722009999998</v>
       </c>
     </row>
     <row r="791" spans="1:6" x14ac:dyDescent="0.3">
@@ -16302,7 +16302,7 @@
         <v>15</v>
       </c>
       <c r="F791" s="4">
-        <v>0.16144377600000001</v>
+        <v>0.40360943999999999</v>
       </c>
     </row>
     <row r="792" spans="1:6" x14ac:dyDescent="0.3">
@@ -16322,7 +16322,7 @@
         <v>15</v>
       </c>
       <c r="F792" s="4">
-        <v>0.94108382000000013</v>
+        <v>2.3527095500000001</v>
       </c>
     </row>
     <row r="793" spans="1:6" x14ac:dyDescent="0.3">
@@ -16342,7 +16342,7 @@
         <v>14</v>
       </c>
       <c r="F793" s="4">
-        <v>30.453836768000002</v>
+        <v>76.134591920000005</v>
       </c>
     </row>
     <row r="794" spans="1:6" x14ac:dyDescent="0.3">
@@ -16362,7 +16362,7 @@
         <v>15</v>
       </c>
       <c r="F794" s="4">
-        <v>0.27628159200000002</v>
+        <v>0.69070398</v>
       </c>
     </row>
     <row r="795" spans="1:6" x14ac:dyDescent="0.3">
@@ -16382,7 +16382,7 @@
         <v>23</v>
       </c>
       <c r="F795" s="4">
-        <v>5.0747462800000003</v>
+        <v>12.6868657</v>
       </c>
     </row>
     <row r="796" spans="1:6" x14ac:dyDescent="0.3">
@@ -16402,7 +16402,7 @@
         <v>15</v>
       </c>
       <c r="F796" s="4">
-        <v>0.279321808</v>
+        <v>0.69830451999999998</v>
       </c>
     </row>
     <row r="797" spans="1:6" x14ac:dyDescent="0.3">
@@ -16422,7 +16422,7 @@
         <v>23</v>
       </c>
       <c r="F797" s="4">
-        <v>15.608991004000002</v>
+        <v>39.022477510000002</v>
       </c>
     </row>
     <row r="798" spans="1:6" x14ac:dyDescent="0.3">
@@ -16462,7 +16462,7 @@
         <v>11</v>
       </c>
       <c r="F799" s="4">
-        <v>3.1094057240000001</v>
+        <v>7.7735143100000004</v>
       </c>
     </row>
     <row r="800" spans="1:6" x14ac:dyDescent="0.3">
@@ -16482,7 +16482,7 @@
         <v>14</v>
       </c>
       <c r="F800" s="4">
-        <v>16.358165592000002</v>
+        <v>40.895413980000001</v>
       </c>
     </row>
     <row r="801" spans="1:6" x14ac:dyDescent="0.3">
@@ -16502,7 +16502,7 @@
         <v>24</v>
       </c>
       <c r="F801" s="4">
-        <v>31.603090903999998</v>
+        <v>79.007727259999996</v>
       </c>
     </row>
     <row r="802" spans="1:6" x14ac:dyDescent="0.3">
@@ -16522,7 +16522,7 @@
         <v>18</v>
       </c>
       <c r="F802" s="4">
-        <v>111.421369568</v>
+        <v>278.55342392</v>
       </c>
     </row>
     <row r="803" spans="1:6" x14ac:dyDescent="0.3">
@@ -16542,7 +16542,7 @@
         <v>14</v>
       </c>
       <c r="F803" s="4">
-        <v>14.937323048</v>
+        <v>37.343307619999997</v>
       </c>
     </row>
     <row r="804" spans="1:6" x14ac:dyDescent="0.3">
@@ -16582,12 +16582,11 @@
         <v>23</v>
       </c>
       <c r="F805" s="4">
-        <v>5.9750079760000006</v>
+        <v>14.93751994</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>